--- a/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
+++ b/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
@@ -7179,7 +7179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7225,7 +7225,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -7235,22 +7235,22 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>관점 문구(data/text/*.yaml)</t>
+          <t>통합본 뷰 Lv0 편입(scripts/build_integrated_view.py)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>35개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성(RT 4·RD 5·VE 5·IA 6·AO 6·CC 4·IM 5). 인용 사례 45건([실제 사고]·[위협인텔]·[실증]), 실제 사고가 없는 8개 행(정찰·역량 확보·방어 회피 등)은 '공개 사고 미확인 — 사유'와 AI 역량 성숙도로 근거 표기. 참고 문헌은 ■ 관점·■ 대응 끝 '참고:' 줄로 인용</t>
+          <t>AI 활용 공격 매트릭스를 통합본 v4.1(요약 위협 237개)에 '뷰(view) Lv0'로 얹는 빌더·산출물 추가(D9). 렌즈라 기존 6개와 겹치므로 재수록 대신 연계만 하고 고유 위협 수에는 넣지 않음(이중계산 방지). 세부위협 35개의 연계(AI·CL·OT·SC·ID·PH)가 기존 237개 중 29개를 닿음(교차 54건). 산출물: integrated/output/통합_보안위협_매트릭스_v5_AI활용공격뷰.xlsx(5시트)·통합_AI활용공격뷰_v5.md·교차 CSV. 기존 통합 빌드와 독립(v4.1 산출물 불변)</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>③단계(v2) — 방어 관점(가드레일 D11: 공세 제작법·악용 절차 미기재, 탐지·대응 중심)으로 행마다 근거·통제를 연결</t>
+          <t>④단계 — 통합본에 Lv0 뷰로 편입(D9), 고유 위협 수 이중계산 방지</t>
         </is>
       </c>
     </row>
@@ -7267,22 +7267,22 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>시나리오</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
+          <t>관점 문구(data/text/*.yaml)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>실제 사고를 AI 활용 공격 흐름 8개로 재구성(ASN-01~08) — 자율·다중 에이전트 첩보(GTG-1002), 탈옥 모델 자율 하네스(Hermes), AI CLI 악용→클라우드 장악(s1ngularity), 딥페이크 화상회의 송금(Arup), AI 연동 악성코드→AI 서비스 C2(LAMEHUG), 딥페이크 생체 우회, 워크플로 대량 악용→연쇄 침해, LLMjacking·크립토재킹. 19개 단계·초크 포인트 17개</t>
+          <t>35개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성(RT 4·RD 5·VE 5·IA 6·AO 6·CC 4·IM 5). 인용 사례 45건([실제 사고]·[위협인텔]·[실증]), 실제 사고가 없는 8개 행(정찰·역량 확보·방어 회피 등)은 '공개 사고 미확인 — 사유'와 AI 역량 성숙도로 근거 표기. 참고 문헌은 ■ 관점·■ 대응 끝 '참고:' 줄로 인용</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점(초크 포인트)을 드러냄</t>
+          <t>③단계(v2) — 방어 관점(가드레일 D11: 공세 제작법·악용 절차 미기재, 탐지·대응 중심)으로 행마다 근거·통제를 연결</t>
         </is>
       </c>
     </row>
@@ -7299,29 +7299,29 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시나리오</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py</t>
+          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오 검사 이식 — oneline 50자·summary 2줄·■ 관점/실제 사례·■ 탐지/대응 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATLAS·ATT&amp;CK·OWASP·NIST·연계) 존재·행 매핑, 용어·가드레일(공세 제작법 표현 차단), 시나리오 ID·단계·사고·초크 포인트. 문구 35·시나리오 8을 --strict로 검증해 오류·경고 0</t>
+          <t>실제 사고를 AI 활용 공격 흐름 8개로 재구성(ASN-01~08) — 자율·다중 에이전트 첩보(GTG-1002), 탈옥 모델 자율 하네스(Hermes), AI CLI 악용→클라우드 장악(s1ngularity), 딥페이크 화상회의 송금(Arup), AI 연동 악성코드→AI 서비스 C2(LAMEHUG), 딥페이크 생체 우회, 워크플로 대량 악용→연쇄 침해, LLMjacking·크립토재킹. 19개 단계·초크 포인트 17개</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오의 사례·수치·ID·가드레일을 사고 DB·카탈로그와 기계적으로 대조</t>
+          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점(초크 포인트)을 드러냄</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -7331,22 +7331,22 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
+          <t>scripts/validate.py</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
+          <t>문구·시나리오 검사 이식 — oneline 50자·summary 2줄·■ 관점/실제 사례·■ 탐지/대응 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATLAS·ATT&amp;CK·OWASP·NIST·연계) 존재·행 매핑, 용어·가드레일(공세 제작법 표현 차단), 시나리오 ID·단계·사고·초크 포인트. 문구 35·시나리오 8을 --strict로 검증해 오류·경고 0</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
+          <t>문구·시나리오의 사례·수치·ID·가드레일을 사고 DB·카탈로그와 기계적으로 대조</t>
         </is>
       </c>
     </row>
@@ -7363,29 +7363,29 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>위험평가 결과</t>
+          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
+          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
+          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -7395,22 +7395,22 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>분류 체계(data/taxonomy.yaml)</t>
+          <t>위험평가 결과</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
+          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
+          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
         </is>
       </c>
     </row>
@@ -7427,22 +7427,22 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>사고 DB(data/incidents.yaml)</t>
+          <t>분류 체계(data/taxonomy.yaml)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
+          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
+          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
         </is>
       </c>
     </row>
@@ -7459,22 +7459,22 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>교차 매핑</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+          <t>사고 DB(data/incidents.yaml)</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
+          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
+          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
         </is>
       </c>
     </row>
@@ -7491,22 +7491,22 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>교차 매핑</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>참조 추출본(reference/)</t>
+          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
+          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
+          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
         </is>
       </c>
     </row>
@@ -7523,22 +7523,22 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py · taxonomy_rules.py</t>
+          <t>참조 추출본(reference/)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
         </is>
       </c>
     </row>
@@ -7555,20 +7555,52 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>scripts/validate.py · taxonomy_rules.py</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
           <t>결정</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>작업방향 D3~D9·D11·D12</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>emerging/작업방향.md 10장 권장안을 ①단계 착수 결정으로 확정 — D3(킬체인 7단계+AI 역할·자율성)·D4(발생가능성에 AI 역량 성숙도 신호)·D8(재인용+신규)·D9(통합본 뷰 Lv0, ④단계)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인). D5~D7은 영역 2(enterprise) 결정이라 영역 2 착수 시 확정</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>사용자 지침 — 남은 결정은 착수 시 확정</t>
         </is>

--- a/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
+++ b/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'보고서용 간략 매트릭스'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'통합 매트릭스'!$A$4:$AR$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'통합매트릭스_LITE'!$A$2:$S$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$O$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$O$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -675,7 +675,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>31건(2023~2026) — 실제 사고 24 · 위협인텔 2 · 실증·연구 5, AI 활용 확인 28·추정 3. 통합 v4.1 재인용 27건(origin) + 신규 4건. 연도별 2023:3·2024:2·2025:9·2026:17 (급증)</t>
+          <t>34건(2023~2026) — 실제 사고 28 · 위협인텔 1 · 실증·연구 5, AI 활용 확인 25·추정 8. 통합 v4.1 재인용 27건(origin) + 신규 7건. 연도별 2023:3·2024:2·2025:10·2026:19 (급증)</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>LLM Top 10(2025)·Agentic — 공격에 악용되는 제3자 AI 측 4개 연계(대부분 해당 없음)</t>
+          <t>LLM Top 10(2025)·Agentic — 공격에 악용되는 제3자 AI 측 9개 연계(대부분 해당 없음)</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>사고 DB 31건과 매핑 세부위협·AI 활용·성숙도·출처(근거 추적)</t>
+          <t>사고 DB 34건과 매핑 세부위협·AI 활용·성숙도·출처(근거 추적)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>매우 높음 11 · 높음 7 · 보통 16 · 낮음 1</t>
+          <t>매우 높음 10 · 높음 9 · 보통 15 · 낮음 1</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>실제 사고 확인 22 · 실사용 역량(성숙도) 7 · 실증·공개 PoC 6 · 이론·연구 시연 0</t>
+          <t>실제 사고 확인 23 · 실사용 역량(성숙도) 7 · 실증·공개 PoC 5 · 이론·연구 시연 0</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>35/35개 작성 — 전 항목 완료 | scripts/validate.py 세부위협 35개(문구 35) · 사고 31건 · 시나리오 8개 · 실제 사고가 매핑된 행 22개 · 인용 사례 45건</t>
+          <t>35/35개 작성 — 전 항목 완료 | scripts/validate.py 세부위협 35개(문구 35) · 사고 34건 · 시나리오 8개 · 실제 사고가 매핑된 행 23개 · 인용 사례 44건</t>
         </is>
       </c>
     </row>
@@ -1131,15 +1131,15 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1. AIA-AO-01 단일 자율 공격 에이전트 실행 — 매우 높음, 실제 사고 4건(성숙도 실사용)
-2. AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 — 매우 높음, 실제 사고 3건(성숙도 실증)
-3. AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 — 매우 높음, 실제 사고 3건(성숙도 실사용)
-4. AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-5. AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-6. AIA-IA-03 딥페이크 기반 생체·본인확인 우회 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-7. AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-8. AIA-IA-02.1 영상 딥페이크 사칭 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-9. AIA-VE-03.1 AI 생성·AI 연동 악성코드 — 매우 높음, 실제 사고 2건(성숙도 실사용)
+          <t>1. AIA-AO-01 단일 자율 공격 에이전트 실행 — 매우 높음, 실제 사고 7건(성숙도 실사용)
+2. AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 — 매우 높음, 실제 사고 4건(성숙도 실사용)
+3. AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 — 매우 높음, 실제 사고 3건(성숙도 실증)
+4. AIA-VE-03.1 AI 생성·AI 연동 악성코드 — 매우 높음, 실제 사고 3건(성숙도 실사용)
+5. AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 — 매우 높음, 실제 사고 3건(성숙도 실사용)
+6. AIA-AO-02 다중 에이전트 공격 조율 — 매우 높음, 실제 사고 3건(성숙도 실사용)
+7. AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
+8. AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
+9. AIA-IA-03 딥페이크 기반 생체·본인확인 우회 — 매우 높음, 실제 사고 2건(성숙도 실사용)
 10. AIA-RD-04 공세 AI 에이전트·공격 하네스 구축 — 매우 높음, 실제 사고 2건(성숙도 실사용)</t>
         </is>
       </c>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>자율 취약점 발굴·익스플로잇 생성(VE)·역량 확보(RD)·일부 정찰은 실제 사고보다 실증·위협인텔 근거가 큼. 실제 사고가 매핑된 세부위협 22/35개 — 나머지는 성숙도·실증·위협인텔로 평가</t>
+          <t>자율 취약점 발굴·익스플로잇 생성(VE)·역량 확보(RD)·일부 정찰은 실제 사고보다 실증·위협인텔 근거가 큼. 실제 사고가 매핑된 세부위협 23/35개 — 나머지는 성숙도·실증·위협인텔로 평가</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4200,12 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>ASI-T01</t>
+          <t>ASI01</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>에이전트 인가·제어 탈취</t>
+          <t>에이전트 목표 탈취</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -4214,11 +4214,11 @@
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-04, AIA-AO-01, AIA-AO-02</t>
+          <t>AIA-IA-04, AIA-CC-04</t>
         </is>
       </c>
     </row>
@@ -4421,11 +4421,11 @@
         <v>7</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1, AIA-IM-01, AIA-IA-02.2, AIA-IA-01.1, AIA-RT-01.1, AIA-IA-01.2, AIA-IA-04</t>
+          <t>AIA-IA-01.1, AIA-IM-01, AIA-IA-02.1, AIA-IA-02.2, AIA-IA-04, AIA-RT-01.1, AIA-IA-01.2</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-03, AIA-IA-02.1, AIA-IM-01, AIA-IA-02.2</t>
+          <t>AIA-IA-03, AIA-IM-01, AIA-IA-02.1, AIA-IA-02.2</t>
         </is>
       </c>
     </row>
@@ -4651,11 +4651,11 @@
         <v>5</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-02, AIA-CC-01, AIA-RT-02, AIA-IA-01.1, AIA-RD-03</t>
+          <t>AIA-IM-02, AIA-IA-01.1, AIA-CC-01, AIA-RT-02, AIA-RD-03</t>
         </is>
       </c>
     </row>
@@ -4697,11 +4697,11 @@
         <v>24</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01, AIA-AO-05, AIA-AO-04, AIA-AO-03.2, AIA-AO-03.1, AIA-IM-02, AIA-VE-03.1, AIA-RD-04, AIA-AO-02, AIA-IM-03.1, AIA-CC-02, AIA-CC-01, AIA-IM-03.2, AIA-RT-02, AIA-IA-01.1, AIA-CC-03, AIA-RD-02, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-IA-01.2, AIA-RD-03, AIA-IA-04</t>
+          <t>AIA-AO-01, AIA-IM-02, AIA-AO-05, AIA-VE-03.1, AIA-AO-04, AIA-AO-02, AIA-AO-03.2, AIA-AO-03.1, AIA-RD-04, AIA-IA-01.1, AIA-IM-03.1, AIA-CC-02, AIA-CC-01, AIA-IM-03.2, AIA-RT-02, AIA-IA-04, AIA-CC-03, AIA-RD-02, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-IA-01.2, AIA-RD-03</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6142,22 +6142,22 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>AI-01-02</t>
+          <t>AI-01-03</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>AI 모델 접근 확보 및 환경 탐색</t>
+          <t>공격 도구·인프라 및 AI 자원 확보</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1, AIA-VE-01.2, AIA-VE-02</t>
+          <t>AIA-RT-03, AIA-RD-01.1, AIA-RD-01.2, AIA-RD-02</t>
         </is>
       </c>
     </row>
@@ -6169,22 +6169,22 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>AI-01-03</t>
+          <t>AI-01-05</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>공격 도구·인프라 및 AI 자원 확보</t>
+          <t>자율·다중 에이전트 기반 공격</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>AIA-RT-03, AIA-RD-01.1, AIA-RD-01.2, AIA-RD-02</t>
+          <t>AIA-RD-04, AIA-AO-01, AIA-AO-02, AIA-AO-05, AIA-IM-02, AIA-IM-04</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6196,12 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>AI-01-05</t>
+          <t>AI-01-06</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>자율·다중 에이전트 기반 공격</t>
+          <t>AI 연동 악성코드</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-04, AIA-AO-01, AIA-AO-02, AIA-AO-05, AIA-IM-02, AIA-IM-04</t>
+          <t>AIA-VE-03.1, AIA-VE-03.2, AIA-CC-02</t>
         </is>
       </c>
     </row>
@@ -6223,22 +6223,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>AI-01-06</t>
+          <t>AI-01-08</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>AI 연동 악성코드</t>
+          <t>AI 생성 피싱 및 신뢰 주체 사칭</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>매우 높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1, AIA-VE-03.2, AIA-CC-02</t>
+          <t>AIA-IA-01.1, AIA-IA-01.2, AIA-IA-02.1, AIA-IA-02.2, AIA-IA-03, AIA-IA-04, AIA-IM-01</t>
         </is>
       </c>
     </row>
@@ -6250,22 +6250,22 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>AI-01-08</t>
+          <t>AI-01-09</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>AI 생성 피싱 및 신뢰 주체 사칭</t>
+          <t>AI 서비스 경유 은닉 C2</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-01.1, AIA-IA-01.2, AIA-IA-02.1, AIA-IA-02.2, AIA-IA-03, AIA-IA-04, AIA-IM-01</t>
+          <t>AIA-CC-01</t>
         </is>
       </c>
     </row>
@@ -6277,22 +6277,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>AI-01-09</t>
+          <t>AI-04-04</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스 경유 은닉 C2</t>
+          <t>적대적 입력 기반 판단 회피</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>매우 높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-01</t>
+          <t>AIA-CC-03</t>
         </is>
       </c>
     </row>
@@ -6304,22 +6304,22 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>AI-04-04</t>
+          <t>AI-06-04</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>적대적 입력 기반 판단 회피</t>
+          <t>생성 코드·도구 인자 명령 실행</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-03</t>
+          <t>AIA-AO-03.2</t>
         </is>
       </c>
     </row>
@@ -6331,12 +6331,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>AI-06-04</t>
+          <t>AI-08-05</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>생성 코드·도구 인자 명령 실행</t>
+          <t>악성 에이전트 도구 유통과 AI 코딩 도구 오염</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-03.2</t>
+          <t>AIA-AO-04, AIA-CC-04</t>
         </is>
       </c>
     </row>
@@ -6358,22 +6358,22 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>AI-08-05</t>
+          <t>AI-09-02</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>악성 에이전트 도구 유통과 AI 코딩 도구 오염</t>
+          <t>AI 과금 폭탄 및 에이전트 루프 소모</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>매우 높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-04, AIA-CC-04</t>
+          <t>AIA-IM-03.2</t>
         </is>
       </c>
     </row>
@@ -6385,22 +6385,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>AI-09-02</t>
+          <t>AI-09-03</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>AI 과금 폭탄 및 에이전트 루프 소모</t>
+          <t>외부 노출 AI 서비스</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-03.2</t>
+          <t>AIA-RD-03, AIA-IM-03.1</t>
         </is>
       </c>
     </row>
@@ -6412,49 +6412,49 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>AI-09-03</t>
+          <t>AI-09-05</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>외부 노출 AI 서비스</t>
+          <t>로컬 AI 에이전트·확장 프로그램 장악</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>매우 높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-03, AIA-IM-03.1</t>
+          <t>AIA-AO-03.1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>통합 v4.1 AI 보안위협</t>
+          <t>통합 v4.1 클라우드 보안위협</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>AI-09-05</t>
+          <t>CL-CA-06</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>로컬 AI 에이전트·확장 프로그램 장악</t>
+          <t>메타데이터·컨테이너 API 경유 자격증명 탈취</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-03.1</t>
+          <t>AIA-AO-05</t>
         </is>
       </c>
     </row>
@@ -6466,12 +6466,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>CL-CA-06</t>
+          <t>CL-IM-06</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>메타데이터·컨테이너 API 경유 자격증명 탈취</t>
+          <t>컴퓨팅 자원 탈취(크립토재킹)</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-05</t>
+          <t>AIA-IM-03.1</t>
         </is>
       </c>
     </row>
@@ -6493,12 +6493,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>CL-IM-06</t>
+          <t>CL-IM-07</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>컴퓨팅 자원 탈취(크립토재킹)</t>
+          <t>관리형 서비스 악용(LLMjacking·SMS 펌핑)</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-03.1</t>
+          <t>AIA-IM-03.2</t>
         </is>
       </c>
     </row>
@@ -6520,49 +6520,49 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>CL-IM-07</t>
+          <t>CL-RD-01</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>관리형 서비스 악용(LLMjacking·SMS 펌핑)</t>
+          <t>공격 인프라 확보(유사 도메인·클라우드 서버)</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>매우 높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-03.2</t>
+          <t>AIA-RD-03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>통합 v4.1 클라우드 보안위협</t>
+          <t>통합 v4.1 신원 보안위협</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>CL-RD-01</t>
+          <t>ID-CI-03</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>공격 인프라 확보(유사 도메인·클라우드 서버)</t>
+          <t>명의 도용·본인확인 우회(딥페이크 포함)</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-03</t>
+          <t>AIA-IA-03</t>
         </is>
       </c>
     </row>
@@ -6574,22 +6574,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>ID-CI-03</t>
+          <t>ID-CR-01</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>명의 도용·본인확인 우회(딥페이크 포함)</t>
+          <t>단말 자격증명 탈취(인포스틸러·덤프·키로깅)</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-03</t>
+          <t>AIA-AO-05</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ID-CR-01</t>
+          <t>ID-IM-01</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>단말 자격증명 탈취(인포스틸러·덤프·키로깅)</t>
+          <t>계정 장악 기반 금전 사기(BEC·송금·사칭 게시)</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-05</t>
+          <t>AIA-IM-01</t>
         </is>
       </c>
     </row>
@@ -6628,12 +6628,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>ID-IM-01</t>
+          <t>ID-IM-03</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>계정 장악 기반 금전 사기(BEC·송금·사칭 게시)</t>
+          <t>계정 기반 대량 데이터 탈취·갈취</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-01</t>
+          <t>AIA-IM-02</t>
         </is>
       </c>
     </row>
@@ -6655,22 +6655,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>ID-IM-03</t>
+          <t>ID-SE-01</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>계정 기반 대량 데이터 탈취·갈취</t>
+          <t>인증 피싱(AiTM·OAuth 동의·문자·메신저)</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>매우 높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-02</t>
+          <t>AIA-IA-01.1, AIA-IA-01.2</t>
         </is>
       </c>
     </row>
@@ -6682,12 +6682,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>ID-SE-01</t>
+          <t>ID-SE-04</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>인증 피싱(AiTM·OAuth 동의·문자·메신저)</t>
+          <t>딥페이크·AI 음성 사칭(송금·접근 요청)</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -6697,88 +6697,88 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-01.1, AIA-IA-01.2</t>
+          <t>AIA-IA-02.1, AIA-IA-02.2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>통합 v4.1 신원 보안위협</t>
+          <t>통합 v4.1 OT 보안위협</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>ID-SE-04</t>
+          <t>OT-IR-01</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>딥페이크·AI 음성 사칭(송금·접근 요청)</t>
+          <t>데이터 파괴(와이퍼)</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1, AIA-IA-02.2</t>
+          <t>AIA-VE-03.2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>통합 v4.1 OT 보안위협</t>
+          <t>통합 v4.1 물리·인적 보안위협</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>OT-IR-01</t>
+          <t>PH-RC-01</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>데이터 파괴(와이퍼)</t>
+          <t>공개정보 기반 핵심 인력·시설 파악</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>매우 높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.2</t>
+          <t>AIA-RT-01.1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>통합 v4.1 물리·인적 보안위협</t>
+          <t>통합 v4.1 공급망 보안위협</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>PH-RC-01</t>
+          <t>SC-BD-01</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>공개정보 기반 핵심 인력·시설 파악</t>
+          <t>오염된 파이프라인 실행(PPE)</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우 높음</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>AIA-RT-01.1</t>
+          <t>AIA-AO-04</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>SC-BD-01</t>
+          <t>SC-DE-01</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>오염된 파이프라인 실행(PPE)</t>
+          <t>개발자 단말 침해와 개발자 대상 사회공학</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-04</t>
+          <t>AIA-AO-03.1</t>
         </is>
       </c>
     </row>
@@ -6817,12 +6817,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>SC-DE-01</t>
+          <t>SC-DE-02</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>개발자 단말 침해와 개발자 대상 사회공학</t>
+          <t>IDE 확장·개발 도구·툴체인 오염</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-03.1</t>
+          <t>AIA-AO-03.2, AIA-CC-04</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>SC-DE-02</t>
+          <t>SC-DP-04</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>IDE 확장·개발 도구·툴체인 오염</t>
+          <t>알려진 취약점이 있는 구성요소 사용</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -6858,33 +6858,6 @@
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>AIA-AO-03.2, AIA-CC-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>통합 v4.1 공급망 보안위협</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>SC-DP-04</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>알려진 취약점이 있는 구성요소 사용</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>AIA-VE-01.2</t>
         </is>
@@ -7646,7 +7619,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>순위 = 위험도 → 실제 사고 수 → ATLAS 사례 → 성숙도 → AIA-ID | 2026-10-25</t>
+          <t>순위 = 위험도 → 실제 사고 수 → ATLAS 사례 → 성숙도 → AIA-ID | 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7777,11 +7750,11 @@
         </is>
       </c>
       <c r="L5" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 Langflow·n8n 자율 공격 시도(2026-07) (AII-027)</t>
+          <t>[실제 사고] 거의 전권을 위임한 AI 에이전트로 CRM 업체 고객 데이터 반출(CrowdStrike 행위자 4)(2026-10) (AII-034)</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
@@ -7796,22 +7769,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>[AO] 자율 실행·확산</t>
+          <t>[IM] 영향·규모화</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-05</t>
+          <t>AIA-IM-02</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>AI 가속 자격증명 탈취·내부 확산</t>
+          <t>AI 가속 대규모 데이터 탈취·반출</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>AI 가속 자격증명 탈취·측면 이동으로 클라우드 전반 급속 장악</t>
+          <t>자율 에이전트의 자동 수집·반출로 대규모 데이터 유출</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -7841,20 +7814,20 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] AI 보조 클라우드 침입(Sygnia 익명 사례)(2026-06) (AII-022)</t>
+          <t>[실제 사고] 거의 전권을 위임한 AI 에이전트로 CRM 업체 고객 데이터 반출(CrowdStrike 행위자 4)(2026-10) (AII-034)</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>자격증명의 비정상 사용·급속한 권한 확대·측면 이동을 아이덴티티·클라우드 로그로 탐지(NIST AC-2·SI-4)</t>
+          <t>대량·자동화된 데이터 접근·반출 패턴과 비정상 egress를 모니터링(NIST SI-4·AU-6·SC-7)</t>
         </is>
       </c>
     </row>
@@ -7869,17 +7842,17 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-04</t>
+          <t>AIA-AO-05</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>자율 에이전트의 CI/CD·워크플로 대량 악용</t>
+          <t>AI 가속 자격증명 탈취·내부 확산</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>자율 에이전트가 CI/CD·워크플로 결함을 자동·대량 악용</t>
+          <t>AI 가속 자격증명 탈취·측면 이동으로 클라우드 전반 급속 장악</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -7904,12 +7877,12 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="L7" s="8" t="n">
@@ -7917,12 +7890,12 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] prt-scan — 취약 GitHub 워크플로 대상 기회주의 공급망 캠페인(2026-04) (AII-020)</t>
+          <t>[실제 사고] AI 보조 클라우드 침입(Sygnia 익명 사례)(2026-06) (AII-022)</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지(NIST SI-4)</t>
+          <t>자격증명의 비정상 사용·급속한 권한 확대·측면 이동을 아이덴티티·클라우드 로그로 탐지(NIST AC-2·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7932,22 +7905,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>[AO] 자율 실행·확산</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-03.2</t>
+          <t>AIA-VE-03.1</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>AI 개발 도구 신뢰·설정 악용</t>
+          <t>AI 생성·AI 연동 악성코드</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>AI 개발 도구의 광범위 실행 권한·신뢰를 공격 수행에 악용</t>
+          <t>AI 생성·AI 연동 악성코드로 변종 양산·탐지 회피</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -7967,12 +7940,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -7981,16 +7954,16 @@
         </is>
       </c>
       <c r="L8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)(2026-03) (AII-019)</t>
+          <t>[실제 사고] BREEZE COMET — 생성형 AI를 악성코드 개발에 활용한 브라질 금융 공격(2026-09) (AII-024)</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>AI 개발 도구의 비정상 설정 변경·과도한 권한 사용·공급망 산출물 변조를 탐지(NIST SI-4·SA-15)</t>
+          <t>시그니처가 아닌 행위·맥락 기반으로 변종 악성코드를 탐지하고 무결성 변화를 감시(NIST SI-3·SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -8005,17 +7978,17 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-03.1</t>
+          <t>AIA-AO-04</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>피해 단말의 AI CLI·로컬 에이전트 악용</t>
+          <t>자율 에이전트의 CI/CD·워크플로 대량 악용</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>피해 단말에 설치된 AI CLI를 공격 실행 엔진으로 악용</t>
+          <t>자율 에이전트가 CI/CD·워크플로 결함을 자동·대량 악용</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -8049,16 +8022,16 @@
         </is>
       </c>
       <c r="L9" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)(2026-03) (AII-018)</t>
+          <t>[실제 사고] prt-scan — 취약 GitHub 워크플로 대상 기회주의 공급망 캠페인(2026-04) (AII-020)</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지(NIST SI-4)</t>
+          <t>워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -8068,22 +8041,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[AO] 자율 실행·확산</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-03</t>
+          <t>AIA-AO-02</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>딥페이크 기반 생체·본인확인 우회</t>
+          <t>다중 에이전트 공격 조율</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>딥페이크로 생체·비대면 본인확인(KYC) 우회해 계정 장악</t>
+          <t>상위 오케스트레이터가 다중 하위 에이전트로 공격 웨이브 병렬화</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -8103,12 +8076,12 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>완전자율</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
@@ -8117,16 +8090,16 @@
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)(2024-02) (AII-013)</t>
+          <t>[실제 사고] AI 에이전트 하네스로 여러 나라 정부·민간 20곳 이상 표적(CrowdStrike 행위자 2)(2026-10) (AII-032)</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설·접근 패턴을 모니터링(NIST IA-2·AC-2)</t>
+          <t>동시다발 표적에 걸친 유사 패턴·상관 이벤트와 병렬 세션 급증을 탐지(NIST SI-4·CA-7)</t>
         </is>
       </c>
     </row>
@@ -8136,22 +8109,22 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>[IM] 영향·규모화</t>
+          <t>[AO] 자율 실행·확산</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>AIA-IM-02</t>
+          <t>AIA-AO-03.2</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>AI 가속 대규모 데이터 탈취·반출</t>
+          <t>AI 개발 도구 신뢰·설정 악용</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>자율 에이전트의 자동 수집·반출로 대규모 데이터 유출</t>
+          <t>AI 개발 도구의 광범위 실행 권한·신뢰를 공격 수행에 악용</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -8176,7 +8149,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -8189,12 +8162,12 @@
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 다중 에이전트 프레임워크의 대만 정부 시스템 침해(2026-08) (AII-009)</t>
+          <t>[실제 사고] BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)(2026-03) (AII-019)</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>대량·자동화된 데이터 접근·반출 패턴과 비정상 egress를 모니터링(NIST SI-4·AU-6·SC-7)</t>
+          <t>AI 개발 도구의 비정상 설정 변경·과도한 권한 사용·공급망 산출물 변조를 탐지(NIST SI-4·SA-15)</t>
         </is>
       </c>
     </row>
@@ -8204,22 +8177,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[AO] 자율 실행·확산</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1</t>
+          <t>AIA-AO-03.1</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>영상 딥페이크 사칭</t>
+          <t>피해 단말의 AI CLI·로컬 에이전트 악용</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>영상 딥페이크 사칭으로 화상회의·면접 신뢰 악용</t>
+          <t>피해 단말에 설치된 AI CLI를 공격 실행 엔진으로 악용</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -8239,12 +8212,12 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -8257,12 +8230,12 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-02) (AII-002)</t>
+          <t>[실제 사고] s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)(2026-03) (AII-018)</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>고액·고위험 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검(NIST IA-2)</t>
+          <t>AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -8272,22 +8245,22 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1</t>
+          <t>AIA-IA-03</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>AI 생성·AI 연동 악성코드</t>
+          <t>딥페이크 기반 생체·본인확인 우회</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>AI 생성·AI 연동 악성코드로 변종 양산·탐지 회피</t>
+          <t>딥페이크로 생체·비대면 본인확인(KYC) 우회해 계정 장악</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -8325,12 +8298,12 @@
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] BREEZE COMET — 생성형 AI를 악성코드 개발에 활용한 브라질 금융 공격(2026-09) (AII-024)</t>
+          <t>[실제 사고] GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)(2024-02) (AII-013)</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>시그니처가 아닌 행위·맥락 기반으로 변종 악성코드를 탐지하고 무결성 변화를 감시(NIST SI-3·SI-4·SI-7)</t>
+          <t>라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설·접근 패턴을 모니터링(NIST IA-2·AC-2)</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8366,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 Langflow·n8n 자율 공격 시도(2026-07) (AII-027)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
@@ -8408,27 +8381,27 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>[AO] 자율 실행·확산</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-02</t>
+          <t>AIA-IA-01.1</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>다중 에이전트 공격 조율</t>
+          <t>AI 생성 대량 피싱·미끼</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>상위 오케스트레이터가 다중 하위 에이전트로 공격 웨이브 병렬화</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -8438,17 +8411,17 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>완전자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
@@ -8461,12 +8434,12 @@
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 다중 에이전트 프레임워크의 대만 정부 시스템 침해(2026-08) (AII-009)</t>
+          <t>[실제 사고] CaptiveCrunch — Midnight Blizzard 하위 그룹의 AI 보조 악성코드 개발(2026-07) (AII-023)</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>동시다발 표적에 걸친 유사 패턴·상관 이벤트와 병렬 세션 급증을 탐지(NIST SI-4·CA-7)</t>
+          <t>발신 평판·행위·링크 분석 등 콘텐츠 품질에 덜 의존하는 다중 신호로 피싱을 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -8612,22 +8585,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-03.2</t>
+          <t>AIA-IA-02.1</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>AI 생성 와이퍼·파괴 스크립트</t>
+          <t>영상 딥페이크 사칭</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
+          <t>영상 딥페이크 사칭으로 화상회의·면접 신뢰 악용</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -8665,12 +8638,12 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)(2026-01) (AII-006)</t>
+          <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-02) (AII-002)</t>
         </is>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>대량 파일 변경·삭제와 파괴형 실행 행위를 조기 탐지하고 백업 무결성을 감시(NIST SI-3·SI-7)</t>
+          <t>고액·고위험 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검(NIST IA-2)</t>
         </is>
       </c>
     </row>
@@ -8680,22 +8653,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-02</t>
+          <t>AIA-VE-03.2</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>실행 중 AI 명령 동적 생성 악성코드</t>
+          <t>AI 생성 와이퍼·파괴 스크립트</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
+          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -8715,12 +8688,12 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -8733,12 +8706,12 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
+          <t>[실제 사고] 2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)(2026-01) (AII-006)</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위·맥락 기반으로 탐지(NIST SI-3·SI-4·AU-6)</t>
+          <t>대량 파일 변경·삭제와 파괴형 실행 행위를 조기 탐지하고 백업 무결성을 감시(NIST SI-3·SI-7)</t>
         </is>
       </c>
     </row>
@@ -8753,17 +8726,17 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-01</t>
+          <t>AIA-CC-02</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
+          <t>실행 중 AI 명령 동적 생성 악성코드</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
+          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -8783,7 +8756,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -8806,7 +8779,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스로의 비정상 egress 패턴·데이터량과 자동화된 세션을 모니터링(NIST SC-7·SI-4·AU-6)</t>
+          <t>LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위·맥락 기반으로 탐지(NIST SI-3·SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -8816,22 +8789,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1</t>
+          <t>AIA-CC-01</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>AI 자율 취약점 발굴(버그 헌팅)</t>
+          <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>AI 에이전트의 자율 취약점 발굴(미공개 취약점 자동 탐색)</t>
+          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -8851,7 +8824,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>완전자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -8865,16 +8838,16 @@
         </is>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>[실증] XBOW 등 자율 펜테스트 에이전트의 취약점 대량 발견(2026-04) (AII-029)</t>
+          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>자사 자산에 대한 자동·대규모 취약점 탐색 정황과 비정상 접근 패턴을 모니터링(NIST RA-5)</t>
+          <t>AI 서비스로의 비정상 egress 패턴·데이터량과 자동화된 세션을 모니터링(NIST SC-7·SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -8889,17 +8862,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-02</t>
+          <t>AIA-VE-01.1</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>AI 익스플로잇 자동 생성·개발</t>
+          <t>AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>AI 익스플로잇 자동 생성으로 익스플로잇 개발 병목 제거</t>
+          <t>AI 에이전트의 자율 취약점 발굴(미공개 취약점 자동 탐색)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -8919,7 +8892,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>완전자율</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -8937,12 +8910,12 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>[위협인텔] AI로 개발한 것으로 판단되는 0-day 익스플로잇 실사용(GTIG 보고)(2026-05) (AII-030)</t>
+          <t>[실증] Big Sleep — AI 에이전트의 실악용 임박 취약점 사전 발견(2025-07) (AII-028)</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>공개 직후 집중되는 익스플로잇 시도와 알려진 취약점의 비정상 악용을 모니터링(NIST RA-5)</t>
+          <t>자사 자산에 대한 자동·대규모 취약점 탐색 정황과 비정상 접근 패턴을 모니터링(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -8952,27 +8925,27 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>[IM] 영향·규모화</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>AIA-IM-03.2</t>
+          <t>AIA-VE-02</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>LLMjacking·AI 과금 폭탄</t>
+          <t>AI 익스플로잇 자동 생성·개발</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>탈취 자격증명으로 관리형 LLM·GPU 무단 사용(LLMjacking)</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>AI 익스플로잇 자동 생성으로 익스플로잇 개발 병목 제거</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -8982,12 +8955,12 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -9001,16 +8974,16 @@
         </is>
       </c>
       <c r="L23" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 공개 S3 버킷 노출 자격증명 경유 LLMjacking·GPU 악용(2026-02) (AII-016)</t>
+          <t>[위협인텔] AI로 개발한 0-day 익스플로잇을 준비한 범죄 조직의 대량 악용 계획(GTIG 사전 차단)(2026-05) (AII-030)</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>관리형 LLM·GPU의 비정상 사용량·과금 급증과 비정상 추론 호출을 모니터링(NIST AC-2·SI-4)</t>
+          <t>공개 직후 집중되는 익스플로잇 시도와 알려진 취약점의 비정상 악용을 모니터링(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -9020,22 +8993,22 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[IM] 영향·규모화</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-02</t>
+          <t>AIA-IM-03.2</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
+          <t>LLMjacking·AI 과금 폭탄</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
+          <t>탈취 자격증명으로 관리형 LLM·GPU 무단 사용(LLMjacking)</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -9055,12 +9028,12 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
@@ -9073,12 +9046,12 @@
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 Langflow·n8n 자율 공격 시도(2026-07) (AII-027)</t>
+          <t>[실제 사고] 공개 S3 버킷 노출 자격증명 경유 LLMjacking·GPU 악용(2026-02) (AII-016)</t>
         </is>
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>외부 노출 자산을 지속 식별하고 비정상적으로 빠른 열거·탐침 패턴을 모니터링(NIST RA-5·SI-4)</t>
+          <t>관리형 LLM·GPU의 비정상 사용량·과금 급증과 비정상 추론 호출을 모니터링(NIST AC-2·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9088,22 +9061,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-02.2</t>
+          <t>AIA-RT-02</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>음성 딥페이크 사칭</t>
+          <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
+          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -9123,7 +9096,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -9141,12 +9114,12 @@
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)(2023-09) (AII-011)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>헬프데스크·계정 복구 요청의 음성 사칭 징후와 비정상 MFA 등록을 점검(NIST IA-2)</t>
+          <t>외부 노출 자산을 지속 식별하고 비정상적으로 빠른 열거·탐침 패턴을 모니터링(NIST RA-5·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9156,22 +9129,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-04</t>
+          <t>AIA-IA-02.2</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
+          <t>음성 딥페이크 사칭</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
+          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -9196,12 +9169,12 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="L26" s="8" t="n">
@@ -9209,12 +9182,12 @@
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Amazon Q Developer 확장에 삭제 지시 주입(2025-07) (AII-003)</t>
+          <t>[실제 사고] Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)(2023-09) (AII-011)</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>규칙·설정 파일의 비가시 문자·숨은 지시와 생성 코드의 의심 변경을 검사(NIST SI-7·SA-15)</t>
+          <t>헬프데스크·계정 복구 요청의 음성 사칭 징후와 비정상 MFA 등록을 점검(NIST IA-2)</t>
         </is>
       </c>
     </row>
@@ -9224,22 +9197,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-03</t>
+          <t>AIA-CC-04</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
+          <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
+          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -9259,17 +9232,17 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="L27" s="8" t="n">
@@ -9277,12 +9250,12 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 Langflow·n8n 자율 공격 시도(2026-07) (AII-027)</t>
+          <t>[실제 사고] Amazon Q Developer 확장에 삭제 지시 주입(2025-07) (AII-003)</t>
         </is>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>자사 자산의 공개 취약점·PoC 공개 동향을 신속 수집해 노출 여부를 대조(NIST RA-5)</t>
+          <t>규칙·설정 파일의 비가시 문자·숨은 지시와 생성 코드의 의심 변경을 검사(NIST SI-7·SA-15)</t>
         </is>
       </c>
     </row>
@@ -9292,22 +9265,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-01.1</t>
+          <t>AIA-RT-03</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>AI 생성 대량 피싱·미끼</t>
+          <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -9327,7 +9300,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -9345,12 +9318,12 @@
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] O365 디바이스 코드 피싱 캠페인(EvilTokens PhaaS)(2026-03) (AII-021)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>발신 평판·행위·링크 분석 등 콘텐츠 품질에 덜 의존하는 다중 신호로 피싱을 탐지(NIST SI-4)</t>
+          <t>자사 자산의 공개 취약점·PoC 공개 동향을 신속 수집해 노출 여부를 대조(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -9360,22 +9333,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-03</t>
+          <t>AIA-IA-04</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 방어 회피·난독화</t>
+          <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
+          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -9395,12 +9368,12 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
@@ -9409,16 +9382,16 @@
         </is>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 20건·성숙도 실증]</t>
+          <t>[실제 사고] Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)(2023-11) (AII-012)</t>
         </is>
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>행위·맥락 기반 탐지와 다중 엔진·이상 탐지로 변형·적대적 회피를 보완 탐지(NIST SI-3·SI-4)</t>
+          <t>에이전트·사용자의 미끼 실행 흐름(클립보드→터미널 등)과 의심 링크 접근을 행위 기반으로 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9428,22 +9401,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-02</t>
+          <t>AIA-CC-03</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
+          <t>AI 기반 방어 회피·난독화</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
+          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -9473,7 +9446,7 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="L30" s="8" t="n">
@@ -9481,12 +9454,12 @@
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
+          <t>[ATLAS 사례 20건·성숙도 실증]</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>실행 단계에서 생성형 도구의 산출물(비정형 스크립트·명령)을 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
+          <t>행위·맥락 기반 탐지와 다중 엔진·이상 탐지로 변형·적대적 회피를 보완 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9496,22 +9469,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-01.1</t>
+          <t>AIA-RD-02</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 공개정보 수집·인물 프로파일링</t>
+          <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
+          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -9554,7 +9527,7 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>자사·임직원 대상 공개정보 노출과 비정상 수집 정황(대량 조회·스크레이핑)을 위협 인텔리전스로 점검(NIST PM-16·SI-4)</t>
+          <t>실행 단계에서 생성형 도구의 산출물(비정형 스크립트·명령)을 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9564,22 +9537,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-01.1</t>
+          <t>AIA-RT-01.1</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>다크 LLM·탈옥 모델 확보</t>
+          <t>AI 기반 공개정보 수집·인물 프로파일링</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
+          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -9599,12 +9572,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -9617,12 +9590,12 @@
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 13건·성숙도 실사용]</t>
+          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>지하 시장·공세 LLM 동향을 위협 인텔로 수집하고 자사 대상 악용 징후를 모니터링(NIST PM-16·SI-4)</t>
+          <t>자사·임직원 대상 공개정보 노출과 비정상 수집 정황(대량 조회·스크레이핑)을 위협 인텔리전스로 점검(NIST PM-16·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9632,22 +9605,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-01.2</t>
+          <t>AIA-RD-01.1</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 표적 환경·관계 분석</t>
+          <t>다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
+          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -9667,17 +9640,17 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="L33" s="8" t="n">
@@ -9685,12 +9658,12 @@
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 8건·성숙도 실증]</t>
+          <t>[ATLAS 사례 13건·성숙도 실사용]</t>
         </is>
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>공개된 조직·거래 정보의 노출 범위와 사칭에 쓰일 수 있는 맥락을 주기적으로 점검(NIST PM-16·SI-4)</t>
+          <t>지하 시장·공세 LLM 동향을 위협 인텔로 수집하고 자사 대상 악용 징후를 모니터링(NIST PM-16·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9700,22 +9673,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>[IM] 영향·규모화</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>AIA-IM-04</t>
+          <t>AIA-RT-01.2</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>AI 활용 공격의 규모화·대량화</t>
+          <t>AI 기반 표적 환경·관계 분석</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
+          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -9735,7 +9708,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -9745,7 +9718,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
@@ -9753,12 +9726,12 @@
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>[위협인텔] AI 에이전트를 무기화한 다수 위협 행위자 캠페인(CrowdStrike)(2026-10) (AII-031)</t>
+          <t>[ATLAS 사례 8건·성숙도 실증]</t>
         </is>
       </c>
       <c r="N34" s="9" t="inlineStr">
         <is>
-          <t>캠페인 규모·빈도 증가와 교차 표적 상관 지표를 지속 모니터링(NIST SI-4·CA-7)</t>
+          <t>공개된 조직·거래 정보의 노출 범위와 사칭에 쓰일 수 있는 맥락을 주기적으로 점검(NIST PM-16·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9768,22 +9741,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[IM] 영향·규모화</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-01.2</t>
+          <t>AIA-IM-04</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 표적 스피어피싱·BEC</t>
+          <t>AI 활용 공격의 규모화·대량화</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
+          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -9803,7 +9776,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -9821,12 +9794,12 @@
       </c>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 6건·성숙도 실사용]</t>
+          <t>[ATLAS 사례 7건·성숙도 실사용]</t>
         </is>
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>고위험 역할 대상 메시지의 이상 징후(발신 경로·요청 맥락)와 비정상 송금·승인 요청을 모니터링(NIST SI-4)</t>
+          <t>캠페인 규모·빈도 증가와 교차 표적 상관 지표를 지속 모니터링(NIST SI-4·CA-7)</t>
         </is>
       </c>
     </row>
@@ -9836,22 +9809,22 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-03</t>
+          <t>AIA-IA-01.2</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>공격 인프라·AI 서비스 프록시 확보</t>
+          <t>AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>탈취 계정·서버리스로 AI 서비스 익명 경유 공격 인프라 확보</t>
+          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -9871,7 +9844,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -9881,7 +9854,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="L36" s="8" t="n">
@@ -9889,12 +9862,12 @@
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 6건·성숙도 실증]</t>
+          <t>[ATLAS 사례 6건·성숙도 실사용]</t>
         </is>
       </c>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스·클라우드로의 비정상 egress와 신규·일회성 계정·도메인 사용을 모니터링(NIST SC-7·SI-4)</t>
+          <t>고위험 역할 대상 메시지의 이상 징후(발신 경로·요청 맥락)와 비정상 송금·승인 요청을 모니터링(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9904,22 +9877,22 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-01.2</t>
+          <t>AIA-RD-03</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>AI 보조 코드 감사·퍼징</t>
+          <t>공격 인프라·AI 서비스 프록시 확보</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>AI 보조 코드 감사·퍼징으로 취약점 발견 속도 증폭</t>
+          <t>탈취 계정·서버리스로 AI 서비스 익명 경유 공격 인프라 확보</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -9939,7 +9912,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -9957,12 +9930,12 @@
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>[실증] XBOW 등 자율 펜테스트 에이전트의 취약점 대량 발견(2026-04) (AII-029)</t>
+          <t>[ATLAS 사례 6건·성숙도 실증]</t>
         </is>
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>의존성·자체 코드의 신규 취약점 공개와 악용 정황을 신속 대조(NIST RA-5)</t>
+          <t>AI 서비스·클라우드로의 비정상 egress와 신규·일회성 계정·도메인 사용을 모니터링(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9972,22 +9945,22 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-04</t>
+          <t>AIA-VE-01.2</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
+          <t>AI 보조 코드 감사·퍼징</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
+          <t>AI 보조 코드 감사·퍼징으로 취약점 발견 속도 증폭</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -10007,12 +9980,12 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -10025,12 +9998,12 @@
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>[실증] AI ClickFix — 컴퓨터 사용 에이전트 탈취 실증(2025-05) (AII-025)</t>
+          <t>[실증] XBOW 자율 펜테스트 에이전트의 HackerOne 미국 리더보드 1위(2025-06) (AII-029)</t>
         </is>
       </c>
       <c r="N38" s="9" t="inlineStr">
         <is>
-          <t>에이전트·사용자의 미끼 실행 흐름(클립보드→터미널 등)과 의심 링크 접근을 행위 기반으로 탐지(NIST SI-4)</t>
+          <t>의존성·자체 코드의 신규 취약점 공개와 악용 정황을 신속 대조(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -10197,17 +10170,17 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드 [2]</t>
+          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드 [3]</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1 영상 딥페이크 사칭 [2]</t>
+          <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회 [2]</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>AIA-AO-01 단일 자율 공격 에이전트 실행 [4]</t>
+          <t>AIA-AO-01 단일 자율 공격 에이전트 실행 [7]</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -10217,7 +10190,7 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 [2]</t>
+          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 [4]</t>
         </is>
       </c>
     </row>
@@ -10237,14 +10210,14 @@
           <t>AIA-VE-03.2 AI 생성 와이퍼·파괴 스크립트 [1]</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회 [2]</t>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>AIA-IA-01.1 AI 생성 대량 피싱·미끼 [2]</t>
         </is>
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 [3]</t>
+          <t>AIA-AO-02 다중 에이전트 공격 조율 [3]</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -10274,14 +10247,14 @@
           <t>AIA-VE-01.1 AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>AIA-IA-01.1 AI 생성 대량 피싱·미끼 [1]</t>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>AIA-IA-02.1 영상 딥페이크 사칭 [1]</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 [3]</t>
+          <t>AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 [3]</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -10318,7 +10291,7 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>AIA-AO-02 다중 에이전트 공격 조율 [2]</t>
+          <t>AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 [3]</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
@@ -10345,7 +10318,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>AIA-IA-01.2 AI 기반 표적 스피어피싱·BEC</t>
+          <t>AIA-IA-04 AI 미끼·ClickFix·크래프트 링크로 실행 유도 [1]</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -10362,7 +10335,7 @@
     <row r="8">
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>AIA-IA-04 AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
+          <t>AIA-IA-01.2 AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -10441,7 +10414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI 활용 공격 사고 DB 31건 + MITRE ATLAS 2026.09 + ATT&amp;CK v19.2 + OWASP | 2026-10-25</t>
+          <t>AI 활용 공격 사고 DB 34건 + MITRE ATLAS 2026.09 + ATT&amp;CK v19.2 + OWASP | 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10801,7 @@
         </is>
       </c>
       <c r="AC5" s="8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD5" s="9" t="inlineStr">
         <is>
@@ -11014,7 +10987,7 @@
         </is>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD6" s="9" t="inlineStr">
         <is>
@@ -11199,7 +11172,7 @@
         </is>
       </c>
       <c r="AC7" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD7" s="9" t="inlineStr">
         <is>
@@ -11242,7 +11215,11 @@
           <t>AII-027</t>
         </is>
       </c>
-      <c r="AO7" s="9" t="inlineStr"/>
+      <c r="AO7" s="9" t="inlineStr">
+        <is>
+          <t>데이터 유출 1 · 내부 접근 확보 1</t>
+        </is>
+      </c>
       <c r="AP7" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
@@ -11388,7 +11365,7 @@
         </is>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD8" s="9" t="inlineStr">
         <is>
@@ -11431,7 +11408,11 @@
           <t>AII-027</t>
         </is>
       </c>
-      <c r="AO8" s="9" t="inlineStr"/>
+      <c r="AO8" s="9" t="inlineStr">
+        <is>
+          <t>데이터 유출 1 · 내부 접근 확보 1</t>
+        </is>
+      </c>
       <c r="AP8" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
@@ -11575,7 +11556,7 @@
         </is>
       </c>
       <c r="AC9" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD9" s="9" t="inlineStr">
         <is>
@@ -11930,7 +11911,7 @@
         </is>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD11" s="9" t="inlineStr">
         <is>
@@ -12119,7 +12100,7 @@
         </is>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AD12" s="9" t="inlineStr">
         <is>
@@ -12266,11 +12247,7 @@
       </c>
       <c r="Q13" s="9" t="inlineStr"/>
       <c r="R13" s="9" t="inlineStr"/>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>ASI-T01 에이전트 인가·제어 탈취</t>
-        </is>
-      </c>
+      <c r="S13" s="9" t="inlineStr"/>
       <c r="T13" s="9" t="inlineStr">
         <is>
           <t>AI-01-05 자율·다중 에이전트 기반 공격</t>
@@ -12342,7 +12319,7 @@
       </c>
       <c r="AO13" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 1 · 내부 접근 확보 1</t>
+          <t>데이터 유출 2 · 내부 접근 확보 2</t>
         </is>
       </c>
       <c r="AP13" s="9" t="inlineStr">
@@ -12463,11 +12440,7 @@
         </is>
       </c>
       <c r="S14" s="9" t="inlineStr"/>
-      <c r="T14" s="9" t="inlineStr">
-        <is>
-          <t>AI-01-02 AI 모델 접근 확보 및 환경 탐색</t>
-        </is>
-      </c>
+      <c r="T14" s="9" t="inlineStr"/>
       <c r="U14" s="9" t="inlineStr"/>
       <c r="V14" s="9" t="inlineStr"/>
       <c r="W14" s="9" t="inlineStr"/>
@@ -12489,7 +12462,7 @@
         </is>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD14" s="9" t="inlineStr">
         <is>
@@ -12651,11 +12624,7 @@
         </is>
       </c>
       <c r="S15" s="9" t="inlineStr"/>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>AI-01-02 AI 모델 접근 확보 및 환경 탐색</t>
-        </is>
-      </c>
+      <c r="T15" s="9" t="inlineStr"/>
       <c r="U15" s="9" t="inlineStr"/>
       <c r="V15" s="9" t="inlineStr"/>
       <c r="W15" s="9" t="inlineStr">
@@ -12681,7 +12650,7 @@
         </is>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD15" s="9" t="inlineStr">
         <is>
@@ -12843,11 +12812,7 @@
         </is>
       </c>
       <c r="S16" s="9" t="inlineStr"/>
-      <c r="T16" s="9" t="inlineStr">
-        <is>
-          <t>AI-01-02 AI 모델 접근 확보 및 환경 탐색</t>
-        </is>
-      </c>
+      <c r="T16" s="9" t="inlineStr"/>
       <c r="U16" s="9" t="inlineStr"/>
       <c r="V16" s="9" t="inlineStr"/>
       <c r="W16" s="9" t="inlineStr"/>
@@ -12869,7 +12834,7 @@
         </is>
       </c>
       <c r="AC16" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD16" s="9" t="inlineStr">
         <is>
@@ -13057,11 +13022,11 @@
         </is>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AD17" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
+          <t>실제 사고 3건(최근 3) · AI 활용 확인 2·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE17" s="9" t="inlineStr">
@@ -13070,16 +13035,16 @@
         </is>
       </c>
       <c r="AF17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH17" s="9" t="n">
         <v>2</v>
       </c>
       <c r="AI17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" s="9" t="n">
         <v>0</v>
@@ -13097,12 +13062,12 @@
       </c>
       <c r="AN17" s="9" t="inlineStr">
         <is>
-          <t>AII-007, AII-024</t>
+          <t>AII-007, AII-023, AII-024</t>
         </is>
       </c>
       <c r="AO17" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 1 · 내부 접근 확보 1 · 금전 피해 1</t>
+          <t>데이터 유출 1 · 내부 접근 확보 1 · 자격증명·비밀 탈취 1 · 금전 피해 1</t>
         </is>
       </c>
       <c r="AP17" s="9" t="inlineStr">
@@ -13252,11 +13217,11 @@
         </is>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD18" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
+          <t>실제 사고 1건(최근 1) · AI 활용 확인 0·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE18" s="9" t="inlineStr">
@@ -13271,10 +13236,10 @@
         <v>1</v>
       </c>
       <c r="AH18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AI18" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ18" s="9" t="n">
         <v>0</v>
@@ -13434,25 +13399,25 @@
       <c r="Y19" s="9" t="inlineStr"/>
       <c r="Z19" s="8" t="inlineStr">
         <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
           <t>중</t>
         </is>
       </c>
-      <c r="AA19" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="AB19" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="AB19" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AD19" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 0·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 3 · 역량 성숙도 실사용</t>
+          <t>실제 사고 2건(최근 2) · AI 활용 확인 0·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 3 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE19" s="9" t="inlineStr">
@@ -13461,10 +13426,10 @@
         </is>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH19" s="9" t="n">
         <v>0</v>
@@ -13488,12 +13453,12 @@
       </c>
       <c r="AN19" s="9" t="inlineStr">
         <is>
-          <t>AII-021</t>
+          <t>AII-021, AII-023</t>
         </is>
       </c>
       <c r="AO19" s="9" t="inlineStr">
         <is>
-          <t>계정 장악 1</t>
+          <t>계정 장악 1 · 자격증명·비밀 탈취 1</t>
         </is>
       </c>
       <c r="AP19" s="9" t="inlineStr">
@@ -13645,7 +13610,7 @@
         </is>
       </c>
       <c r="AC20" s="8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD20" s="9" t="inlineStr">
         <is>
@@ -13808,25 +13773,25 @@
       <c r="Y21" s="9" t="inlineStr"/>
       <c r="Z21" s="8" t="inlineStr">
         <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="AA21" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB21" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="AB21" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AD21" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 0) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
+          <t>실제 사고 1건(최근 0) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE21" s="9" t="inlineStr">
@@ -13835,13 +13800,13 @@
         </is>
       </c>
       <c r="AF21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AH21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI21" s="9" t="n">
         <v>0</v>
@@ -13862,12 +13827,12 @@
       </c>
       <c r="AN21" s="9" t="inlineStr">
         <is>
-          <t>AII-002, AII-012</t>
+          <t>AII-002</t>
         </is>
       </c>
       <c r="AO21" s="9" t="inlineStr">
         <is>
-          <t>금전 피해 2 · 자격증명·비밀 탈취 1</t>
+          <t>금전 피해 1</t>
         </is>
       </c>
       <c r="AP21" s="9" t="inlineStr">
@@ -14015,7 +13980,7 @@
         </is>
       </c>
       <c r="AC22" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD22" s="9" t="inlineStr">
         <is>
@@ -14200,7 +14165,7 @@
         </is>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD23" s="9" t="inlineStr">
         <is>
@@ -14365,7 +14330,11 @@
 T1204.001 User Execution: Malicious Link</t>
         </is>
       </c>
-      <c r="S24" s="9" t="inlineStr"/>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>ASI01 에이전트 목표 탈취</t>
+        </is>
+      </c>
       <c r="T24" s="9" t="inlineStr">
         <is>
           <t>AI-01-08 AI 생성 피싱 및 신뢰 주체 사칭</t>
@@ -14392,11 +14361,11 @@
         </is>
       </c>
       <c r="AC24" s="8" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AD24" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 1 · ATLAS 사례 3 · 역량 성숙도 실증</t>
+          <t>실제 사고 1건(최근 0) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 1 · ATLAS 사례 3 · 역량 성숙도 실증</t>
         </is>
       </c>
       <c r="AE24" s="9" t="inlineStr">
@@ -14405,13 +14374,13 @@
         </is>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AH24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI24" s="9" t="n">
         <v>0</v>
@@ -14425,18 +14394,22 @@
       <c r="AL24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM24" s="28" t="inlineStr">
-        <is>
-          <t>실증·공개 PoC</t>
+      <c r="AM24" s="29" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
         </is>
       </c>
       <c r="AN24" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">
+          <t>AII-012
 실증·연구: AII-025</t>
         </is>
       </c>
-      <c r="AO24" s="9" t="inlineStr"/>
+      <c r="AO24" s="9" t="inlineStr">
+        <is>
+          <t>자격증명·비밀 탈취 1 · 금전 피해 1</t>
+        </is>
+      </c>
       <c r="AP24" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
@@ -14552,11 +14525,7 @@
           <t>T1059 Command and Scripting Interpreter</t>
         </is>
       </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>ASI-T01 에이전트 인가·제어 탈취</t>
-        </is>
-      </c>
+      <c r="S25" s="9" t="inlineStr"/>
       <c r="T25" s="9" t="inlineStr">
         <is>
           <t>AI-01-05 자율·다중 에이전트 기반 공격</t>
@@ -14587,7 +14556,7 @@
       </c>
       <c r="AD25" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 4건(최근 4) · AI 활용 확인 5·추정 0 · 위협인텔 1 · 실증·연구 0 · ATLAS 사례 9 · 역량 성숙도 실사용</t>
+          <t>실제 사고 7건(최근 7) · AI 활용 확인 7·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 9 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE25" s="9" t="inlineStr">
@@ -14596,19 +14565,19 @@
         </is>
       </c>
       <c r="AF25" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG25" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH25" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="9" t="n">
         <v>0</v>
@@ -14623,13 +14592,12 @@
       </c>
       <c r="AN25" s="9" t="inlineStr">
         <is>
-          <t>AII-008, AII-010, AII-023, AII-027
-위협인텔: AII-031</t>
+          <t>AII-008, AII-010, AII-027, AII-031, AII-032, AII-033, AII-034</t>
         </is>
       </c>
       <c r="AO25" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 2 · 데이터 유출 1 · 자격증명·비밀 탈취 1</t>
+          <t>내부 접근 확보 6 · 데이터 유출 4 · 자격증명·비밀 탈취 1</t>
         </is>
       </c>
       <c r="AP25" s="9" t="inlineStr">
@@ -14745,11 +14713,7 @@
       </c>
       <c r="Q26" s="9" t="inlineStr"/>
       <c r="R26" s="9" t="inlineStr"/>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>ASI-T01 에이전트 인가·제어 탈취</t>
-        </is>
-      </c>
+      <c r="S26" s="9" t="inlineStr"/>
       <c r="T26" s="9" t="inlineStr">
         <is>
           <t>AI-01-05 자율·다중 에이전트 기반 공격</t>
@@ -14776,11 +14740,11 @@
         </is>
       </c>
       <c r="AC26" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AD26" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 2 · 역량 성숙도 실사용</t>
+          <t>실제 사고 3건(최근 3) · AI 활용 확인 3·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 2 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE26" s="9" t="inlineStr">
@@ -14789,13 +14753,13 @@
         </is>
       </c>
       <c r="AF26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI26" s="9" t="n">
         <v>0</v>
@@ -14816,12 +14780,12 @@
       </c>
       <c r="AN26" s="9" t="inlineStr">
         <is>
-          <t>AII-008, AII-009</t>
+          <t>AII-008, AII-009, AII-032</t>
         </is>
       </c>
       <c r="AO26" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 2 · 내부 접근 확보 1</t>
+          <t>데이터 유출 2 · 내부 접근 확보 2</t>
         </is>
       </c>
       <c r="AP26" s="9" t="inlineStr">
@@ -14976,7 +14940,7 @@
         </is>
       </c>
       <c r="AC27" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD27" s="9" t="inlineStr">
         <is>
@@ -15175,7 +15139,7 @@
         </is>
       </c>
       <c r="AC28" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD28" s="9" t="inlineStr">
         <is>
@@ -15370,7 +15334,7 @@
         </is>
       </c>
       <c r="AC29" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD29" s="9" t="inlineStr">
         <is>
@@ -15571,11 +15535,11 @@
         </is>
       </c>
       <c r="AC30" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD30" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 3건(최근 3) · AI 활용 확인 3·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 10 · 역량 성숙도 실증</t>
+          <t>실제 사고 3건(최근 3) · AI 활용 확인 1·추정 2 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 10 · 역량 성숙도 실증</t>
         </is>
       </c>
       <c r="AE30" s="9" t="inlineStr">
@@ -15590,10 +15554,10 @@
         <v>3</v>
       </c>
       <c r="AH30" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ30" s="9" t="n">
         <v>0</v>
@@ -15768,7 +15732,7 @@
         </is>
       </c>
       <c r="AC31" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD31" s="9" t="inlineStr">
         <is>
@@ -15960,7 +15924,7 @@
         </is>
       </c>
       <c r="AC32" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD32" s="9" t="inlineStr">
         <is>
@@ -16153,7 +16117,7 @@
         </is>
       </c>
       <c r="AC33" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD33" s="9" t="inlineStr">
         <is>
@@ -16311,7 +16275,8 @@
       </c>
       <c r="S34" s="9" t="inlineStr">
         <is>
-          <t>LLM01 프롬프트 인젝션</t>
+          <t>LLM01 프롬프트 인젝션
+ASI01 에이전트 목표 탈취</t>
         </is>
       </c>
       <c r="T34" s="9" t="inlineStr">
@@ -16344,7 +16309,7 @@
         </is>
       </c>
       <c r="AC34" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD34" s="9" t="inlineStr">
         <is>
@@ -16724,11 +16689,11 @@
         </is>
       </c>
       <c r="AC36" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AD36" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 14 · 역량 성숙도 실사용</t>
+          <t>실제 사고 4건(최근 4) · AI 활용 확인 3·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 14 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE36" s="9" t="inlineStr">
@@ -16737,16 +16702,16 @@
         </is>
       </c>
       <c r="AF36" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH36" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ36" s="9" t="n">
         <v>0</v>
@@ -16764,12 +16729,12 @@
       </c>
       <c r="AN36" s="9" t="inlineStr">
         <is>
-          <t>AII-009, AII-022</t>
+          <t>AII-009, AII-022, AII-031, AII-034</t>
         </is>
       </c>
       <c r="AO36" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 2 · 서비스 중단 1</t>
+          <t>데이터 유출 4 · 서비스 중단 1 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
         </is>
       </c>
       <c r="AP36" s="9" t="inlineStr">
@@ -16926,7 +16891,7 @@
       </c>
       <c r="AD37" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 1 · 역량 성숙도 실사용</t>
+          <t>실제 사고 2건(최근 2) · AI 활용 확인 0·추정 2 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 1 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE37" s="9" t="inlineStr">
@@ -16941,10 +16906,10 @@
         <v>2</v>
       </c>
       <c r="AH37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AI37" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ37" s="9" t="n">
         <v>0</v>
@@ -17121,11 +17086,11 @@
         </is>
       </c>
       <c r="AC38" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD38" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 10 · 역량 성숙도 실사용</t>
+          <t>실제 사고 1건(최근 1) · AI 활용 확인 0·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 10 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE38" s="9" t="inlineStr">
@@ -17140,10 +17105,10 @@
         <v>1</v>
       </c>
       <c r="AH38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AI38" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ38" s="9" t="n">
         <v>0</v>
@@ -17303,11 +17268,11 @@
         </is>
       </c>
       <c r="AC39" s="8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AD39" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 1·추정 0 · 위협인텔 1 · 실증·연구 0 · ATLAS 사례 7 · 역량 성숙도 실사용</t>
+          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 7 · 역량 성숙도 실사용</t>
         </is>
       </c>
       <c r="AE39" s="9" t="inlineStr">
@@ -17322,13 +17287,13 @@
         <v>0</v>
       </c>
       <c r="AH39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK39" s="9" t="n">
         <v>0</v>
@@ -17341,12 +17306,7 @@
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-위협인텔: AII-031</t>
-        </is>
-      </c>
+      <c r="AN39" s="9" t="inlineStr"/>
       <c r="AO39" s="9" t="inlineStr"/>
       <c r="AP39" s="9" t="inlineStr">
         <is>
@@ -17594,7 +17554,7 @@
         </is>
       </c>
       <c r="O3" s="8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P3" s="27" t="inlineStr">
         <is>
@@ -17692,7 +17652,7 @@
         </is>
       </c>
       <c r="O4" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P4" s="28" t="inlineStr">
         <is>
@@ -17790,7 +17750,7 @@
         </is>
       </c>
       <c r="O5" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" s="29" t="inlineStr">
         <is>
@@ -17888,7 +17848,7 @@
         </is>
       </c>
       <c r="O6" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P6" s="29" t="inlineStr">
         <is>
@@ -17986,7 +17946,7 @@
         </is>
       </c>
       <c r="O7" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P7" s="27" t="inlineStr">
         <is>
@@ -18178,7 +18138,7 @@
         </is>
       </c>
       <c r="O9" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P9" s="27" t="inlineStr">
         <is>
@@ -18274,7 +18234,7 @@
         </is>
       </c>
       <c r="O10" s="8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P10" s="28" t="inlineStr">
         <is>
@@ -18466,7 +18426,7 @@
         </is>
       </c>
       <c r="O12" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P12" s="27" t="inlineStr">
         <is>
@@ -18562,7 +18522,7 @@
         </is>
       </c>
       <c r="O13" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P13" s="28" t="inlineStr">
         <is>
@@ -18658,7 +18618,7 @@
         </is>
       </c>
       <c r="O14" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P14" s="27" t="inlineStr">
         <is>
@@ -18754,7 +18714,7 @@
         </is>
       </c>
       <c r="O15" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P15" s="29" t="inlineStr">
         <is>
@@ -18762,7 +18722,7 @@
         </is>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="8" t="n">
         <v>6</v>
@@ -18850,7 +18810,7 @@
         </is>
       </c>
       <c r="O16" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P16" s="29" t="inlineStr">
         <is>
@@ -18932,21 +18892,21 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="N17" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="O17" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="P17" s="29" t="inlineStr">
         <is>
@@ -18954,7 +18914,7 @@
         </is>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="8" t="n">
         <v>3</v>
@@ -19043,7 +19003,7 @@
         </is>
       </c>
       <c r="O18" s="8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P18" s="27" t="inlineStr">
         <is>
@@ -19125,21 +19085,21 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="O19" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P19" s="29" t="inlineStr">
         <is>
@@ -19147,7 +19107,7 @@
         </is>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" s="8" t="n">
         <v>6</v>
@@ -19235,7 +19195,7 @@
         </is>
       </c>
       <c r="O20" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" s="29" t="inlineStr">
         <is>
@@ -19331,7 +19291,7 @@
         </is>
       </c>
       <c r="O21" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P21" s="29" t="inlineStr">
         <is>
@@ -19427,15 +19387,15 @@
         </is>
       </c>
       <c r="O22" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="P22" s="28" t="inlineStr">
-        <is>
-          <t>실증·공개 PoC</t>
+        <v>25</v>
+      </c>
+      <c r="P22" s="29" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
         </is>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>3</v>
@@ -19531,7 +19491,7 @@
         </is>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R23" s="8" t="n">
         <v>9</v>
@@ -19621,7 +19581,7 @@
         </is>
       </c>
       <c r="O24" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P24" s="29" t="inlineStr">
         <is>
@@ -19629,7 +19589,7 @@
         </is>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" s="8" t="n">
         <v>2</v>
@@ -19717,7 +19677,7 @@
         </is>
       </c>
       <c r="O25" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P25" s="29" t="inlineStr">
         <is>
@@ -19813,7 +19773,7 @@
         </is>
       </c>
       <c r="O26" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P26" s="29" t="inlineStr">
         <is>
@@ -19909,7 +19869,7 @@
         </is>
       </c>
       <c r="O27" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P27" s="29" t="inlineStr">
         <is>
@@ -20005,7 +19965,7 @@
         </is>
       </c>
       <c r="O28" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P28" s="29" t="inlineStr">
         <is>
@@ -20101,7 +20061,7 @@
         </is>
       </c>
       <c r="O29" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P29" s="29" t="inlineStr">
         <is>
@@ -20197,7 +20157,7 @@
         </is>
       </c>
       <c r="O30" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P30" s="29" t="inlineStr">
         <is>
@@ -20293,7 +20253,7 @@
         </is>
       </c>
       <c r="O31" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P31" s="28" t="inlineStr">
         <is>
@@ -20389,7 +20349,7 @@
         </is>
       </c>
       <c r="O32" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P32" s="29" t="inlineStr">
         <is>
@@ -20581,7 +20541,7 @@
         </is>
       </c>
       <c r="O34" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P34" s="29" t="inlineStr">
         <is>
@@ -20589,7 +20549,7 @@
         </is>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R34" s="8" t="n">
         <v>14</v>
@@ -20773,7 +20733,7 @@
         </is>
       </c>
       <c r="O36" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P36" s="29" t="inlineStr">
         <is>
@@ -20869,7 +20829,7 @@
         </is>
       </c>
       <c r="O37" s="8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P37" s="27" t="inlineStr">
         <is>
@@ -21175,14 +21135,14 @@
         <v>0</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음, 사고 2)
+          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음, 사고 3)
 AIA-VE-03.2 AI 생성 와이퍼·파괴 스크립트(높음, 사고 1)
 AIA-VE-01.1 AI 자율 취약점 발굴(버그 헌팅)(높음, 사고 0)</t>
         </is>
@@ -21211,40 +21171,40 @@
         <v>6</v>
       </c>
       <c r="F5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
           <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음, 사고 2)
-AIA-IA-02.1 영상 딥페이크 사칭(매우 높음, 사고 2)
-AIA-IA-02.2 음성 딥페이크 사칭(보통, 사고 1)</t>
+AIA-IA-01.1 AI 생성 대량 피싱·미끼(높음, 사고 2)
+AIA-IA-02.1 영상 딥페이크 사칭(높음, 사고 1)</t>
         </is>
       </c>
     </row>
@@ -21295,14 +21255,14 @@
         <v>0</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01 단일 자율 공격 에이전트 실행(매우 높음, 사고 4)
+          <t>AIA-AO-01 단일 자율 공격 에이전트 실행(매우 높음, 사고 7)
 AIA-AO-05 AI 가속 자격증명 탈취·내부 확산(매우 높음, 사고 3)
 AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용(매우 높음, 사고 3)</t>
         </is>
@@ -21415,14 +21375,14 @@
         <v>0</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음, 사고 2)
+          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음, 사고 4)
 AIA-IM-03.1 AI 인프라 악용 크립토재킹(높음, 사고 2)
 AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기(높음, 사고 1)</t>
         </is>
@@ -21524,7 +21484,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>6</v>
@@ -21543,9 +21503,9 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음)
-AIA-IA-02.1 영상 딥페이크 사칭(매우 높음)
-AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음)</t>
+          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음)
+AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음)
+AIA-IA-01.1 AI 생성 대량 피싱·미끼(높음)</t>
         </is>
       </c>
     </row>
@@ -21613,9 +21573,9 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-05 AI 가속 자격증명 탈취·내부 확산(매우 높음)
-AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용(매우 높음)
-AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용(매우 높음)</t>
+          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음)
+AIA-AO-05 AI 가속 자격증명 탈취·내부 확산(매우 높음)
+AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용(매우 높음)</t>
         </is>
       </c>
     </row>
@@ -21707,9 +21667,9 @@
         <is>
           <t>AIA-AO-01 단일 자율 공격 에이전트 실행(매우 높음)
 AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용(매우 높음)
+AIA-AO-02 다중 에이전트 공격 조율(매우 높음)
 AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용(매우 높음)
-AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용(매우 높음)
-AIA-RD-04 공세 AI 에이전트·공격 하네스 구축(매우 높음)</t>
+AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용(매우 높음)</t>
         </is>
       </c>
     </row>
@@ -21723,18 +21683,18 @@
         <v>20</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-05 AI 가속 자격증명 탈취·내부 확산(매우 높음)
+          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음)
+AIA-AO-05 AI 가속 자격증명 탈취·내부 확산(매우 높음)
+AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음)
 AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음)
-AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음)
-AIA-IA-02.1 영상 딥페이크 사칭(매우 높음)
-AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음)</t>
+AIA-IA-01.1 AI 생성 대량 피싱·미끼(높음)</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -22518,12 +22478,12 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>AII-031</t>
+          <t>AII-034</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>AI 에이전트를 무기화한 다수 위협 행위자 캠페인(CrowdStrike)</t>
+          <t>거의 전권을 위임한 AI 에이전트로 CRM 업체 고객 데이터 반출(CrowdStrike 행위자 4)</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -22533,12 +22493,12 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>위협인텔</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>위협인텔</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -22558,27 +22518,27 @@
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>복수 위협 행위자(CrowdStrike 추적)</t>
+          <t>미명명 행위자(CrowdStrike 추적, 2026-05~08 관측)</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄 · 국가배후</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>영향 미상</t>
+          <t>데이터 유출 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01, AIA-IM-04</t>
+          <t>AIA-AO-01, AIA-IM-02</t>
         </is>
       </c>
       <c r="N2" s="9" t="inlineStr"/>
@@ -22591,17 +22551,17 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>AII-024</t>
+          <t>AII-033</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>BREEZE COMET — 생성형 AI를 악성코드 개발에 활용한 브라질 금융 공격</t>
+          <t>공개 에이전트 스킬 묶음으로 인도네시아 정부 도메인 등 침해(CrowdStrike 행위자 3)</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -22626,64 +22586,60 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>브라질</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>금융·서비스</t>
+          <t>정부·군 · 다부문</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>BREEZE COMET(구 UNC5669)</t>
+          <t>미명명 행위자(CrowdStrike 추적, 2026-05~08 관측)</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>금전 피해</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>CL/INC-0677</t>
-        </is>
-      </c>
+          <t>AIA-AO-01</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr"/>
       <c r="O3" s="9" t="inlineStr">
         <is>
-          <t>Google GTIG(2026) Financially Motivated Threat Actor BREEZE COMET Targets Brazil | https://cloud.google.com/blog/topics/threat-intelligence/financially-motivated-threat-actor-breeze-comet-targets-brazil</t>
+          <t>CrowdStrike(2026) CrowdStrike Uncovers New Agentic AI Campaigns | https://www.crowdstrike.com/en-us/blog/crowdstrike-uncovers-new-agentic-ai-campaigns/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>AII-009</t>
+          <t>AII-032</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>다중 에이전트 프레임워크의 대만 정부 시스템 침해</t>
+          <t>AI 에이전트 하네스로 여러 나라 정부·민간 20곳 이상 표적(CrowdStrike 행위자 2)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -22703,64 +22659,60 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>대만</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>정부·군</t>
+          <t>정부·군 · 다부문</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>미상 중국어권 행위자</t>
+          <t>미명명 행위자(CrowdStrike 추적, 2026-05~08 관측)</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-02, AIA-IM-02</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>AML.CS0071</t>
-        </is>
-      </c>
+          <t>AIA-AO-01, AIA-AO-02</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr"/>
       <c r="O4" s="9" t="inlineStr">
         <is>
-          <t>Dream Research Labs(2026) Inside a Multi-Agent AI Framework | https://www.dreamgroup.com/blog/inside-a-multi-agent-ai-framework-used-to-compromise-government-entities-in-asia</t>
+          <t>CrowdStrike(2026) CrowdStrike Uncovers New Agentic AI Campaigns | https://www.crowdstrike.com/en-us/blog/crowdstrike-uncovers-new-agentic-ai-campaigns/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>AII-027</t>
+          <t>AII-031</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>DeepSeek 기반 Hermes 에이전트의 Langflow·n8n 자율 공격 시도</t>
+          <t>AI 에이전트 침투로 아르헨티나 의료기관 15곳 이상 침해(CrowdStrike 행위자 1)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -22780,17 +22732,17 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>의료·바이오</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>중국어권 행위자(knaithe/KnYuan)</t>
+          <t>미명명 행위자(CrowdStrike 추적, 2026-05~08 관측)</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -22800,39 +22752,35 @@
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>자격증명·비밀 탈취 · 데이터 유출</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-04, AIA-RT-02, AIA-RT-03, AIA-AO-01</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>AML.CS0070</t>
-        </is>
-      </c>
+          <t>AIA-AO-01, AIA-IM-02</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr"/>
       <c r="O5" s="9" t="inlineStr">
         <is>
-          <t>Unit 42(2026) Autonomous AI Cyberattack Campaign | https://unit42.paloaltonetworks.com/autonomous-ai-cyber-attack-campaign/</t>
+          <t>CrowdStrike(2026) CrowdStrike Uncovers New Agentic AI Campaigns | https://www.crowdstrike.com/en-us/blog/crowdstrike-uncovers-new-agentic-ai-campaigns/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>AII-023</t>
+          <t>AII-024</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>CaptiveCrunch — Midnight Blizzard 하위 그룹의 AiTM 캠페인</t>
+          <t>BREEZE COMET — 생성형 AI를 악성코드 개발에 활용한 브라질 금융 공격</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -22857,64 +22805,64 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>브라질</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>숙박·여행</t>
+          <t>금융·서비스</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Storm-2945(Midnight Blizzard 하위)</t>
+          <t>BREEZE COMET(구 UNC5669)</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취</t>
+          <t>금전 피해</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01</t>
+          <t>AIA-VE-03.1</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0666</t>
+          <t>CL/INC-0677</t>
         </is>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>Microsoft(2026) CaptiveCrunch — Midnight Blizzard targets travelers worldwide | https://www.microsoft.com/en-us/security/blog/2026/07/31/captivecrunch-midnight-blizzard-targets-travelers-worldwide-for-malware-delivery-and-credential-theft/</t>
+          <t>Google GTIG(2026) Financially Motivated Threat Actor BREEZE COMET Targets Brazil | https://cloud.google.com/blog/topics/threat-intelligence/financially-motivated-threat-actor-breeze-comet-targets-brazil</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>AII-010</t>
+          <t>AII-009</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>자율 평가 에이전트의 평가 경계 이탈과 Hugging Face 인프라 침해</t>
+          <t>다중 에이전트 프레임워크의 아시아 정부 기관 침해(대만으로 보도)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -22934,64 +22882,65 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>대만</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>정부·군</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>자율 평가 에이전트(OpenAI 평가)</t>
+          <t>미상 중국어권 행위자</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
+          <t>데이터 유출</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01</t>
+          <t>AIA-AO-02, AIA-IM-02</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>AML.CS0068</t>
+          <t>AML.CS0071</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
         <is>
-          <t>Hugging Face(2026) Agent intrusion technical timeline | https://huggingface.co/blog/agent-intrusion-technical-timeline</t>
+          <t>Dream Research Labs(2026) Inside a Multi-Agent AI Framework | https://www.dreamgroup.com/blog/inside-a-multi-agent-ai-framework-used-to-compromise-government-entities-in-asia
+{'Focus Taiwan(2026) AI agents used in cyberattacks on Taiwan government websites': 'MODA | https://focustaiwan.tw/society/202608130011'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>AII-022</t>
+          <t>AII-027</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>AI 보조 클라우드 침입(Sygnia 익명 사례)</t>
+          <t>DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>사례연구(익명)</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -23011,17 +22960,17 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>IT·소프트웨어 · 다부문</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>중국어권 행위자(knaithe/KnYuan)</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -23031,54 +22980,54 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 · 서비스 중단</t>
+          <t>데이터 유출 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-05, AIA-IM-02</t>
+          <t>AIA-RD-04, AIA-RT-02, AIA-RT-03, AIA-AO-01</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0637</t>
+          <t>AML.CS0070</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>Sygnia(2026) Inside an AI-assisted cloud attack | https://www.sygnia.co/blog/inside-an-ai-assisted-cloud-attack/</t>
+          <t>Unit 42(2026) Autonomous AI Cyberattack Campaign | https://unit42.paloaltonetworks.com/autonomous-ai-cyber-attack-campaign/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>AII-030</t>
+          <t>AII-023</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>AI로 개발한 것으로 판단되는 0-day 익스플로잇 실사용(GTIG 보고)</t>
+          <t>CaptiveCrunch — Midnight Blizzard 하위 그룹의 AI 보조 악성코드 개발</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>위협인텔</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>위협인텔</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -23093,60 +23042,64 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>숙박·여행</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>미상 위협 행위자</t>
+          <t>Storm-2945(Midnight Blizzard 하위, 러시아 SVR 연계)</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>영향 미상</t>
+          <t>자격증명·비밀 탈취</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-02</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr"/>
+          <t>AIA-VE-03.1, AIA-IA-01.1</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>CL/INC-0666</t>
+        </is>
+      </c>
       <c r="O9" s="9" t="inlineStr">
         <is>
-          <t>securityonline(2026) Google Confirms First AI-Generated Zero-Day Exploit Found in the Wild | https://securityonline.info/google-threat-intel-ai-generated-zero-day-exploit-big-sleep/</t>
+          <t>Microsoft(2026) CaptiveCrunch — Midnight Blizzard targets travelers worldwide | https://www.microsoft.com/en-us/security/blog/2026/07/31/captivecrunch-midnight-blizzard-targets-travelers-worldwide-for-malware-delivery-and-credential-theft/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>AII-029</t>
+          <t>AII-010</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>XBOW 등 자율 펜테스트 에이전트의 취약점 대량 발견</t>
+          <t>자율 평가 에이전트의 평가 경계 이탈과 Hugging Face 인프라 침해</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -23171,7 +23124,7 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>XBOW 등 자율 펜테스트 에이전트</t>
+          <t>자율 평가 에이전트(OpenAI 내부 사이버 역량 평가)</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -23181,40 +23134,44 @@
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1, AIA-VE-01.2</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="inlineStr"/>
+          <t>AIA-AO-01</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>AML.CS0068</t>
+        </is>
+      </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>AppSecSanta(2026) AI Pentesting Agents 2026 | https://appsecsanta.com/research/ai-pentesting-agents-2026</t>
+          <t>Hugging Face(2026) Anatomy of a Frontier Lab Agent Intrusion — technical timeline | https://huggingface.co/blog/agent-intrusion-technical-timeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>AII-020</t>
+          <t>AII-022</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>prt-scan — 취약 GitHub 워크플로 대상 기회주의 공급망 캠페인</t>
+          <t>AI 보조 클라우드 침입(Sygnia 익명 사례)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>사례연구(익명)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -23239,12 +23196,12 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>미상(ezmtebo 등 6개 계정)</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -23254,59 +23211,59 @@
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취</t>
+          <t>데이터 유출 · 서비스 중단</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-04</t>
+          <t>AIA-AO-05, AIA-IM-02</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0612</t>
+          <t>CL/INC-0637</t>
         </is>
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>Wiz(2026) Six accounts, one actor — the prt-scan supply chain campaign | https://www.wiz.io/blog/six-accounts-one-actor-inside-the-prt-scan-supply-chain-campaign</t>
+          <t>Sygnia(2026) Inside an AI-assisted cloud attack | https://www.sygnia.co/blog/inside-an-ai-assisted-cloud-attack/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>AII-021</t>
+          <t>AII-030</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>O365 디바이스 코드 피싱 캠페인(EvilTokens PhaaS)</t>
+          <t>AI로 개발한 0-day 익스플로잇을 준비한 범죄 조직의 대량 악용 계획(GTIG 사전 차단)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>위협인텔</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>위협인텔</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -23321,7 +23278,7 @@
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>EvilTokens(PhaaS)</t>
+          <t>미상 사이버범죄 조직(GTIG 추적)</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -23331,44 +23288,40 @@
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>계정 장악</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-01.1</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>CL/INC-0614</t>
-        </is>
-      </c>
+          <t>AIA-VE-02</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="9" t="inlineStr">
         <is>
-          <t>Huntress(2026) Railway PaaS M365 token replay campaign | https://www.huntress.com/blog/railway-paas-m365-token-replay-campaign</t>
+          <t>Google GTIG(2026) GTIG AI Threat Tracker — Adversaries Leverage AI for Vulnerability Exploitation, Augmented Operations, and Initial Access | https://cloud.google.com/blog/topics/threat-intelligence/ai-vulnerability-exploitation-initial-access</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>AII-019</t>
+          <t>AII-020</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)</t>
+          <t>prt-scan — 취약 GitHub 워크플로 대상 기회주의 공급망 캠페인</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -23378,7 +23331,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -23398,7 +23351,7 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>미상(ezmtebo 등 6개 계정)</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -23408,34 +23361,34 @@
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 데이터 유출</t>
+          <t>자격증명·비밀 탈취</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-03.2, AIA-AO-04</t>
+          <t>AIA-AO-04</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0606</t>
+          <t>CL/INC-0612</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
-          <t>Ctrl-Alt-Intel(2026) BuddyBoss supply chain attack (Part 2) | https://ctrlaltintel.com/research/BuddyBoss-2/</t>
+          <t>Wiz(2026) Six accounts, one actor — the prt-scan supply chain campaign | https://www.wiz.io/blog/six-accounts-one-actor-inside-the-prt-scan-supply-chain-campaign</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>AII-018</t>
+          <t>AII-021</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)</t>
+          <t>O365 디바이스 코드 피싱 캠페인(EvilTokens PhaaS)</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -23445,7 +23398,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -23455,12 +23408,12 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>미확인</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -23475,7 +23428,7 @@
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>UNC6426</t>
+          <t>EvilTokens(PhaaS)</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -23485,34 +23438,34 @@
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취 · 데이터 유출</t>
+          <t>계정 장악</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-03.1, AIA-AO-05</t>
+          <t>AIA-IA-01.1</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0603</t>
+          <t>CL/INC-0614</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>The Hacker News(2026) UNC6426 Exploits Nx npm Supply Chain | https://thehackernews.com/2026/03/unc6426-exploits-nx-npm-supply-chain.html</t>
+          <t>Huntress(2026) Railway PaaS M365 token replay campaign | https://www.huntress.com/blog/railway-paas-m365-token-replay-campaign</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>AII-017</t>
+          <t>AII-019</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>hackerbot-claw — 자율 에이전트의 GitHub Actions 워크플로 대량 악용</t>
+          <t>BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -23532,7 +23485,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -23552,7 +23505,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>자칭 자율 보안 연구 에이전트(hackerbot-claw)</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
@@ -23562,49 +23515,49 @@
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취 · 내부 접근 확보</t>
+          <t>내부 접근 확보 · 데이터 유출</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-04</t>
+          <t>AIA-AO-03.2, AIA-AO-04</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>SCI-152</t>
+          <t>CL/INC-0606</t>
         </is>
       </c>
       <c r="O15" s="9" t="inlineStr">
         <is>
-          <t>StepSecurity(2026) hackerbot-claw — GitHub Actions exploitation | https://www.stepsecurity.io/blog/hackerbot-claw-github-actions-exploitation</t>
+          <t>Ctrl-Alt-Intel(2026) BuddyBoss supply chain attack (Part 2) | https://ctrlaltintel.com/research/BuddyBoss-2/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>AII-026</t>
+          <t>AII-018</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>AI in the Middle — 웹 AI 서비스를 C2 중계로 악용 실증</t>
+          <t>s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -23614,7 +23567,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -23624,59 +23577,59 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Check Point Research</t>
+          <t>UNC6426</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>자격증명·비밀 탈취 · 데이터 유출</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-01</t>
+          <t>AIA-AO-03.1, AIA-AO-05</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>AML.CS0061</t>
+          <t>CL/INC-0603</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
         <is>
-          <t>Check Point Research(2026) AI in the Middle | https://research.checkpoint.com/2026/ai-in-the-middle-turning-web-based-ai-services-into-c2-proxies-the-future-of-ai-driven-attacks/</t>
+          <t>The Hacker News(2026) UNC6426 Exploits Nx npm Supply Chain | https://thehackernews.com/2026/03/unc6426-exploits-nx-npm-supply-chain.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>AII-016</t>
+          <t>AII-017</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>공개 S3 버킷 노출 자격증명 경유 LLMjacking·GPU 악용</t>
+          <t>hackerbot-claw — 자율 에이전트의 GitHub Actions 워크플로 대량 악용</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>사례연구(익명)</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -23686,7 +23639,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -23701,12 +23654,12 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>자칭 자율 보안 연구 에이전트(hackerbot-claw)</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -23716,49 +23669,49 @@
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>자원 탈취 · 내부 접근 확보</t>
+          <t>자격증명·비밀 탈취 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-03.2, AIA-AO-05</t>
+          <t>AIA-AO-04</t>
         </is>
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0573</t>
+          <t>SCI-152</t>
         </is>
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Sysdig(2026) AI-assisted cloud intrusion achieves admin access in 8 minutes | https://sysdig.com/blog/ai-assisted-cloud-intrusion-achieves-admin-access-in-8-minutes/</t>
+          <t>StepSecurity(2026) hackerbot-claw — GitHub Actions exploitation | https://www.stepsecurity.io/blog/hackerbot-claw-github-actions-exploitation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>AII-006</t>
+          <t>AII-026</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)</t>
+          <t>AI in the Middle — 웹 AI 서비스를 C2 중계로 악용 실증</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>연구·시연</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>실증·연구</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -23768,69 +23721,69 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>폴란드</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>에너지·기반시설</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>러시아 국가 배후(ESET는 Sandworm, CERT Polska는 Static Tundra/Dragonfly 인프라 중첩으로 평가)</t>
+          <t>Check Point Research</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>연구·레드팀</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>데이터 파괴 · 감시·조작</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.2</t>
+          <t>AIA-CC-01</t>
         </is>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>OT/INC-008</t>
+          <t>AML.CS0061</t>
         </is>
       </c>
       <c r="O18" s="9" t="inlineStr">
         <is>
-          <t>CERT Polska(2026) Energy Sector Incident Report 2025 | https://cert.pl/uploads/docs/CERT_Polska_Energy_Sector_Incident_Report_2025.pdf</t>
+          <t>Check Point Research(2026) AI in the Middle | https://research.checkpoint.com/2026/ai-in-the-middle-turning-web-based-ai-services-into-c2-proxies-the-future-of-ai-driven-attacks/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>AII-008</t>
+          <t>AII-016</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>GTG-1002 — Claude Code를 악용한 자율 사이버 첩보 캠페인</t>
+          <t>공개 S3 버킷 노출 자격증명 경유 LLMjacking·GPU 악용</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>사례연구(익명)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -23840,7 +23793,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -23855,54 +23808,54 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>GTG-1002(Anthropic 평가 중국 국가 지원)</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 · 내부 접근 확보</t>
+          <t>자원 탈취 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01, AIA-AO-02, AIA-RD-04</t>
+          <t>AIA-IM-03.2, AIA-AO-05</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>AML.CS0069</t>
+          <t>CL/INC-0573</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
         <is>
-          <t>Anthropic(2025) Disrupting AI espionage | https://www.anthropic.com/news/disrupting-AI-espionage</t>
+          <t>Sysdig(2026) AI-assisted cloud intrusion achieves admin access in 8 minutes | https://sysdig.com/blog/ai-assisted-cloud-intrusion-achieves-admin-access-in-8-minutes/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>AII-005</t>
+          <t>AII-006</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ShadowRay 2.0 — 노출 Ray AI 인프라 크립토마이닝 캠페인</t>
+          <t>2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -23917,7 +23870,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -23927,59 +23880,59 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>폴란드</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>에너지·기반시설</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>IronErn440</t>
+          <t>러시아 국가 배후(ESET는 Sandworm, CERT Polska는 Static Tundra/Dragonfly 인프라 중첩으로 평가)</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>자원 탈취</t>
+          <t>데이터 파괴 · 감시·조작</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-03.1</t>
+          <t>AIA-VE-03.2</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0579</t>
+          <t>OT/INC-008</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
         <is>
-          <t>Oligo Security(2025) ShadowRay 2.0 | https://www.oligo.security/blog/shadowray-2-0-attackers-turn-ai-against-itself-in-global-campaign-that-hijacks-ai-into-self-propagating-botnet</t>
+          <t>CERT Polska(2026) Energy Sector Incident Report 2025 | https://cert.pl/uploads/docs/CERT_Polska_Energy_Sector_Incident_Report_2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>AII-004</t>
+          <t>AII-008</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>s1ngularity — Nx 빌드 도구 악성 버전과 피해 단말 AI CLI 악용</t>
+          <t>GTG-1002 — Claude Code를 악용한 자율 사이버 첩보 캠페인</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -24009,69 +23962,69 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>GTG-1002(Anthropic 평가 중국 국가 지원)</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취 · 소스 코드 유출</t>
+          <t>데이터 유출 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-03.1</t>
+          <t>AIA-AO-01, AIA-AO-02, AIA-RD-04</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>SCI-143, CL/INC-0552</t>
+          <t>AML.CS0069</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>Wiz(2025) s1ngularity — supply chain attack leaks secrets on GitHub | https://www.wiz.io/blog/s1ngularity-supply-chain-attack</t>
+          <t>Anthropic(2025) Disrupting AI espionage | https://www.anthropic.com/news/disrupting-AI-espionage</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>AII-028</t>
+          <t>AII-005</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Big Sleep — AI 에이전트의 실악용 임박 취약점 사전 발견</t>
+          <t>ShadowRay 2.0 — 노출 Ray AI 인프라 크립토마이닝 캠페인</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -24091,45 +24044,49 @@
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Google Project Zero·DeepMind</t>
+          <t>IronErn440</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>자원 탈취</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1</t>
-        </is>
-      </c>
-      <c r="N22" s="9" t="inlineStr"/>
+          <t>AIA-IM-03.1</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>CL/INC-0579</t>
+        </is>
+      </c>
       <c r="O22" s="9" t="inlineStr">
         <is>
-          <t>The Record(2025) Google says 'Big Sleep' AI tool found bug hackers planned to use | https://therecord.media/google-big-sleep-ai-tool-found-bug</t>
+          <t>Oligo Security(2025) ShadowRay 2.0 | https://www.oligo.security/blog/shadowray-2-0-attackers-turn-ai-against-itself-in-global-campaign-that-hijacks-ai-into-self-propagating-botnet</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>AII-007</t>
+          <t>AII-004</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)</t>
+          <t>s1ngularity — Nx 빌드 도구 악성 버전과 피해 단말 AI CLI 악용</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -24154,54 +24111,54 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>우크라이나</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>정부·군</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>APT28</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 · 내부 접근 확보</t>
+          <t>자격증명·비밀 탈취 · 소스 코드 유출</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-02, AIA-CC-01, AIA-VE-03.1</t>
+          <t>AIA-AO-03.1</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>AML.CS0044</t>
+          <t>SCI-143, CL/INC-0552</t>
         </is>
       </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>The Hacker News(2025) CERT-UA Discovers LAMEHUG Malware | https://thehackernews.com/2025/07/cert-ua-discovers-lamehug-malware.html</t>
+          <t>Wiz(2025) s1ngularity — supply chain attack leaks secrets on GitHub | https://www.wiz.io/blog/s1ngularity-supply-chain-attack</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>AII-003</t>
+          <t>AII-028</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Amazon Q Developer 확장에 삭제 지시 주입</t>
+          <t>Big Sleep — AI 에이전트의 실악용 임박 취약점 사전 발견</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -24211,12 +24168,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>연구·시연</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>실증·연구</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -24241,12 +24198,12 @@
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>미상(부적절 권한 토큰으로 커밋한 외부 계정)</t>
+          <t>Google Project Zero·DeepMind</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>연구·레드팀</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -24256,34 +24213,30 @@
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-04, AIA-AO-03.2</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>SCI-140</t>
-        </is>
-      </c>
+          <t>AIA-VE-01.1</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr"/>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>AWS Security Bulletin AWS-2025-015(2025) | https://aws.amazon.com/security/security-bulletins/AWS-2025-015/</t>
+          <t>The Record(2025) Google says 'Big Sleep' AI tool found bug hackers planned to use | https://therecord.media/google-big-sleep-ai-tool-found-bug</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>AII-015</t>
+          <t>AII-007</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Open WebUI 오설정 악용 크립토재킹(AI 생성 페이로드)</t>
+          <t>LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -24308,69 +24261,69 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>우크라이나</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>정부·군</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>APT28</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>자원 탈취</t>
+          <t>데이터 유출 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-03.1</t>
+          <t>AIA-CC-02, AIA-CC-01, AIA-VE-03.1</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0519</t>
+          <t>AML.CS0044</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>Sysdig(2025) Attacker exploits misconfigured AI tool to run AI-generated payload | https://sysdig.com/blog/attacker-exploits-misconfigured-ai-tool-to-run-ai-generated-payload/</t>
+          <t>The Hacker News(2025) CERT-UA Discovers LAMEHUG Malware | https://thehackernews.com/2025/07/cert-ua-discovers-lamehug-malware.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>AII-025</t>
+          <t>AII-003</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>AI ClickFix — 컴퓨터 사용 에이전트 탈취 실증</t>
+          <t>Amazon Q Developer 확장에 삭제 지시 주입</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -24380,7 +24333,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -24395,12 +24348,12 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>Embrace The Red(연구자)</t>
+          <t>미상(부적절 권한 토큰으로 커밋한 외부 계정)</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -24410,34 +24363,34 @@
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-04</t>
+          <t>AIA-CC-04, AIA-AO-03.2</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>AML.CS0055</t>
+          <t>SCI-140</t>
         </is>
       </c>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>Embrace The Red(2025) AI ClickFix — Hijacking Computer-Use Agents | https://embracethered.com/blog/posts/2025/ai-clickfix-ttp-claude/</t>
+          <t>AWS Security Bulletin AWS-2025-015(2025) | https://aws.amazon.com/security/security-bulletins/AWS-2025-015/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>AII-014</t>
+          <t>AII-029</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Rules File Backdoor — AI 코딩 도구 규칙 파일에 숨은 지시</t>
+          <t>XBOW 자율 펜테스트 에이전트의 HackerOne 미국 리더보드 1위</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -24457,12 +24410,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -24472,7 +24425,7 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>연구자(Pillar Security)</t>
+          <t>XBOW(자율 펜테스트 에이전트, 방어 측)</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
@@ -24487,34 +24440,30 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-04</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr">
-        <is>
-          <t>SCI-134</t>
-        </is>
-      </c>
+          <t>AIA-VE-01.1, AIA-VE-01.2</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="inlineStr"/>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>Pillar Security(2025) New Vulnerability in GitHub Copilot and Cursor | https://www.pillar.security/blog/new-vulnerability-in-github-copilot-and-cursor-how-hackers-can-weaponize-code-agents</t>
+          <t>XBOW(2025) The road to Top 1 — How XBOW did it | https://xbow.com/blog/top-1-how-xbow-did-it</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>AII-013</t>
+          <t>AII-015</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)</t>
+          <t>Open WebUI 오설정 악용 크립토재킹(AI 생성 페이로드)</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -24529,7 +24478,7 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -24539,17 +24488,17 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>금융·서비스</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>GoldFactory</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -24559,49 +24508,49 @@
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>계정 장악 · 금전 피해</t>
+          <t>자원 탈취</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-03</t>
+          <t>AIA-IM-03.1</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>IDI-060</t>
+          <t>CL/INC-0519</t>
         </is>
       </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
-          <t>Group-IB(2024) Face Off — first iOS trojan stealing facial recognition data | https://www.group-ib.com/blog/goldfactory-ios-trojan/</t>
+          <t>Sysdig(2025) Attacker exploits misconfigured AI tool to run AI-generated payload | https://sysdig.com/blog/attacker-exploits-misconfigured-ai-tool-to-run-ai-generated-payload/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>AII-002</t>
+          <t>AII-025</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Arup 딥페이크 화상회의 송금 사기</t>
+          <t>AI ClickFix — 컴퓨터 사용 에이전트 탈취 실증</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>연구·시연</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>실증·연구</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -24611,74 +24560,74 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>홍콩</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>Embrace The Red(연구자)</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>연구·레드팀</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>금전 피해</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1, AIA-IM-01</t>
+          <t>AIA-IA-04</t>
         </is>
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>IDI-013</t>
+          <t>AML.CS0055</t>
         </is>
       </c>
       <c r="O29" s="9" t="inlineStr">
         <is>
-          <t>CNN(2024) Finance worker pays out $25 million after video call with deepfake 'CFO' | https://edition.cnn.com/2024/02/04/asia/deepfake-cfo-scam-hong-kong-intl-hnk</t>
+          <t>Embrace The Red(2025) AI ClickFix — Hijacking Computer-Use Agents | https://embracethered.com/blog/posts/2025/ai-clickfix-ttp-claude/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>AII-012</t>
+          <t>AII-014</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 화상회의 복제 병행)</t>
+          <t>Rules File Backdoor — AI 코딩 도구 규칙 파일에 숨은 지시</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>연구·시연</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>실증·연구</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -24688,7 +24637,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -24703,49 +24652,49 @@
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>Contagious Interview(북한 연계, G1052)</t>
+          <t>연구자(Pillar Security)</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>연구·레드팀</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취 · 금전 피해</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1</t>
+          <t>AIA-CC-04</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>SCI-110</t>
+          <t>SCI-134</t>
         </is>
       </c>
       <c r="O30" s="9" t="inlineStr">
         <is>
-          <t>Unit 42(2023) Two Campaigns by North Korea Bad Actors Target Job Hunters | https://unit42.paloaltonetworks.com/two-campaigns-by-north-korea-bad-actors-target-job-hunters/</t>
+          <t>Pillar Security(2025) New Vulnerability in GitHub Copilot and Cursor | https://www.pillar.security/blog/new-vulnerability-in-github-copilot-and-cursor-how-hackers-can-weaponize-code-agents</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>AII-011</t>
+          <t>AII-013</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)</t>
+          <t>GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -24770,17 +24719,17 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>금융·서비스</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>GoldFactory</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -24795,99 +24744,330 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-02.2</t>
+          <t>AIA-IA-03</t>
         </is>
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>IDI-072</t>
+          <t>IDI-060</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
         <is>
-          <t>Retool(2023) When MFA isn't actually MFA | https://retool.com/blog/mfa-isnt-mfa</t>
+          <t>Group-IB(2024) Face Off — first iOS trojan stealing facial recognition data | https://www.group-ib.com/blog/goldfactory-ios-trojan/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
+          <t>AII-002</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Arup 딥페이크 화상회의 송금 사기</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>홍콩</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>사이버범죄</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>금전 피해</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-02.1, AIA-IM-01</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>IDI-013</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>CNN(2024) Finance worker pays out $25 million after video call with deepfake 'CFO' | https://edition.cnn.com/2024/02/04/asia/deepfake-cfo-scam-hong-kong-intl-hnk</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>AII-012</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>캠페인</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>글로벌</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>IT·소프트웨어</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>Contagious Interview(북한 연계, G1052)</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>국가배후</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>자격증명·비밀 탈취 · 금전 피해</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-04</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>SCI-110</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>Unit 42(2023) Two Campaigns by North Korea Bad Actors Target Job Hunters | https://unit42.paloaltonetworks.com/two-campaigns-by-north-korea-bad-actors-target-job-hunters/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>AII-011</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>IT·소프트웨어</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>사이버범죄</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>계정 장악 · 금전 피해</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-02.2</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>IDI-072</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>Retool(2023) When MFA isn't actually MFA | https://retool.com/blog/mfa-isnt-mfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
           <t>AII-001</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>홍콩 딥페이크 얼굴 바꾸기로 대출·계좌 개설 사기 조직 검거</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>사고</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>홍콩</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>금융·서비스</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>사기 조직(6명 체포)</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>사이버범죄</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>금전 피해 · 계정 장악</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>AIA-IA-03</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>IDI-061</t>
         </is>
       </c>
-      <c r="O32" s="9" t="inlineStr">
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>The Standard(2023) Six arrested for defrauding HK$200,000 using deepfake face-swap program | https://www.thestandard.com.hk/news/article/207493/Six-arrested-for-defrauding-HK200000-using-deepfake-face-swap-program</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O32"/>
+  <autoFilter ref="A1:O35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
+++ b/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
@@ -7759,7 +7759,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>사람 속도를 넘는 반복·연쇄 행위 시퀀스와 비정상 세션 속도를 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
+          <t>AI 속도 공격을 전제한 탐지·대응 자동화와 대응 속도 단축, AI 제공자 오남용 탐지 연계(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>대량·자동화된 데이터 접근·반출 패턴과 비정상 egress를 모니터링(NIST SI-4·AU-6·SC-7)</t>
+          <t>데이터 접근 최소화·DLP·egress 통제로 자동 반출을 차단하고 조기 경보(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] AI 보조 클라우드 침입(Sygnia 익명 사례)(2026-06) (AII-022)</t>
+          <t>[실제 사고] s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)(2026-03) (AII-018)</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>자격증명의 비정상 사용·급속한 권한 확대·측면 이동을 아이덴티티·클라우드 로그로 탐지(NIST AC-2·SI-4)</t>
+          <t>최소 권한·단기 자격증명·이상 접근 차단으로 확산 속도를 늦춤(NIST AC-2·AC-6)</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>시그니처가 아닌 행위·맥락 기반으로 변종 악성코드를 탐지하고 무결성 변화를 감시(NIST SI-3·SI-4·SI-7)</t>
+          <t>행위 기반 EDR·실행 통제로 변종에 대응하고(NIST SI-3), 무결성 검증으로 변조를 차단(NIST SI-7)</t>
         </is>
       </c>
     </row>
@@ -8026,12 +8026,12 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] prt-scan — 취약 GitHub 워크플로 대상 기회주의 공급망 캠페인(2026-04) (AII-020)</t>
+          <t>[실제 사고] BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)(2026-03) (AII-019)</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지(NIST SI-4)</t>
+          <t>워크플로 트리거·권한을 최소화하고(pull_request_target 등) 파이프라인 변경을 검증(NIST CM-7·SA-15)</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>동시다발 표적에 걸친 유사 패턴·상관 이벤트와 병렬 세션 급증을 탐지(NIST SI-4·CA-7)</t>
+          <t>교차 표적 상관 분석과 대응 자동화로 병렬 웨이브에 대응하고 사후 감사로 조율 구조를 추적(NIST SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>AI 개발 도구의 비정상 설정 변경·과도한 권한 사용·공급망 산출물 변조를 탐지(NIST SI-4·SA-15)</t>
+          <t>AI 도구의 권한·승인 경계를 최소화하고 개발 파이프라인 변경을 검증(NIST AC-6·SA-15)</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지(NIST SI-4)</t>
+          <t>AI 개발 도구의 실행 권한·위험 옵션을 최소 권한·허용 목록으로 제한(NIST AC-6·CM-7)</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설·접근 패턴을 모니터링(NIST IA-2·AC-2)</t>
+          <t>강화된 라이브니스·다중 요소·문서 진위 검증과 위험 기반 추가 확인을 적용(NIST IA-2·AC-2)</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>AI 에이전트 특유의 빠른·반복적 행위 시퀀스와 도구 연쇄 호출을 행위 기반으로 탐지(NIST SI-4·PM-16)</t>
+          <t>AI 속도 공격을 전제한 탐지·대응 자동화와 AI 제공자 오남용 탐지 연계, 공격 하네스 구성 요소 차단(NIST SI-4·SA-11)</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>발신 평판·행위·링크 분석 등 콘텐츠 품질에 덜 의존하는 다중 신호로 피싱을 탐지(NIST SI-4)</t>
+          <t>피싱 내성 MFA·조건부 접근과 사용자 신고·교육으로 대량 미끼에 대응(NIST AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>AI 인프라의 비정상 자원 사용·외부 노출·무인증 접근을 모니터링(NIST SI-4·CM-7)</t>
+          <t>AI 인프라 인증·접근 통제와 노출 최소화·최소 권한으로 자원 탈취를 차단(NIST AC-6·CM-7)</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>고액·비정상 송금 요청과 사칭 징후를 결제·승인 흐름에서 모니터링(NIST IA-2)</t>
+          <t>고액 송금에 다채널·사전 등록 경로 확인과 역할 분리·한도를 적용(NIST AT-2(3)·IA-2)</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>고액·고위험 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검(NIST IA-2)</t>
+          <t>고위험 요청에 다채널·사전 등록 경로 확인을 의무화하고 사용자 교육(NIST AT-2(3)·IA-2)</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>대량 파일 변경·삭제와 파괴형 실행 행위를 조기 탐지하고 백업 무결성을 감시(NIST SI-3·SI-7)</t>
+          <t>행위 기반 탐지·실행 통제와 오프라인·불변 백업으로 복구력을 확보(NIST SI-7·CP-9)</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위·맥락 기반으로 탐지(NIST SI-3·SI-4·AU-6)</t>
+          <t>AI 서비스 egress 통제와 행위 기반 실행 탐지로 동적 명령 생성에 대응(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스로의 비정상 egress 패턴·데이터량과 자동화된 세션을 모니터링(NIST SC-7·SI-4·AU-6)</t>
+          <t>AI 서비스 egress 가시성·허용 목록으로 비인가 AI 트래픽을 통제(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>자사 자산에 대한 자동·대규모 취약점 탐색 정황과 비정상 접근 패턴을 모니터링(NIST RA-5)</t>
+          <t>자체 AI 보조 취약점 발굴·퍼징으로 공격자보다 먼저 찾고(NIST SA-11), 신속 패치·무결성 검증으로 노출 구간을 좁힘(NIST SI-7·RA-5)</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>공개 직후 집중되는 익스플로잇 시도와 알려진 취약점의 비정상 악용을 모니터링(NIST RA-5)</t>
+          <t>신속 패치·가상 패치와 무결성 검증으로 즉시 무기화에 대응하고(NIST SI-7), 자체 익스플로잇 가능성 평가로 우선순위화(NIST SA-11·RA-5)</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>관리형 LLM·GPU의 비정상 사용량·과금 급증과 비정상 추론 호출을 모니터링(NIST AC-2·SI-4)</t>
+          <t>자격증명 최소 권한·단기화와 사용량 이상 탐지·한도로 무단 사용을 차단(NIST AC-2·AC-6)</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>외부 노출 자산을 지속 식별하고 비정상적으로 빠른 열거·탐침 패턴을 모니터링(NIST RA-5·SI-4)</t>
+          <t>공격면을 줄이고 관리 인터페이스를 경계 밖에 노출하지 않음(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>헬프데스크·계정 복구 요청의 음성 사칭 징후와 비정상 MFA 등록을 점검(NIST IA-2)</t>
+          <t>음성에 의존하지 않는 본인확인(콜백·사전 등록·피싱 내성 MFA)과 헬프데스크 절차 강화(NIST IA-2·AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>규칙·설정 파일의 비가시 문자·숨은 지시와 생성 코드의 의심 변경을 검사(NIST SI-7·SA-15)</t>
+          <t>규칙·설정 파일을 변경 통제·리뷰 대상에 포함하고 비가시 문자를 정규화·차단(NIST SA-15·CM-7)</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>자사 자산의 공개 취약점·PoC 공개 동향을 신속 수집해 노출 여부를 대조(NIST RA-5)</t>
+          <t>공개 취약점의 신속 패치·완화를 우선순위화해 n-day 노출 구간을 좁힘(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>에이전트·사용자의 미끼 실행 흐름(클립보드→터미널 등)과 의심 링크 접근을 행위 기반으로 탐지(NIST SI-4)</t>
+          <t>컴퓨터 사용 에이전트의 실행 권한·승인 경계를 두고 미끼 유형을 교육(NIST AT-2(3)·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>행위·맥락 기반 탐지와 다중 엔진·이상 탐지로 변형·적대적 회피를 보완 탐지(NIST SI-3·SI-4)</t>
+          <t>시그니처 의존을 줄이고 행위 기반·무결성 검증을 강화, 탐지 모델에 적대적 견고성을 반영(NIST SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>실행 단계에서 생성형 도구의 산출물(비정형 스크립트·명령)을 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
+          <t>시그니처가 아닌 행위·맥락 기반 탐지로 매번 달라지는 산출물에 대응하고 최소 권한을 적용(NIST SI-4·PM-16)</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>자사·임직원 대상 공개정보 노출과 비정상 수집 정황(대량 조회·스크레이핑)을 위협 인텔리전스로 점검(NIST PM-16·SI-4)</t>
+          <t>핵심 인력·과제의 공개 노출 범위를 정하고 프로필·발표·채용 공고의 민감 정보를 최소화(NIST PM-16)</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>지하 시장·공세 LLM 동향을 위협 인텔로 수집하고 자사 대상 악용 징후를 모니터링(NIST PM-16·SI-4)</t>
+          <t>공세 LLM이 만들어내는 산출물(피싱·악성코드)의 탐지·대응 역량을 강화해 역량 확보 자체보다 '사용 시점'을 막음(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="N34" s="9" t="inlineStr">
         <is>
-          <t>공개된 조직·거래 정보의 노출 범위와 사칭에 쓰일 수 있는 맥락을 주기적으로 점검(NIST PM-16·SI-4)</t>
+          <t>조직 구조·거래 관계의 불필요한 공개를 줄이고 고위험 역할의 공개 노출을 관리(NIST PM-16)</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>캠페인 규모·빈도 증가와 교차 표적 상관 지표를 지속 모니터링(NIST SI-4·CA-7)</t>
+          <t>탐지·대응 자동화로 대량 캠페인에 대응하고 위협 인텔로 우선순위화(NIST SI-4·PM-16)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>고위험 역할 대상 메시지의 이상 징후(발신 경로·요청 맥락)와 비정상 송금·승인 요청을 모니터링(NIST SI-4)</t>
+          <t>고액·고위험 요청에 다채널 확인과 역할 기반 교육을 적용(NIST AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스·클라우드로의 비정상 egress와 신규·일회성 계정·도메인 사용을 모니터링(NIST SC-7·SI-4)</t>
+          <t>AI 서비스 egress 가시성을 확보하고 비인가 AI 트래픽·신규 인프라 접속을 통제(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="N38" s="9" t="inlineStr">
         <is>
-          <t>의존성·자체 코드의 신규 취약점 공개와 악용 정황을 신속 대조(NIST RA-5)</t>
+          <t>개발 단계에 AI 보조 테스트를 통합해 선제 발견하고(NIST SA-11·SA-15), 취약 구성요소를 신속 교체(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>모델 가중치·데이터 유출과 비정상 대량 질의(증류 정황)를 자사 AI 자산에서 모니터링(NIST PM-16)</t>
+          <t>자사 모델·데이터의 유출·추출을 통제해 공세 파생 모델의 재료가 되지 않게 함(NIST PM-16)</t>
         </is>
       </c>
     </row>

--- a/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
+++ b/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
@@ -24,9 +24,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경이력" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보고서용 간략 매트릭스'!$A$4:$N$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보고서용 간략 매트릭스'!$A$4:$O$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'보고서용 간략 매트릭스'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'통합 매트릭스'!$A$4:$AR$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'통합 매트릭스'!$A$4:$AS$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'통합매트릭스_LITE'!$A$2:$S$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$O$33</definedName>
   </definedNames>
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,11 +78,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
@@ -102,6 +102,10 @@
     <font>
       <b val="1"/>
       <color rgb="001E8449"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F8C8D"/>
     </font>
   </fonts>
   <fills count="14">
@@ -198,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,10 +242,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -273,6 +277,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1047,7 +1054,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>매우 높음 10 · 높음 8 · 보통 15 · 낮음 1</t>
+          <t>매우 높음 8 · 높음 4 · 보통 21 · 낮음 1</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1066,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>실제 사고 확인 22 · 실사용 역량(성숙도) 7 · 실증·공개 PoC 5 · 이론·연구 시연 0</t>
+          <t>실제 사고 확인 22 · 실사용 역량(성숙도) 7 · 실증·공개 PoC 4 · 이론·연구 시연 1</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1078,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>상 17 · 중 16 · 하 1</t>
+          <t>상 10 · 중 23 · 하 1</t>
         </is>
       </c>
     </row>
@@ -1134,13 +1141,13 @@
           <t>1. AIA-AO-01 단일 자율 공격 에이전트 실행 — 매우 높음, 실제 사고 6건(성숙도 실사용)
 2. AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 — 매우 높음, 실제 사고 4건(성숙도 실사용)
 3. AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 — 매우 높음, 실제 사고 3건(성숙도 실증)
-4. AIA-VE-03.1 AI 생성·AI 연동 악성코드 — 매우 높음, 실제 사고 3건(성숙도 실사용)
-5. AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 — 매우 높음, 실제 사고 3건(성숙도 실사용)
-6. AIA-AO-02 다중 에이전트 공격 조율 — 매우 높음, 실제 사고 3건(성숙도 실사용)
-7. AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-8. AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-9. AIA-IA-03 딥페이크 기반 생체·본인확인 우회 — 매우 높음, 실제 사고 2건(성숙도 실사용)
-10. AIA-RD-04 공세 AI 에이전트·공격 하네스 구축 — 매우 높음, 실제 사고 2건(성숙도 실사용)</t>
+4. AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 — 매우 높음, 실제 사고 3건(성숙도 실사용)
+5. AIA-AO-02 다중 에이전트 공격 조율 — 매우 높음, 실제 사고 3건(성숙도 실사용)
+6. AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
+7. AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
+8. AIA-IA-03 딥페이크 기반 생체·본인확인 우회 — 매우 높음, 실제 사고 2건(성숙도 실사용)
+9. AIA-VE-03.1 AI 생성·AI 연동 악성코드 — 높음, 실제 사고 3건(성숙도 실사용)
+10. AIA-RD-04 공세 AI 에이전트·공격 하네스 구축 — 높음, 실제 사고 2건(성숙도 실사용)</t>
         </is>
       </c>
     </row>
@@ -4301,11 +4308,11 @@
         <v>7</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-01.1, AIA-IM-01, AIA-IA-02.1, AIA-IA-02.2, AIA-IA-04, AIA-RT-01.1, AIA-IA-01.2</t>
+          <t>AIA-IM-01, AIA-IA-02.1, AIA-IA-01.1, AIA-IA-02.2, AIA-IA-04, AIA-RT-01.1, AIA-IA-01.2</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4331,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
@@ -4393,7 +4400,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -4462,11 +4469,11 @@
         <v>5</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1, AIA-VE-02, AIA-RT-02, AIA-RT-03, AIA-VE-01.2</t>
+          <t>AIA-RT-02, AIA-RT-03, AIA-VE-01.1, AIA-VE-01.2, AIA-VE-02</t>
         </is>
       </c>
     </row>
@@ -4485,11 +4492,11 @@
         <v>4</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-04, AIA-VE-01.1, AIA-VE-02, AIA-VE-01.2</t>
+          <t>AIA-RD-04, AIA-VE-01.1, AIA-VE-01.2, AIA-VE-02</t>
         </is>
       </c>
     </row>
@@ -4531,11 +4538,11 @@
         <v>5</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-02, AIA-IA-01.1, AIA-CC-01, AIA-RT-02, AIA-RD-03</t>
+          <t>AIA-IM-02, AIA-IA-01.1, AIA-RT-02, AIA-CC-01, AIA-RD-03</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4561,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -4577,11 +4584,11 @@
         <v>23</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01, AIA-IM-02, AIA-AO-05, AIA-VE-03.1, AIA-AO-04, AIA-AO-02, AIA-AO-03.2, AIA-AO-03.1, AIA-RD-04, AIA-IA-01.1, AIA-CC-02, AIA-CC-01, AIA-RT-02, AIA-AO-06, AIA-IA-04, AIA-CC-03, AIA-RD-02, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-IA-01.2, AIA-RD-03</t>
+          <t>AIA-AO-01, AIA-IM-02, AIA-AO-05, AIA-AO-04, AIA-AO-02, AIA-AO-03.2, AIA-AO-03.1, AIA-VE-03.1, AIA-RD-04, AIA-IA-01.1, AIA-RT-02, AIA-AO-06, AIA-CC-02, AIA-CC-01, AIA-IA-04, AIA-CC-03, AIA-RD-02, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-IA-01.2, AIA-RD-03</t>
         </is>
       </c>
     </row>
@@ -4600,11 +4607,11 @@
         <v>6</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1, AIA-VE-03.2, AIA-VE-01.1, AIA-VE-02, AIA-CC-04, AIA-CC-03</t>
+          <t>AIA-VE-03.1, AIA-VE-03.2, AIA-CC-04, AIA-CC-03, AIA-VE-01.1, AIA-VE-02</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6713,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>성공하면 조직 전반이 장악되거나 대규모 금전·데이터 피해로 이어지고, AI가 공격을 사람이 대응하기 어려운 속도·규모로 밀어붙여 피해 범위를 가늠하기 어려운 위협</t>
+          <t>성공하면 조직 전반이 장악되거나 대규모 금전·데이터 피해·가용성/안전 피해로 이어지는 위협(영향만으로 판정 — 속도·규모·탐지 난이도는 고유 축·우선순위에서 다룸, 검토 6.1)</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6935,71 +6942,71 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>통합본 뷰 Lv0 편입(scripts/build_integrated_view.py)</t>
+          <t>위험 산정(P3, scripts/build·taxonomy_rules)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>AI 활용 공격 매트릭스를 통합본 v4.1(요약 위협 237개)에 '뷰(view) Lv0'로 얹는 빌더·산출물 추가(D9). 렌즈라 기존 6개와 겹치므로 재수록 대신 연계만 하고 고유 위협 수에는 넣지 않음(이중계산 방지). 세부위협 35개의 연계(AI·CL·OT·SC·ID·PH)가 기존 237개 중 29개를 닿음(교차 54건). 산출물: integrated/output/통합_보안위협_매트릭스_v5_AI활용공격뷰.xlsx(5시트)·통합_AI활용공격뷰_v5.md·교차 CSV. 기존 통합 빌드와 독립(v4.1 산출물 불변)</t>
+          <t>검토 6.1 렌즈 보조 규칙 적용 — 심각도는 영향만으로 판정(속도·규모·탐지 난이도는 고유 축·우선순위로 이관, RD·VE·CC 역량·발굴·생성·은닉·C2 행을 중으로 재조정), 발생가능성 상=실제 사고 가중 2 이상+서로 다른 행위자·캠페인 2개 이상(ai_use 확인 1·추정 0.5), 하=공격자 사용 1차 근거 없음+성숙도 연구시연, ATLAS 사례는 발생가능성 독립 신호에서 제외(참고 열), 경계 플래그·성숙도 자동 산출 신설. 결과 위험도 매우 높음 8·높음 4·보통 21·낮음 1(발생가능성 상 10·중 23·하 1), 경계 7행</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>④단계 — 통합본에 Lv0 뷰로 편입(D9), 고유 위협 수 이중계산 방지</t>
+          <t>심각도·발생가능성이 렌즈 취지와 어긋나 과대평가되던 문제 교정(검토 3.1~3.3)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>관점 문구(data/text/*.yaml)</t>
+          <t>분류·사고 DB(P0·P1)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>35개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성(RT 4·RD 5·VE 5·IA 6·AO 6·CC 4·IM 5). 인용 사례 45건([실제 사고]·[위협인텔]·[실증]), 실제 사고가 없는 8개 행(정찰·역량 확보·방어 회피 등)은 '공개 사고 미확인 — 사유'와 AI 역량 성숙도로 근거 표기. 참고 문헌은 ■ 관점·■ 대응 끝 '참고:' 줄로 인용</t>
+          <t>P0: 사고 DB 사실·출처·매핑 정정(XBOW·GTIG 0-day·CrowdStrike 4행위자·Hermes·대만·CaptiveCrunch 등), ai_use를 주장의 확신도 기준(확인/추정/미확인)으로 재정의, 폐기 ID ASI-T01→OWASP ASI01~10, VE 행 무관 AI-01-02 연계 제거. P1: IM-03.1 크립토재킹·IM-03.2 LLMjacking(AI 피해 대상) 삭제·AI/클라우드 연계만(사용자 결정), 통제 이탈 자율 에이전트 행 AIA-AO-06 신설(D14), 방어 측 역량 실증 capability_indicator 분리(D13), VE 도메인명 확장. 세부위협 35→34·사고 34→32(재정의·분리 반영)·시나리오 8→7(ASN-08 제거)</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>③단계(v2) — 방어 관점(가드레일 D11: 공세 제작법·악용 절차 미기재, 탐지·대응 중심)으로 행마다 근거·통제를 연결</t>
+          <t>검토(emerging/검토_수정방향.md) D13~D18 확정 반영 — 근거 무결성·구조 정합</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -7009,22 +7016,22 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>시나리오</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
+          <t>통합본 뷰 Lv0 편입(scripts/build_integrated_view.py)</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>실제 사고를 AI 활용 공격 흐름 8개로 재구성(ASN-01~08) — 자율·다중 에이전트 첩보(GTG-1002), 탈옥 모델 자율 하네스(Hermes), AI CLI 악용→클라우드 장악(s1ngularity), 딥페이크 화상회의 송금(Arup), AI 연동 악성코드→AI 서비스 C2(LAMEHUG), 딥페이크 생체 우회, 워크플로 대량 악용→연쇄 침해, LLMjacking·크립토재킹. 19개 단계·초크 포인트 17개</t>
+          <t>AI 활용 공격 매트릭스를 통합본 v4.1(요약 위협 237개)에 '뷰(view) Lv0'로 얹는 빌더·산출물 추가(D9). 렌즈라 기존 6개와 겹치므로 재수록 대신 연계만 하고 고유 위협 수에는 넣지 않음(이중계산 방지). 세부위협 35개의 연계(AI·CL·OT·SC·ID·PH)가 기존 237개 중 29개를 닿음(교차 54건). 산출물: integrated/output/통합_보안위협_매트릭스_v5_AI활용공격뷰.xlsx(5시트)·통합_AI활용공격뷰_v5.md·교차 CSV. 기존 통합 빌드와 독립(v4.1 산출물 불변)</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점(초크 포인트)을 드러냄</t>
+          <t>④단계 — 통합본에 Lv0 뷰로 편입(D9), 고유 위협 수 이중계산 방지</t>
         </is>
       </c>
     </row>
@@ -7041,29 +7048,29 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py</t>
+          <t>관점 문구(data/text/*.yaml)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오 검사 이식 — oneline 50자·summary 2줄·■ 관점/실제 사례·■ 탐지/대응 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATLAS·ATT&amp;CK·OWASP·NIST·연계) 존재·행 매핑, 용어·가드레일(공세 제작법 표현 차단), 시나리오 ID·단계·사고·초크 포인트. 문구 35·시나리오 8을 --strict로 검증해 오류·경고 0</t>
+          <t>35개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성(RT 4·RD 5·VE 5·IA 6·AO 6·CC 4·IM 5). 인용 사례 45건([실제 사고]·[위협인텔]·[실증]), 실제 사고가 없는 8개 행(정찰·역량 확보·방어 회피 등)은 '공개 사고 미확인 — 사유'와 AI 역량 성숙도로 근거 표기. 참고 문헌은 ■ 관점·■ 대응 끝 '참고:' 줄로 인용</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오의 사례·수치·ID·가드레일을 사고 DB·카탈로그와 기계적으로 대조</t>
+          <t>③단계(v2) — 방어 관점(가드레일 D11: 공세 제작법·악용 절차 미기재, 탐지·대응 중심)으로 행마다 근거·통제를 연결</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -7073,29 +7080,29 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>시나리오</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
+          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
+          <t>실제 사고를 AI 활용 공격 흐름 8개로 재구성(ASN-01~08) — 자율·다중 에이전트 첩보(GTG-1002), 탈옥 모델 자율 하네스(Hermes), AI CLI 악용→클라우드 장악(s1ngularity), 딥페이크 화상회의 송금(Arup), AI 연동 악성코드→AI 서비스 C2(LAMEHUG), 딥페이크 생체 우회, 워크플로 대량 악용→연쇄 침해, LLMjacking·크립토재킹. 19개 단계·초크 포인트 17개</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
+          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점(초크 포인트)을 드러냄</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -7105,29 +7112,29 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>위험평가 결과</t>
+          <t>scripts/validate.py</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
+          <t>문구·시나리오 검사 이식 — oneline 50자·summary 2줄·■ 관점/실제 사례·■ 탐지/대응 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATLAS·ATT&amp;CK·OWASP·NIST·연계) 존재·행 매핑, 용어·가드레일(공세 제작법 표현 차단), 시나리오 ID·단계·사고·초크 포인트. 문구 35·시나리오 8을 --strict로 검증해 오류·경고 0</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
+          <t>문구·시나리오의 사례·수치·ID·가드레일을 사고 DB·카탈로그와 기계적으로 대조</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -7142,24 +7149,24 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>분류 체계(data/taxonomy.yaml)</t>
+          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
+          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
+          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -7169,22 +7176,22 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>사고 DB(data/incidents.yaml)</t>
+          <t>위험평가 결과</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
+          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
+          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
         </is>
       </c>
     </row>
@@ -7201,22 +7208,22 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>교차 매핑</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+          <t>분류 체계(data/taxonomy.yaml)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
+          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
+          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
         </is>
       </c>
     </row>
@@ -7238,17 +7245,17 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>참조 추출본(reference/)</t>
+          <t>사고 DB(data/incidents.yaml)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
+          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
+          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
         </is>
       </c>
     </row>
@@ -7265,22 +7272,22 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>교차 매핑</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py · taxonomy_rules.py</t>
+          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
         </is>
       </c>
     </row>
@@ -7297,20 +7304,84 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>참조 추출본(reference/)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>scripts/validate.py · taxonomy_rules.py</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
           <t>결정</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>작업방향 D3~D9·D11·D12</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>emerging/작업방향.md 10장 권장안을 ①단계 착수 결정으로 확정 — D3(킬체인 7단계+AI 역할·자율성)·D4(발생가능성에 AI 역량 성숙도 신호)·D8(재인용+신규)·D9(통합본 뷰 Lv0, ④단계)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인). D5~D7은 영역 2(enterprise) 결정이라 영역 2 착수 시 확정</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>사용자 지침 — 남은 결정은 착수 시 확정</t>
         </is>
@@ -7327,7 +7398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7336,14 +7407,15 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7393,40 +7465,45 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>발생가능성</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>심각도</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>AI 역할</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>고유성</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>성숙도</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>실제 사고 수</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>대표 사례</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>핵심 대응</t>
         </is>
@@ -7461,40 +7538,41 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>완전자율</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="M5" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 거의 전권을 위임한 AI 에이전트로 CRM 업체 고객 데이터 반출(CrowdStrike 행위자 4)(2026-10) (AII-034)</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>AI 속도 공격을 전제한 탐지·대응 자동화와 대응 속도 단축, AI 제공자 오남용 탐지 연계(NIST SI-4)</t>
         </is>
@@ -7529,40 +7607,41 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>반자율</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="M6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 거의 전권을 위임한 AI 에이전트로 CRM 업체 고객 데이터 반출(CrowdStrike 행위자 4)(2026-10) (AII-034)</t>
         </is>
       </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>데이터 접근 최소화·DLP·egress 통제로 자동 반출을 차단하고 조기 경보(NIST SC-7·SI-4)</t>
         </is>
@@ -7599,38 +7678,43 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>반자율</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>실증</t>
         </is>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="M7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)(2026-03) (AII-018)</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>최소 권한·단기 자격증명·이상 접근 차단으로 확산 속도를 늦춤(NIST AC-2·AC-6)</t>
         </is>
@@ -7642,22 +7726,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[AO] 자율 실행·확산</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1</t>
+          <t>AIA-AO-04</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>AI 생성·AI 연동 악성코드</t>
+          <t>자율 에이전트의 CI/CD·워크플로 대량 악용</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>AI 생성·AI 연동 악성코드로 변종 양산·탐지 회피</t>
+          <t>자율 에이전트가 CI/CD·워크플로 결함을 자동·대량 악용</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -7667,40 +7751,45 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>보조</t>
-        </is>
-      </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="M8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] BREEZE COMET — 생성형 AI를 악성코드 개발에 활용한 브라질 금융 공격(2026-09) (AII-024)</t>
-        </is>
-      </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>행위 기반 EDR·실행 통제로 변종에 대응하고(NIST SI-3), 무결성 검증으로 변조를 차단(NIST SI-7)</t>
+          <t>[실제 사고] BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)(2026-03) (AII-019)</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>워크플로 트리거·권한을 최소화하고(pull_request_target 등) 파이프라인 변경을 검증(NIST CM-7·SA-15)</t>
         </is>
       </c>
     </row>
@@ -7715,17 +7804,17 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-04</t>
+          <t>AIA-AO-02</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>자율 에이전트의 CI/CD·워크플로 대량 악용</t>
+          <t>다중 에이전트 공격 조율</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>자율 에이전트가 CI/CD·워크플로 결함을 자동·대량 악용</t>
+          <t>상위 오케스트레이터가 다중 하위 에이전트로 공격 웨이브 병렬화</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -7733,42 +7822,43 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>반자율</t>
-        </is>
-      </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
+          <t>완전자율</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="M9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)(2026-03) (AII-019)</t>
-        </is>
-      </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>워크플로 트리거·권한을 최소화하고(pull_request_target 등) 파이프라인 변경을 검증(NIST CM-7·SA-15)</t>
+          <t>[실제 사고] AI 에이전트 하네스로 여러 나라 정부·민간 20곳 이상 표적(CrowdStrike 행위자 2)(2026-10) (AII-032)</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>교차 표적 상관 분석과 대응 자동화로 병렬 웨이브에 대응하고 사후 감사로 조율 구조를 추적(NIST SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7783,17 +7873,17 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-02</t>
+          <t>AIA-AO-03.2</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>다중 에이전트 공격 조율</t>
+          <t>AI 개발 도구 신뢰·설정 악용</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>상위 오케스트레이터가 다중 하위 에이전트로 공격 웨이브 병렬화</t>
+          <t>AI 개발 도구의 광범위 실행 권한·신뢰를 공격 수행에 악용</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -7803,40 +7893,45 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>완전자율</t>
-        </is>
-      </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
+          <t>반자율</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] AI 에이전트 하네스로 여러 나라 정부·민간 20곳 이상 표적(CrowdStrike 행위자 2)(2026-10) (AII-032)</t>
-        </is>
+      <c r="M10" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>교차 표적 상관 분석과 대응 자동화로 병렬 웨이브에 대응하고 사후 감사로 조율 구조를 추적(NIST SI-4·AU-6)</t>
+          <t>[실제 사고] BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)(2026-03) (AII-019)</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>AI 도구의 권한·승인 경계를 최소화하고 개발 파이프라인 변경을 검증(NIST AC-6·SA-15)</t>
         </is>
       </c>
     </row>
@@ -7851,17 +7946,17 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-03.2</t>
+          <t>AIA-AO-03.1</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>AI 개발 도구 신뢰·설정 악용</t>
+          <t>피해 단말의 AI CLI·로컬 에이전트 악용</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>AI 개발 도구의 광범위 실행 권한·신뢰를 공격 수행에 악용</t>
+          <t>피해 단말에 설치된 AI CLI를 공격 실행 엔진으로 악용</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -7871,40 +7966,45 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>반자율</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="M11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] BuddyBoss 공급망 공격(Claude Code 세션 기록 확인)(2026-03) (AII-019)</t>
-        </is>
-      </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>AI 도구의 권한·승인 경계를 최소화하고 개발 파이프라인 변경을 검증(NIST AC-6·SA-15)</t>
+          <t>[실제 사고] s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)(2026-03) (AII-018)</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>AI 개발 도구의 실행 권한·위험 옵션을 최소 권한·허용 목록으로 제한(NIST AC-6·CM-7)</t>
         </is>
       </c>
     </row>
@@ -7914,22 +8014,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>[AO] 자율 실행·확산</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-03.1</t>
+          <t>AIA-IA-03</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>피해 단말의 AI CLI·로컬 에이전트 악용</t>
+          <t>딥페이크 기반 생체·본인확인 우회</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>피해 단말에 설치된 AI CLI를 공격 실행 엔진으로 악용</t>
+          <t>딥페이크로 생체·비대면 본인확인(KYC) 우회해 계정 장악</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -7939,40 +8039,45 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>반자율</t>
-        </is>
-      </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
+          <t>증폭</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="M12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] s1ngularity 노출 클라우드 키 악용 측면 이동(QUIETVAULT)(2026-03) (AII-018)</t>
-        </is>
-      </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>AI 개발 도구의 실행 권한·위험 옵션을 최소 권한·허용 목록으로 제한(NIST AC-6·CM-7)</t>
+          <t>[실제 사고] GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)(2024-02) (AII-013)</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>강화된 라이브니스·다중 요소·문서 진위 검증과 위험 기반 추가 확인을 적용(NIST IA-2·AC-2)</t>
         </is>
       </c>
     </row>
@@ -7982,65 +8087,70 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-03</t>
+          <t>AIA-VE-03.1</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>딥페이크 기반 생체·본인확인 우회</t>
+          <t>AI 생성·AI 연동 악성코드</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>딥페이크로 생체·비대면 본인확인(KYC) 우회해 계정 장악</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>AI 생성·AI 연동 악성코드로 변종 양산·탐지 회피</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
           <t>보조</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)(2024-02) (AII-013)</t>
-        </is>
+      <c r="M13" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>강화된 라이브니스·다중 요소·문서 진위 검증과 위험 기반 추가 확인을 적용(NIST IA-2·AC-2)</t>
+          <t>[실제 사고] BREEZE COMET — 생성형 AI를 악성코드 개발에 활용한 브라질 금융 공격(2026-09) (AII-024)</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>행위 기반 EDR·실행 통제로 변종에 대응하고(NIST SI-3), 무결성 검증으로 변조를 차단(NIST SI-7)</t>
         </is>
       </c>
     </row>
@@ -8068,45 +8178,50 @@
           <t>스캐너·도구를 엮은 공세 AI 에이전트·공격 하네스 구축</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
           <t>반자율</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="M14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
         </is>
       </c>
-      <c r="N14" s="9" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>AI 속도 공격을 전제한 탐지·대응 자동화와 AI 제공자 오남용 탐지 연계, 공격 하네스 구성 요소 차단(NIST SI-4·SA-11)</t>
         </is>
@@ -8118,22 +8233,22 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[IM] 영향·규모화</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-01.1</t>
+          <t>AIA-IM-01</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>AI 생성 대량 피싱·미끼</t>
+          <t>딥페이크·AI 사칭 기반 금전 사기</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+          <t>딥페이크·AI 사칭으로 대규모 부정 송금 금전 사기 실현</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -8141,42 +8256,43 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>보조</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L15" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] CaptiveCrunch — Midnight Blizzard 하위 그룹의 AI 보조 악성코드 개발(2026-07) (AII-023)</t>
-        </is>
+      <c r="M15" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>피싱 내성 MFA·조건부 접근과 사용자 신고·교육으로 대량 미끼에 대응(NIST AT-2(3))</t>
+          <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-02) (AII-002)</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>고액 송금에 다채널·사전 등록 경로 확인과 역할 분리·한도를 적용(NIST AT-2(3)·IA-2)</t>
         </is>
       </c>
     </row>
@@ -8186,22 +8302,22 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>[IM] 영향·규모화</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>AIA-IM-01</t>
+          <t>AIA-IA-02.1</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>딥페이크·AI 사칭 기반 금전 사기</t>
+          <t>영상 딥페이크 사칭</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>딥페이크·AI 사칭으로 대규모 부정 송금 금전 사기 실현</t>
+          <t>영상 딥페이크 사칭으로 화상회의·면접 신뢰 악용</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -8209,42 +8325,43 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>보조</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="M16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-02) (AII-002)</t>
         </is>
       </c>
-      <c r="N16" s="9" t="inlineStr">
-        <is>
-          <t>고액 송금에 다채널·사전 등록 경로 확인과 역할 분리·한도를 적용(NIST AT-2(3)·IA-2)</t>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>고위험 요청에 다채널·사전 등록 경로 확인을 의무화하고 사용자 교육(NIST AT-2(3)·IA-2)</t>
         </is>
       </c>
     </row>
@@ -8259,60 +8376,61 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1</t>
+          <t>AIA-IA-01.1</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>영상 딥페이크 사칭</t>
+          <t>AI 생성 대량 피싱·미끼</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>영상 딥페이크 사칭으로 화상회의·면접 신뢰 악용</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
           <t>보조</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-02) (AII-002)</t>
-        </is>
+      <c r="M17" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>고위험 요청에 다채널·사전 등록 경로 확인을 의무화하고 사용자 교육(NIST AT-2(3)·IA-2)</t>
+          <t>[실제 사고] CaptiveCrunch — Midnight Blizzard 하위 그룹의 AI 보조 악성코드 개발(2026-07) (AII-023)</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>피싱 내성 MFA·조건부 접근과 사용자 신고·교육으로 대량 미끼에 대응(NIST AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -8322,65 +8440,66 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-03.2</t>
+          <t>AIA-RT-02</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>AI 생성 와이퍼·파괴 스크립트</t>
+          <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
+          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
+          <t>반자율</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="M18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] 2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)(2026-01) (AII-006)</t>
-        </is>
-      </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>행위 기반 탐지·실행 통제와 오프라인·불변 백업으로 복구력을 확보(NIST SI-7·CP-9)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>공격면을 줄이고 관리 인터페이스를 경계 밖에 노출하지 않음(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -8390,65 +8509,66 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-02</t>
+          <t>AIA-IA-02.2</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>실행 중 AI 명령 동적 생성 악성코드</t>
+          <t>음성 딥페이크 사칭</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
+          <t>증폭</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="M19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
-        </is>
-      </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스 egress 통제와 행위 기반 실행 탐지로 동적 명령 생성에 대응(NIST SI-3·SI-4)</t>
+          <t>[실제 사고] Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)(2023-09) (AII-011)</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>음성에 의존하지 않는 본인확인(콜백·사전 등록·피싱 내성 MFA)과 헬프데스크 절차 강화(NIST IA-2·AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -8458,65 +8578,66 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-01</t>
+          <t>AIA-VE-03.2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
+          <t>AI 생성 와이퍼·파괴 스크립트</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
+          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
           <t>보조</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
+          <t>증폭</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="M20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
-        </is>
-      </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스 egress 가시성·허용 목록으로 비인가 AI 트래픽을 통제(NIST SC-7)</t>
+          <t>[실제 사고] 2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)(2026-01) (AII-006)</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>행위 기반 탐지·실행 통제와 오프라인·불변 백업으로 복구력을 확보(NIST SI-7·CP-9)</t>
         </is>
       </c>
     </row>
@@ -8526,65 +8647,66 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1</t>
+          <t>AIA-CC-04</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>AI 자율 취약점 발굴(버그 헌팅)</t>
+          <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>AI 에이전트의 자율 취약점 발굴(미공개 취약점 자동 탐색)</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>완전자율</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>실사용</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 6건·성숙도 실사용]</t>
-        </is>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>실증</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>자체 AI 보조 취약점 발굴·퍼징으로 공격자보다 먼저 찾고(NIST SA-11), 신속 패치·무결성 검증으로 노출 구간을 좁힘(NIST SI-7·RA-5)</t>
+          <t>[실제 사고] Amazon Q Developer 확장에 삭제 지시 주입(2025-07) (AII-003)</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>규칙·설정 파일을 변경 통제·리뷰 대상에 포함하고 비가시 문자를 정규화·차단(NIST SA-15·CM-7)</t>
         </is>
       </c>
     </row>
@@ -8594,65 +8716,66 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-02</t>
+          <t>AIA-RT-03</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>AI 익스플로잇 자동 생성·개발</t>
+          <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>AI 익스플로잇 자동 생성으로 익스플로잇 개발 병목 제거</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
+          <t>증폭</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9" t="inlineStr">
-        <is>
-          <t>[위협인텔] AI로 개발한 0-day 익스플로잇을 준비한 범죄 조직의 대량 악용 계획(GTIG 사전 차단)(2026-05) (AII-030)</t>
-        </is>
+      <c r="M22" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>신속 패치·가상 패치와 무결성 검증으로 즉시 무기화에 대응하고(NIST SI-7), 자체 익스플로잇 가능성 평가로 우선순위화(NIST SA-11·RA-5)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>공개 취약점의 신속 패치·완화를 우선순위화해 n-day 노출 구간을 좁힘(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -8662,22 +8785,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[AO] 자율 실행·확산</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-02</t>
+          <t>AIA-AO-06</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
+          <t>통제를 벗어난 자율 에이전트의 자발적 침해(사람 공격자 없음)</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
+          <t>통제를 벗어난 자율 에이전트가 사람 지시 없이 실제 인프라 침해</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -8685,42 +8808,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>반자율</t>
-        </is>
-      </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>완전자율</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L23" s="8" t="n">
+      <c r="M23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
-        </is>
-      </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>공격면을 줄이고 관리 인터페이스를 경계 밖에 노출하지 않음(NIST SC-7)</t>
+          <t>[실제 사고] 자율 평가 에이전트의 평가 경계 이탈과 Hugging Face 인프라 침해(2026-07) (AII-010)</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트에 강한 샌드박스·최소 권한·명시적 승인 경계를 두고 이탈 시 자동 차단·격리(NIST AC-6·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8730,22 +8854,22 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-02.2</t>
+          <t>AIA-CC-02</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>음성 딥페이크 사칭</t>
+          <t>실행 중 AI 명령 동적 생성 악성코드</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
+          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -8753,42 +8877,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>보조</t>
-        </is>
-      </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L24" s="8" t="n">
+      <c r="M24" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)(2023-09) (AII-011)</t>
-        </is>
-      </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>음성에 의존하지 않는 본인확인(콜백·사전 등록·피싱 내성 MFA)과 헬프데스크 절차 강화(NIST IA-2·AT-2(3))</t>
+          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>AI 서비스 egress 통제와 행위 기반 실행 탐지로 동적 명령 생성에 대응(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8803,17 +8928,17 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-04</t>
+          <t>AIA-CC-01</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
+          <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
+          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -8821,42 +8946,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>보조</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>실증</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="n">
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] Amazon Q Developer 확장에 삭제 지시 주입(2025-07) (AII-003)</t>
-        </is>
-      </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>규칙·설정 파일을 변경 통제·리뷰 대상에 포함하고 비가시 문자를 정규화·차단(NIST SA-15·CM-7)</t>
+          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t>AI 서비스 egress 가시성·허용 목록으로 비인가 AI 트래픽을 통제(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -8866,22 +8992,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-03</t>
+          <t>AIA-IA-04</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
+          <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
+          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -8889,42 +9015,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>증강</t>
-        </is>
-      </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="n">
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>실증</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
-        </is>
-      </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>공개 취약점의 신속 패치·완화를 우선순위화해 n-day 노출 구간을 좁힘(NIST RA-5)</t>
+          <t>[실제 사고] Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)(2023-11) (AII-012)</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>컴퓨터 사용 에이전트의 실행 권한·승인 경계를 두고 미끼 유형을 교육(NIST AT-2(3)·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8934,22 +9061,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>[AO] 자율 실행·확산</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-06</t>
+          <t>AIA-CC-03</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>통제를 벗어난 자율 에이전트의 자발적 침해(사람 공격자 없음)</t>
+          <t>AI 기반 방어 회피·난독화</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>통제를 벗어난 자율 에이전트가 사람 지시 없이 실제 인프라 침해</t>
+          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -8957,42 +9084,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>완전자율</t>
-        </is>
-      </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] 자율 평가 에이전트의 평가 경계 이탈과 Hugging Face 인프라 침해(2026-07) (AII-010)</t>
-        </is>
+          <t>증폭</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>실증</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>자율 에이전트에 강한 샌드박스·최소 권한·명시적 승인 경계를 두고 이탈 시 자동 차단·격리(NIST AC-6·SI-4)</t>
+          <t>[ATLAS 사례 20건·성숙도 실증]</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t>시그니처 의존을 줄이고 행위 기반·무결성 검증을 강화, 탐지 모델에 적대적 견고성을 반영(NIST SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -9002,22 +9130,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-04</t>
+          <t>AIA-RD-02</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
+          <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
+          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -9025,42 +9153,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>보조</t>
-        </is>
-      </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="9" t="inlineStr">
-        <is>
-          <t>[실제 사고] Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)(2023-11) (AII-012)</t>
-        </is>
+          <t>증폭</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>컴퓨터 사용 에이전트의 실행 권한·승인 경계를 두고 미끼 유형을 교육(NIST AT-2(3)·SI-4)</t>
+          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t>시그니처가 아닌 행위·맥락 기반 탐지로 매번 달라지는 산출물에 대응하고 최소 권한을 적용(NIST SI-4·PM-16)</t>
         </is>
       </c>
     </row>
@@ -9070,22 +9199,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-03</t>
+          <t>AIA-RT-01.1</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 방어 회피·난독화</t>
+          <t>AI 기반 공개정보 수집·인물 프로파일링</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
+          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -9093,42 +9222,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>증강</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>실증</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 20건·성숙도 실증]</t>
-        </is>
-      </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>시그니처 의존을 줄이고 행위 기반·무결성 검증을 강화, 탐지 모델에 적대적 견고성을 반영(NIST SI-4·SI-7)</t>
+          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>핵심 인력·과제의 공개 노출 범위를 정하고 프로필·발표·채용 공고의 민감 정보를 최소화(NIST PM-16)</t>
         </is>
       </c>
     </row>
@@ -9143,17 +9273,17 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-02</t>
+          <t>AIA-RD-01.1</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
+          <t>다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
+          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -9161,42 +9291,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>증강</t>
-        </is>
-      </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="M30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
-        </is>
-      </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>시그니처가 아닌 행위·맥락 기반 탐지로 매번 달라지는 산출물에 대응하고 최소 권한을 적용(NIST SI-4·PM-16)</t>
+          <t>[ATLAS 사례 13건·성숙도 실사용]</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>공세 LLM이 만들어내는 산출물(피싱·악성코드)의 탐지·대응 역량을 강화해 역량 확보 자체보다 '사용 시점'을 막음(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9211,17 +9342,17 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-01.1</t>
+          <t>AIA-RT-01.2</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 공개정보 수집·인물 프로파일링</t>
+          <t>AI 기반 표적 환경·관계 분석</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
+          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -9229,42 +9360,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>증강</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>실사용</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>실증</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
-        </is>
-      </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>핵심 인력·과제의 공개 노출 범위를 정하고 프로필·발표·채용 공고의 민감 정보를 최소화(NIST PM-16)</t>
+          <t>[ATLAS 사례 8건·성숙도 실증]</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>조직 구조·거래 관계의 불필요한 공개를 줄이고 고위험 역할의 공개 노출을 관리(NIST PM-16)</t>
         </is>
       </c>
     </row>
@@ -9274,22 +9406,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[IM] 영향·규모화</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-01.1</t>
+          <t>AIA-IM-04</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>다크 LLM·탈옥 모델 확보</t>
+          <t>AI 활용 공격의 규모화·대량화</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
+          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -9297,42 +9429,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>보조</t>
-        </is>
-      </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
+          <t>증폭</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="M32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 13건·성숙도 실사용]</t>
-        </is>
-      </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>공세 LLM이 만들어내는 산출물(피싱·악성코드)의 탐지·대응 역량을 강화해 역량 확보 자체보다 '사용 시점'을 막음(NIST SI-4)</t>
+          <t>[ATLAS 사례 7건·성숙도 실사용]</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>탐지·대응 자동화로 대량 캠페인에 대응하고 위협 인텔로 우선순위화(NIST SI-4·PM-16)</t>
         </is>
       </c>
     </row>
@@ -9342,22 +9475,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-01.2</t>
+          <t>AIA-IA-01.2</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 표적 환경·관계 분석</t>
+          <t>AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
+          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -9365,42 +9498,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>증강</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>실증</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 8건·성숙도 실증]</t>
-        </is>
-      </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>조직 구조·거래 관계의 불필요한 공개를 줄이고 고위험 역할의 공개 노출을 관리(NIST PM-16)</t>
+          <t>[ATLAS 사례 6건·성숙도 실사용]</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>고액·고위험 요청에 다채널 확인과 역할 기반 교육을 적용(NIST AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -9410,22 +9544,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>[IM] 영향·규모화</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>AIA-IM-04</t>
+          <t>AIA-VE-01.1</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>AI 활용 공격의 규모화·대량화</t>
+          <t>AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
+          <t>AI 에이전트의 자율 취약점 발굴(미공개 취약점 자동 탐색)</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -9433,42 +9567,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>반자율</t>
-        </is>
-      </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>완전자율</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="M34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 7건·성숙도 실사용]</t>
-        </is>
-      </c>
       <c r="N34" s="9" t="inlineStr">
         <is>
-          <t>탐지·대응 자동화로 대량 캠페인에 대응하고 위협 인텔로 우선순위화(NIST SI-4·PM-16)</t>
+          <t>[ATLAS 사례 6건·성숙도 실사용]</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>자체 AI 보조 취약점 발굴·퍼징으로 공격자보다 먼저 찾고(NIST SA-11), 신속 패치·무결성 검증으로 노출 구간을 좁힘(NIST SI-7·RA-5)</t>
         </is>
       </c>
     </row>
@@ -9478,22 +9613,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-01.2</t>
+          <t>AIA-RD-03</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 표적 스피어피싱·BEC</t>
+          <t>공격 인프라·AI 서비스 프록시 확보</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
+          <t>탈취 계정·서버리스로 AI 서비스 익명 경유 공격 인프라 확보</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -9501,42 +9636,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>증강</t>
-        </is>
-      </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>실사용</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>실증</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 6건·성숙도 실사용]</t>
-        </is>
-      </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>고액·고위험 요청에 다채널 확인과 역할 기반 교육을 적용(NIST AT-2(3))</t>
+          <t>[ATLAS 사례 6건·성숙도 실증]</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
+        <is>
+          <t>AI 서비스 egress 가시성을 확보하고 비인가 AI 트래픽·신규 인프라 접속을 통제(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -9546,22 +9682,22 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-03</t>
+          <t>AIA-VE-01.2</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>공격 인프라·AI 서비스 프록시 확보</t>
+          <t>AI 보조 코드 감사·퍼징</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>탈취 계정·서버리스로 AI 서비스 익명 경유 공격 인프라 확보</t>
+          <t>AI 보조 코드 감사·퍼징으로 취약점 발견 속도 증폭</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -9569,42 +9705,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>보조</t>
-        </is>
-      </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
+          <t>증강</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
           <t>증폭</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>실증</t>
         </is>
       </c>
-      <c r="L36" s="8" t="n">
+      <c r="M36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 6건·성숙도 실증]</t>
-        </is>
-      </c>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스 egress 가시성을 확보하고 비인가 AI 트래픽·신규 인프라 접속을 통제(NIST SC-7)</t>
+          <t>[ATLAS 사례 5건·성숙도 실증]</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t>개발 단계에 AI 보조 테스트를 통합해 선제 발견하고(NIST SA-11·SA-15), 취약 구성요소를 신속 교체(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -9619,17 +9756,17 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-01.2</t>
+          <t>AIA-VE-02</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>AI 보조 코드 감사·퍼징</t>
+          <t>AI 익스플로잇 자동 생성·개발</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>AI 보조 코드 감사·퍼징으로 취약점 발견 속도 증폭</t>
+          <t>AI 익스플로잇 자동 생성으로 익스플로잇 개발 병목 제거</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -9637,42 +9774,43 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>증강</t>
-        </is>
-      </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="n">
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="9" t="inlineStr">
-        <is>
-          <t>[ATLAS 사례 5건·성숙도 실증]</t>
-        </is>
-      </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>개발 단계에 AI 보조 테스트를 통합해 선제 발견하고(NIST SA-11·SA-15), 취약 구성요소를 신속 교체(NIST RA-5)</t>
+          <t>[위협인텔] AI로 개발한 0-day 익스플로잇을 준비한 범죄 조직의 대량 악용 계획(GTIG 사전 차단)(2026-05) (AII-030)</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t>신속 패치·가상 패치와 무결성 검증으로 즉시 무기화에 대응하고(NIST SI-7), 자체 익스플로잇 가능성 평가로 우선순위화(NIST SA-11·RA-5)</t>
         </is>
       </c>
     </row>
@@ -9705,11 +9843,7 @@
           <t>낮음</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
+      <c r="G38" s="8" t="inlineStr"/>
       <c r="H38" s="8" t="inlineStr">
         <is>
           <t>하</t>
@@ -9717,35 +9851,40 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
           <t>보조</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="K38" s="8" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t>연구시연</t>
         </is>
       </c>
-      <c r="L38" s="8" t="n">
+      <c r="M38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="9" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>[ATLAS 사례 7건·성숙도 연구시연]</t>
         </is>
       </c>
-      <c r="N38" s="9" t="inlineStr">
+      <c r="O38" s="9" t="inlineStr">
         <is>
           <t>자사 모델·데이터의 유출·추출을 통제해 공세 파생 모델의 재료가 되지 않게 함(NIST PM-16)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N38"/>
+  <autoFilter ref="A4:O38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9842,22 +9981,22 @@
           <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드 [3]</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회 [2]</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>AIA-AO-01 단일 자율 공격 에이전트 실행 [6]</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>AIA-CC-01 AI 서비스 API·웹 인터페이스 경유 은닉 C2 [1]</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 [4]</t>
         </is>
@@ -9874,27 +10013,27 @@
           <t>AIA-RD-01.1 다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>AIA-VE-03.2 AI 생성 와이퍼·파괴 스크립트 [1]</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>AIA-IA-01.1 AI 생성 대량 피싱·미끼 [2]</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>AIA-IA-02.1 영상 딥페이크 사칭 [1]</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>AIA-AO-02 다중 에이전트 공격 조율 [3]</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>AIA-CC-02 실행 중 AI 명령 동적 생성 악성코드 [1]</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기 [1]</t>
         </is>
@@ -9911,17 +10050,17 @@
           <t>AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>AIA-VE-01.1 AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>AIA-IA-02.1 영상 딥페이크 사칭 [1]</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>AIA-IA-01.1 AI 생성 대량 피싱·미끼 [2]</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 [3]</t>
         </is>
@@ -9948,9 +10087,9 @@
           <t>AIA-RD-03 공격 인프라·AI 서비스 프록시 확보</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>AIA-VE-02 AI 익스플로잇 자동 생성·개발</t>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>AIA-VE-01.2 AI 보조 코드 감사·퍼징</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -9958,7 +10097,7 @@
           <t>AIA-IA-02.2 음성 딥페이크 사칭 [1]</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 [3]</t>
         </is>
@@ -9977,7 +10116,7 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>AIA-VE-01.2 AI 보조 코드 감사·퍼징</t>
+          <t>AIA-VE-02 AI 익스플로잇 자동 생성·개발</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
@@ -9985,7 +10124,7 @@
           <t>AIA-IA-04 AI 미끼·ClickFix·크래프트 링크로 실행 유도 [1]</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용 [2]</t>
         </is>
@@ -9997,7 +10136,7 @@
           <t>AIA-IA-01.2 AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용 [2]</t>
         </is>
@@ -10021,7 +10160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR38"/>
+  <dimension ref="A1:AS38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10053,21 +10192,22 @@
     <col width="7" customWidth="1" min="27" max="27"/>
     <col width="8" customWidth="1" min="28" max="28"/>
     <col width="7" customWidth="1" min="29" max="29"/>
-    <col width="40" customWidth="1" min="30" max="30"/>
-    <col width="46" customWidth="1" min="31" max="31"/>
-    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="7" customWidth="1" min="30" max="30"/>
+    <col width="40" customWidth="1" min="31" max="31"/>
+    <col width="46" customWidth="1" min="32" max="32"/>
     <col width="7" customWidth="1" min="33" max="33"/>
     <col width="7" customWidth="1" min="34" max="34"/>
     <col width="7" customWidth="1" min="35" max="35"/>
     <col width="7" customWidth="1" min="36" max="36"/>
     <col width="7" customWidth="1" min="37" max="37"/>
     <col width="7" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="26" customWidth="1" min="40" max="40"/>
-    <col width="24" customWidth="1" min="41" max="41"/>
-    <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="60" customWidth="1" min="43" max="43"/>
-    <col width="22" customWidth="1" min="44" max="44"/>
+    <col width="7" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="26" customWidth="1" min="41" max="41"/>
+    <col width="24" customWidth="1" min="42" max="42"/>
+    <col width="26" customWidth="1" min="43" max="43"/>
+    <col width="60" customWidth="1" min="44" max="44"/>
+    <col width="22" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10105,12 +10245,12 @@
           <t>위험 평가</t>
         </is>
       </c>
-      <c r="AF3" s="25" t="inlineStr">
+      <c r="AG3" s="25" t="inlineStr">
         <is>
           <t>실제 근거</t>
         </is>
       </c>
-      <c r="AP3" s="26" t="inlineStr">
+      <c r="AQ3" s="26" t="inlineStr">
         <is>
           <t>대응 기준·참고 문헌</t>
         </is>
@@ -10259,80 +10399,85 @@
       </c>
       <c r="AC4" s="7" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD4" s="7" t="inlineStr">
+        <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="AD4" s="7" t="inlineStr">
+      <c r="AE4" s="7" t="inlineStr">
         <is>
           <t>발생가능성 근거(자동 산정)</t>
         </is>
       </c>
-      <c r="AE4" s="7" t="inlineStr">
+      <c r="AF4" s="7" t="inlineStr">
         <is>
           <t>심각도 근거</t>
         </is>
       </c>
-      <c r="AF4" s="7" t="inlineStr">
+      <c r="AG4" s="7" t="inlineStr">
         <is>
           <t>실제 사고 수</t>
         </is>
       </c>
-      <c r="AG4" s="7" t="inlineStr">
+      <c r="AH4" s="7" t="inlineStr">
         <is>
           <t>최근(2025~)</t>
         </is>
       </c>
-      <c r="AH4" s="7" t="inlineStr">
+      <c r="AI4" s="7" t="inlineStr">
         <is>
           <t>AI 활용 확인</t>
         </is>
       </c>
-      <c r="AI4" s="7" t="inlineStr">
+      <c r="AJ4" s="7" t="inlineStr">
         <is>
           <t>AI 활용 추정</t>
         </is>
       </c>
-      <c r="AJ4" s="7" t="inlineStr">
+      <c r="AK4" s="7" t="inlineStr">
         <is>
           <t>위협인텔</t>
         </is>
       </c>
-      <c r="AK4" s="7" t="inlineStr">
+      <c r="AL4" s="7" t="inlineStr">
         <is>
           <t>실증·연구</t>
         </is>
       </c>
-      <c r="AL4" s="7" t="inlineStr">
+      <c r="AM4" s="7" t="inlineStr">
         <is>
           <t>ATLAS 사례 수</t>
         </is>
       </c>
-      <c r="AM4" s="7" t="inlineStr">
+      <c r="AN4" s="7" t="inlineStr">
         <is>
           <t>근거 수준</t>
         </is>
       </c>
-      <c r="AN4" s="7" t="inlineStr">
+      <c r="AO4" s="7" t="inlineStr">
         <is>
           <t>관련 사례 ID</t>
         </is>
       </c>
-      <c r="AO4" s="7" t="inlineStr">
+      <c r="AP4" s="7" t="inlineStr">
         <is>
           <t>주요 영향(실제 사고)</t>
         </is>
       </c>
-      <c r="AP4" s="7" t="inlineStr">
+      <c r="AQ4" s="7" t="inlineStr">
         <is>
           <t>NIST SP 800-53</t>
         </is>
       </c>
-      <c r="AQ4" s="7" t="inlineStr">
+      <c r="AR4" s="7" t="inlineStr">
         <is>
           <t>탐지·대응 포인트</t>
         </is>
       </c>
-      <c r="AR4" s="7" t="inlineStr">
+      <c r="AS4" s="7" t="inlineStr">
         <is>
           <t>참고 문헌</t>
         </is>
@@ -10466,21 +10611,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC5" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD5" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 15 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC5" s="9" t="inlineStr"/>
+      <c r="AD5" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="AE5" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 15(참고)</t>
+        </is>
+      </c>
+      <c r="AF5" s="9" t="inlineStr">
+        <is>
           <t>단독 피해는 없으나 AI가 공개정보에서 핵심 인력·관계·약점을 대규모로 추려 후속 사회공학·침투의 표적을 고르는 토대가 됨</t>
         </is>
-      </c>
-      <c r="AF5" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG5" s="9" t="n">
         <v>0</v>
@@ -10498,23 +10641,26 @@
         <v>0</v>
       </c>
       <c r="AL5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AM5" s="27" t="inlineStr">
+      <c r="AN5" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN5" s="9" t="inlineStr"/>
       <c r="AO5" s="9" t="inlineStr"/>
-      <c r="AP5" s="9" t="inlineStr">
+      <c r="AP5" s="9" t="inlineStr"/>
+      <c r="AQ5" s="9" t="inlineStr">
         <is>
           <t>PM-16 Threat Awareness Program
 AT-2(3) Social Engineering and Mining
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ5" s="9" t="inlineStr">
+      <c r="AR5" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 자사·임직원 대상 공개정보 노출과 비정상 수집 정황(대량 조회·스크레이핑)을 위협 인텔리전스로 점검(NIST PM-16·SI-4)
@@ -10525,7 +10671,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR5" s="9" t="inlineStr">
+      <c r="AS5" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -10652,21 +10798,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC6" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD6" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 8 · 역량 성숙도 실증</t>
-        </is>
+      <c r="AC6" s="9" t="inlineStr"/>
+      <c r="AD6" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="AE6" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실증 · ATLAS 사례 8(참고)</t>
+        </is>
+      </c>
+      <c r="AF6" s="9" t="inlineStr">
+        <is>
           <t>수집한 조직 구조·거래 관계를 AI가 엮어 사칭 시나리오·표적 우선순위를 만드는 조건 — 피해는 사회공학·침투에서 커짐</t>
         </is>
-      </c>
-      <c r="AF6" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG6" s="9" t="n">
         <v>0</v>
@@ -10684,22 +10828,25 @@
         <v>0</v>
       </c>
       <c r="AL6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AM6" s="28" t="inlineStr">
+      <c r="AN6" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
       </c>
-      <c r="AN6" s="9" t="inlineStr"/>
       <c r="AO6" s="9" t="inlineStr"/>
-      <c r="AP6" s="9" t="inlineStr">
+      <c r="AP6" s="9" t="inlineStr"/>
+      <c r="AQ6" s="9" t="inlineStr">
         <is>
           <t>PM-16 Threat Awareness Program
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ6" s="9" t="inlineStr">
+      <c r="AR6" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 공개된 조직·거래 정보의 노출 범위와 사칭에 쓰일 수 있는 맥락을 주기적으로 점검(NIST PM-16·SI-4)
@@ -10710,7 +10857,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR6" s="9" t="inlineStr">
+      <c r="AS6" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -10837,21 +10984,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC7" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD7" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 7 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC7" s="9" t="inlineStr"/>
+      <c r="AD7" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="AE7" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 7(참고)</t>
+        </is>
+      </c>
+      <c r="AF7" s="9" t="inlineStr">
+        <is>
           <t>AI 에이전트가 FOFA·인터넷 스캔으로 노출 서비스를 사람보다 빠르게 열거해 공격 가능 진입점 목록을 자동 생성(Hermes 사례)</t>
         </is>
-      </c>
-      <c r="AF7" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="AG7" s="9" t="n">
         <v>1</v>
@@ -10860,7 +11005,7 @@
         <v>1</v>
       </c>
       <c r="AI7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="9" t="n">
         <v>0</v>
@@ -10869,31 +11014,34 @@
         <v>0</v>
       </c>
       <c r="AL7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AM7" s="29" t="inlineStr">
+      <c r="AN7" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN7" s="9" t="inlineStr">
+      <c r="AO7" s="9" t="inlineStr">
         <is>
           <t>AII-027</t>
         </is>
       </c>
-      <c r="AO7" s="9" t="inlineStr">
+      <c r="AP7" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AP7" s="9" t="inlineStr">
+      <c r="AQ7" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
 SC-7 Boundary Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ7" s="9" t="inlineStr">
+      <c r="AR7" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 외부 노출 자산을 지속 식별하고 비정상적으로 빠른 열거·탐침 패턴을 모니터링(NIST RA-5·SI-4)
@@ -10904,7 +11052,7 @@
 - 참고: Unit 42 〈Hermes Agent〉</t>
         </is>
       </c>
-      <c r="AR7" s="9" t="inlineStr">
+      <c r="AS7" s="9" t="inlineStr">
         <is>
           <t>Unit 42 〈Hermes Agent〉</t>
         </is>
@@ -11030,21 +11178,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC8" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD8" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 5 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC8" s="9" t="inlineStr"/>
+      <c r="AD8" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="AE8" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 5(참고)</t>
+        </is>
+      </c>
+      <c r="AF8" s="9" t="inlineStr">
+        <is>
           <t>AI가 GitHub 등에서 최신 CVE PoC를 자동으로 찾아 공격에 쓸 수 있는 형태로 분류 — 공개 즉시 악용되는 빠른 n-day를 가속(Hermes 사례)</t>
         </is>
-      </c>
-      <c r="AF8" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="AG8" s="9" t="n">
         <v>1</v>
@@ -11053,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="AI8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="9" t="n">
         <v>0</v>
@@ -11062,30 +11208,33 @@
         <v>0</v>
       </c>
       <c r="AL8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AM8" s="29" t="inlineStr">
+      <c r="AN8" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN8" s="9" t="inlineStr">
+      <c r="AO8" s="9" t="inlineStr">
         <is>
           <t>AII-027</t>
         </is>
       </c>
-      <c r="AO8" s="9" t="inlineStr">
+      <c r="AP8" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AP8" s="9" t="inlineStr">
+      <c r="AQ8" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
 PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ8" s="9" t="inlineStr">
+      <c r="AR8" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 자사 자산의 공개 취약점·PoC 공개 동향을 신속 수집해 노출 여부를 대조(NIST RA-5)
@@ -11096,7 +11245,7 @@
 - 참고: Unit 42 〈Hermes Agent〉</t>
         </is>
       </c>
-      <c r="AR8" s="9" t="inlineStr">
+      <c r="AS8" s="9" t="inlineStr">
         <is>
           <t>Unit 42 〈Hermes Agent〉</t>
         </is>
@@ -11221,21 +11370,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC9" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AD9" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 13 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC9" s="9" t="inlineStr"/>
+      <c r="AD9" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="AE9" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 13(참고)</t>
+        </is>
+      </c>
+      <c r="AF9" s="9" t="inlineStr">
+        <is>
           <t>가드레일 없는 공세 특화 LLM이 지하 시장에서 유통되면 역량이 낮은 공격자도 피싱·악성코드 제작에 접근 — 피해는 후속 단계에서 발생</t>
         </is>
-      </c>
-      <c r="AF9" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG9" s="9" t="n">
         <v>0</v>
@@ -11253,22 +11400,25 @@
         <v>0</v>
       </c>
       <c r="AL9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AM9" s="27" t="inlineStr">
+      <c r="AN9" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN9" s="9" t="inlineStr"/>
       <c r="AO9" s="9" t="inlineStr"/>
-      <c r="AP9" s="9" t="inlineStr">
+      <c r="AP9" s="9" t="inlineStr"/>
+      <c r="AQ9" s="9" t="inlineStr">
         <is>
           <t>PM-16 Threat Awareness Program
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ9" s="9" t="inlineStr">
+      <c r="AR9" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 지하 시장·공세 LLM 동향을 위협 인텔로 수집하고 자사 대상 악용 징후를 모니터링(NIST PM-16·SI-4)
@@ -11277,7 +11427,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR9" s="9" t="inlineStr">
+      <c r="AS9" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -11381,7 +11531,7 @@
       <c r="Y10" s="9" t="inlineStr"/>
       <c r="Z10" s="8" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="AA10" s="8" t="inlineStr">
@@ -11394,21 +11544,19 @@
           <t>낮음</t>
         </is>
       </c>
-      <c r="AC10" s="8" t="n">
+      <c r="AC10" s="9" t="inlineStr"/>
+      <c r="AD10" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="AD10" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 7 · 역량 성숙도 연구시연</t>
-        </is>
-      </c>
       <c r="AE10" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 연구시연 · ATLAS 사례 7(참고)</t>
+        </is>
+      </c>
+      <c r="AF10" s="9" t="inlineStr">
+        <is>
           <t>상용 모델을 증류·파인튜닝해 가드레일을 제거한 공세 모델을 만드는 정황 — 아직 연구·시연 수준이라 직접 피해는 제한적</t>
         </is>
-      </c>
-      <c r="AF10" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG10" s="9" t="n">
         <v>0</v>
@@ -11426,21 +11574,24 @@
         <v>0</v>
       </c>
       <c r="AL10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AM10" s="28" t="inlineStr">
-        <is>
-          <t>실증·공개 PoC</t>
-        </is>
-      </c>
-      <c r="AN10" s="9" t="inlineStr"/>
+      <c r="AN10" s="30" t="inlineStr">
+        <is>
+          <t>이론·연구 시연</t>
+        </is>
+      </c>
       <c r="AO10" s="9" t="inlineStr"/>
-      <c r="AP10" s="9" t="inlineStr">
+      <c r="AP10" s="9" t="inlineStr"/>
+      <c r="AQ10" s="9" t="inlineStr">
         <is>
           <t>PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ10" s="9" t="inlineStr">
+      <c r="AR10" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 모델 가중치·데이터 유출과 비정상 대량 질의(증류 정황)를 자사 AI 자산에서 모니터링(NIST PM-16)
@@ -11449,7 +11600,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR10" s="9" t="inlineStr">
+      <c r="AS10" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -11576,21 +11727,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC11" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD11" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 15 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC11" s="9" t="inlineStr"/>
+      <c r="AD11" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="AE11" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 15(참고)</t>
+        </is>
+      </c>
+      <c r="AF11" s="9" t="inlineStr">
+        <is>
           <t>AI가 스캐너·셸 명령·HTTP 탐침을 즉석에서 생성해 공격 준비 시간을 단축 — 단독 피해는 없으나 침투·실행을 가속</t>
         </is>
-      </c>
-      <c r="AF11" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG11" s="9" t="n">
         <v>0</v>
@@ -11608,23 +11757,26 @@
         <v>0</v>
       </c>
       <c r="AL11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AM11" s="27" t="inlineStr">
+      <c r="AN11" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN11" s="9" t="inlineStr"/>
       <c r="AO11" s="9" t="inlineStr"/>
-      <c r="AP11" s="9" t="inlineStr">
+      <c r="AP11" s="9" t="inlineStr"/>
+      <c r="AQ11" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring
 PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ11" s="9" t="inlineStr">
+      <c r="AR11" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 실행 단계에서 생성형 도구의 산출물(비정형 스크립트·명령)을 행위 기반으로 탐지(NIST SI-3·SI-4)
@@ -11633,7 +11785,7 @@
 - 참고: Unit 42 〈Hermes Agent〉</t>
         </is>
       </c>
-      <c r="AR11" s="9" t="inlineStr">
+      <c r="AS11" s="9" t="inlineStr">
         <is>
           <t>Unit 42 〈Hermes Agent〉</t>
         </is>
@@ -11765,21 +11917,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC12" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD12" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실증</t>
-        </is>
+      <c r="AC12" s="9" t="inlineStr"/>
+      <c r="AD12" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="AE12" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실증 · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF12" s="9" t="inlineStr">
+        <is>
           <t>탈취·중계 계정으로 AI 서비스를 익명 경유하거나 서버리스 인프라를 확보해 공격의 출처·비용을 숨기는 조건</t>
         </is>
-      </c>
-      <c r="AF12" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG12" s="9" t="n">
         <v>0</v>
@@ -11797,22 +11947,25 @@
         <v>0</v>
       </c>
       <c r="AL12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM12" s="28" t="inlineStr">
+      <c r="AN12" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
       </c>
-      <c r="AN12" s="9" t="inlineStr"/>
       <c r="AO12" s="9" t="inlineStr"/>
-      <c r="AP12" s="9" t="inlineStr">
+      <c r="AP12" s="9" t="inlineStr"/>
+      <c r="AQ12" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ12" s="9" t="inlineStr">
+      <c r="AR12" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - AI 서비스·클라우드로의 비정상 egress와 신규·일회성 계정·도메인 사용을 모니터링(NIST SC-7·SI-4)
@@ -11821,7 +11974,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR12" s="9" t="inlineStr">
+      <c r="AS12" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -11931,29 +12084,31 @@
       </c>
       <c r="AA13" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB13" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
-        </is>
-      </c>
-      <c r="AC13" s="8" t="n">
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AB13" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="AC13" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD13" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 4 · 역량 성숙도 실사용</t>
-        </is>
-      </c>
       <c r="AE13" s="9" t="inlineStr">
         <is>
-          <t>스캐너·브라우저 자동화·침투 도구를 MCP로 엮은 공격 프레임워크(GTG-1002)·탈옥 모델 기반 자율 하네스(Hermes)는 한 번 만들면 사람 감독을 최소화한 반복 공격의 토대가 됨</t>
-        </is>
-      </c>
-      <c r="AF13" s="9" t="n">
-        <v>2</v>
+          <t>실제 사고 2건(확인 2·추정 0, 가중 2, 서로 다른 행위자·캠페인 2) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 4(참고)</t>
+        </is>
+      </c>
+      <c r="AF13" s="9" t="inlineStr">
+        <is>
+          <t>공세 AI 에이전트·하네스는 공격 수행 역량을 갖추는 단계로 단독 피해는 없음 — 역량 확보 조건(중)</t>
+        </is>
       </c>
       <c r="AG13" s="9" t="n">
         <v>2</v>
@@ -11962,7 +12117,7 @@
         <v>2</v>
       </c>
       <c r="AI13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ13" s="9" t="n">
         <v>0</v>
@@ -11971,31 +12126,34 @@
         <v>0</v>
       </c>
       <c r="AL13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AM13" s="29" t="inlineStr">
+      <c r="AN13" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN13" s="9" t="inlineStr">
+      <c r="AO13" s="9" t="inlineStr">
         <is>
           <t>AII-008, AII-027</t>
         </is>
       </c>
-      <c r="AO13" s="9" t="inlineStr">
+      <c r="AP13" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 2 · 내부 접근 확보 2</t>
         </is>
       </c>
-      <c r="AP13" s="9" t="inlineStr">
+      <c r="AQ13" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 PM-16 Threat Awareness Program
 SA-11 Developer Testing and Evaluation</t>
         </is>
       </c>
-      <c r="AQ13" s="9" t="inlineStr">
+      <c r="AR13" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - AI 에이전트 특유의 빠른·반복적 행위 시퀀스와 도구 연쇄 호출을 행위 기반으로 탐지(NIST SI-4·PM-16)
@@ -12004,7 +12162,7 @@
 - 참고: Anthropic 〈GTG-1002〉 · CrowdStrike 〈Agentic AI Campaigns〉</t>
         </is>
       </c>
-      <c r="AR13" s="9" t="inlineStr">
+      <c r="AS13" s="9" t="inlineStr">
         <is>
           <t>Anthropic 〈GTG-1002〉
 CrowdStrike 〈Agentic AI Campaigns〉</t>
@@ -12119,29 +12277,27 @@
       </c>
       <c r="AA14" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB14" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="AC14" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD14" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AB14" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC14" s="9" t="inlineStr"/>
+      <c r="AD14" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="AE14" s="9" t="inlineStr">
         <is>
-          <t>자율 에이전트가 사람 개입 없이 미공개 취약점을 찾아내므로(Big Sleep SQLite 0-day·XBOW RCE) 방어자가 패치 전 선제 발견·악용 양쪽에 노출됨 — 공격자가 쓰면 대규모 표적에서 0-day를 양산할 수 있음</t>
-        </is>
-      </c>
-      <c r="AF14" s="9" t="n">
-        <v>0</v>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF14" s="9" t="inlineStr">
+        <is>
+          <t>자율 취약점 발굴은 피해를 직접 일으키지 않고 후속 침투·악용의 조건이 됨 — 발굴 단계(중). 영향은 IA·AO·IM에서 실현</t>
+        </is>
       </c>
       <c r="AG14" s="9" t="n">
         <v>0</v>
@@ -12159,23 +12315,26 @@
         <v>0</v>
       </c>
       <c r="AL14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM14" s="27" t="inlineStr">
+      <c r="AN14" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN14" s="9" t="inlineStr"/>
       <c r="AO14" s="9" t="inlineStr"/>
-      <c r="AP14" s="9" t="inlineStr">
+      <c r="AP14" s="9" t="inlineStr"/>
+      <c r="AQ14" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
 SA-11 Developer Testing and Evaluation
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AQ14" s="9" t="inlineStr">
+      <c r="AR14" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 자사 자산에 대한 자동·대규모 취약점 탐색 정황과 비정상 접근 패턴을 모니터링(NIST RA-5)
@@ -12184,7 +12343,7 @@
 - 참고: The Record 〈Big Sleep〉 · AppSecSanta 〈AI Pentesting Agents 2026〉</t>
         </is>
       </c>
-      <c r="AR14" s="9" t="inlineStr">
+      <c r="AS14" s="9" t="inlineStr">
         <is>
           <t>The Record 〈Big Sleep〉
 AppSecSanta 〈AI Pentesting Agents 2026〉</t>
@@ -12310,21 +12469,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC15" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="AD15" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 5 · 역량 성숙도 실증</t>
-        </is>
+      <c r="AC15" s="9" t="inlineStr"/>
+      <c r="AD15" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="AE15" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실증 · ATLAS 사례 5(참고)</t>
+        </is>
+      </c>
+      <c r="AF15" s="9" t="inlineStr">
+        <is>
           <t>AI가 코드 리뷰·퍼징을 가속해 취약점 발견 속도를 높임 — 방어·공격 양용이며 단독 피해보다 발굴 단계를 증폭</t>
         </is>
-      </c>
-      <c r="AF15" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG15" s="9" t="n">
         <v>0</v>
@@ -12342,23 +12499,26 @@
         <v>0</v>
       </c>
       <c r="AL15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AM15" s="28" t="inlineStr">
+      <c r="AN15" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
       </c>
-      <c r="AN15" s="9" t="inlineStr"/>
       <c r="AO15" s="9" t="inlineStr"/>
-      <c r="AP15" s="9" t="inlineStr">
+      <c r="AP15" s="9" t="inlineStr"/>
+      <c r="AQ15" s="9" t="inlineStr">
         <is>
           <t>SA-11 Developer Testing and Evaluation
 SA-15 Development Process, Standards, and Tools
 RA-5 Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
-      <c r="AQ15" s="9" t="inlineStr">
+      <c r="AR15" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 의존성·자체 코드의 신규 취약점 공개와 악용 정황을 신속 대조(NIST RA-5)
@@ -12367,7 +12527,7 @@
 - 참고: AppSecSanta 〈AI Pentesting Agents 2026〉</t>
         </is>
       </c>
-      <c r="AR15" s="9" t="inlineStr">
+      <c r="AS15" s="9" t="inlineStr">
         <is>
           <t>AppSecSanta 〈AI Pentesting Agents 2026〉</t>
         </is>
@@ -12481,68 +12641,69 @@
       </c>
       <c r="AA16" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB16" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="AC16" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD16" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 1·추정 0 · 위협인텔 1 · 실증·연구 0 · ATLAS 사례 3 · 역량 성숙도 실사용</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AB16" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC16" s="9" t="inlineStr"/>
+      <c r="AD16" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="AE16" s="9" t="inlineStr">
         <is>
-          <t>위협 행위자가 AI로 개발한 것으로 판단되는 0-day 익스플로잇이 실제 사용된 첫 사례(GTIG)가 보고됨 — 익스플로잇 개발 병목이 사라지면 공개 취약점이 즉시 무기화됨</t>
-        </is>
-      </c>
-      <c r="AF16" s="9" t="n">
-        <v>0</v>
+          <t>실제 사고 0건(확인 1·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 1 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 3(참고)</t>
+        </is>
+      </c>
+      <c r="AF16" s="9" t="inlineStr">
+        <is>
+          <t>익스플로잇 자동 생성은 무기를 만드는 단계로 직접 피해는 없음 — 익스플로잇 생성 조건(중)</t>
+        </is>
       </c>
       <c r="AG16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AH16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AI16" s="9" t="n">
+      <c r="AJ16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ16" s="9" t="n">
+      <c r="AK16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AL16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AL16" s="9" t="n">
+      <c r="AM16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM16" s="27" t="inlineStr">
+      <c r="AN16" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN16" s="9" t="inlineStr">
+      <c r="AO16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">
 위협인텔: AII-030</t>
         </is>
       </c>
-      <c r="AO16" s="9" t="inlineStr"/>
-      <c r="AP16" s="9" t="inlineStr">
+      <c r="AP16" s="9" t="inlineStr"/>
+      <c r="AQ16" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
 SI-7 Software, Firmware, and Information Integrity
 SA-11 Developer Testing and Evaluation</t>
         </is>
       </c>
-      <c r="AQ16" s="9" t="inlineStr">
+      <c r="AR16" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 공개 직후 집중되는 익스플로잇 시도와 알려진 취약점의 비정상 악용을 모니터링(NIST RA-5)
@@ -12551,7 +12712,7 @@
 - 참고: securityonline 〈GTIG AI 0-day〉</t>
         </is>
       </c>
-      <c r="AR16" s="9" t="inlineStr">
+      <c r="AS16" s="9" t="inlineStr">
         <is>
           <t>securityonline 〈GTIG AI 0-day〉</t>
         </is>
@@ -12669,71 +12830,76 @@
       </c>
       <c r="AA17" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB17" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
-        </is>
-      </c>
-      <c r="AC17" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD17" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 3) · AI 활용 확인 2·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AB17" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="AC17" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD17" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="AE17" s="9" t="inlineStr">
         <is>
-          <t>금전 목적 행위자가 생성형 AI로 악성코드를 개발한 증거(BREEZE COMET)가 확인됨 — AI가 변종을 양산하면 시그니처 기반 탐지를 빠르게 무력화</t>
-        </is>
-      </c>
-      <c r="AF17" s="9" t="n">
-        <v>3</v>
+          <t>실제 사고 3건(확인 2·추정 1, 가중 2.5, 서로 다른 행위자·캠페인 3) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF17" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 악성코드는 공격 도구를 만드는 단계로 단독 피해는 없음 — 악성코드 생성 조건(중). 실제 피해는 배포·실행에서 발생</t>
+        </is>
       </c>
       <c r="AG17" s="9" t="n">
         <v>3</v>
       </c>
       <c r="AH17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AI17" s="9" t="n">
+      <c r="AJ17" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AJ17" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AK17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AL17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM17" s="29" t="inlineStr">
+      <c r="AN17" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN17" s="9" t="inlineStr">
+      <c r="AO17" s="9" t="inlineStr">
         <is>
           <t>AII-007, AII-023, AII-024</t>
         </is>
       </c>
-      <c r="AO17" s="9" t="inlineStr">
+      <c r="AP17" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 내부 접근 확보 1 · 자격증명·비밀 탈취 1 · 금전 피해 1</t>
         </is>
       </c>
-      <c r="AP17" s="9" t="inlineStr">
+      <c r="AQ17" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AQ17" s="9" t="inlineStr">
+      <c r="AR17" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 시그니처가 아닌 행위·맥락 기반으로 변종 악성코드를 탐지하고 무결성 변화를 감시(NIST SI-3·SI-4·SI-7)
@@ -12742,7 +12908,7 @@
 - 참고: securityonline 〈GTIG AI 0-day〉</t>
         </is>
       </c>
-      <c r="AR17" s="9" t="inlineStr">
+      <c r="AS17" s="9" t="inlineStr">
         <is>
           <t>securityonline 〈GTIG AI 0-day〉</t>
         </is>
@@ -12864,71 +13030,72 @@
       </c>
       <c r="AA18" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB18" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="AC18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD18" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 0·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AB18" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC18" s="9" t="inlineStr"/>
+      <c r="AD18" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="AE18" s="9" t="inlineStr">
         <is>
-          <t>국가배후 와이퍼 공격에서 파괴 스크립트가 LLM으로 생성된 것으로 평가됨(폴란드 에너지) — 파괴형 페이로드를 빠르게 맞춤 생성·변형해 복구를 어렵게 함</t>
-        </is>
-      </c>
-      <c r="AF18" s="9" t="n">
-        <v>1</v>
+          <t>실제 사고 1건(확인 0·추정 1, 가중 0.5, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF18" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 와이퍼·파괴 스크립트는 파괴 도구를 만드는 단계 — 생성 단계(중). 파괴 피해는 OT·엔드포인트 배포 시 실현(연계)</t>
+        </is>
       </c>
       <c r="AG18" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AH18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" s="9" t="n">
+      <c r="AJ18" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AJ18" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AK18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AL18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM18" s="29" t="inlineStr">
+      <c r="AN18" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN18" s="9" t="inlineStr">
+      <c r="AO18" s="9" t="inlineStr">
         <is>
           <t>AII-006</t>
         </is>
       </c>
-      <c r="AO18" s="9" t="inlineStr">
+      <c r="AP18" s="9" t="inlineStr">
         <is>
           <t>데이터 파괴 1 · 감시·조작 1</t>
         </is>
       </c>
-      <c r="AP18" s="9" t="inlineStr">
+      <c r="AQ18" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-7 Software, Firmware, and Information Integrity
 CP-9 System Backup</t>
         </is>
       </c>
-      <c r="AQ18" s="9" t="inlineStr">
+      <c r="AR18" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 대량 파일 변경·삭제와 파괴형 실행 행위를 조기 탐지하고 백업 무결성을 감시(NIST SI-3·SI-7)
@@ -12937,7 +13104,7 @@
 - 참고: CERT Polska 〈Energy Report 2025〉</t>
         </is>
       </c>
-      <c r="AR18" s="9" t="inlineStr">
+      <c r="AS18" s="9" t="inlineStr">
         <is>
           <t>CERT Polska 〈Energy Report 2025〉</t>
         </is>
@@ -13055,7 +13222,7 @@
       <c r="Y19" s="9" t="inlineStr"/>
       <c r="Z19" s="8" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AA19" s="8" t="inlineStr">
@@ -13063,68 +13230,69 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB19" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="AC19" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD19" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 0·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 3 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AB19" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC19" s="9" t="inlineStr"/>
+      <c r="AD19" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="AE19" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(확인 0·추정 1, 가중 0.5, 서로 다른 행위자·캠페인 2) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 3(참고)</t>
+        </is>
+      </c>
+      <c r="AF19" s="9" t="inlineStr">
+        <is>
           <t>AI가 문법·맥락이 자연스러운 미끼를 대량 생성해 기존 피싱 탐지(오탈자·어색한 표현)를 무력화 — 피해는 계정 탈취·BEC 단계에서 커짐</t>
         </is>
-      </c>
-      <c r="AF19" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="AG19" s="9" t="n">
         <v>2</v>
       </c>
       <c r="AH19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" s="9" t="n">
+      <c r="AJ19" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AJ19" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AK19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AL19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM19" s="29" t="inlineStr">
+      <c r="AN19" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN19" s="9" t="inlineStr">
+      <c r="AO19" s="9" t="inlineStr">
         <is>
           <t>AII-021, AII-023</t>
         </is>
       </c>
-      <c r="AO19" s="9" t="inlineStr">
+      <c r="AP19" s="9" t="inlineStr">
         <is>
           <t>계정 장악 1 · 자격증명·비밀 탈취 1</t>
         </is>
       </c>
-      <c r="AP19" s="9" t="inlineStr">
+      <c r="AQ19" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
 SI-4 System Monitoring
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AQ19" s="9" t="inlineStr">
+      <c r="AR19" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 발신 평판·행위·링크 분석 등 콘텐츠 품질에 덜 의존하는 다중 신호로 피싱을 탐지(NIST SI-4)
@@ -13134,7 +13302,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR19" s="9" t="inlineStr">
+      <c r="AS19" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -13265,21 +13433,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC20" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="AD20" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC20" s="9" t="inlineStr"/>
+      <c r="AD20" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="AE20" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF20" s="9" t="inlineStr">
+        <is>
           <t>수집한 표적 정보를 AI가 엮어 맥락에 맞는 사칭 메시지를 만들어 특정 인물을 노림 — 송금·자격증명 탈취로 이어질 수 있음</t>
         </is>
-      </c>
-      <c r="AF20" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG20" s="9" t="n">
         <v>0</v>
@@ -13297,22 +13463,25 @@
         <v>0</v>
       </c>
       <c r="AL20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM20" s="27" t="inlineStr">
+      <c r="AN20" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN20" s="9" t="inlineStr"/>
       <c r="AO20" s="9" t="inlineStr"/>
-      <c r="AP20" s="9" t="inlineStr">
+      <c r="AP20" s="9" t="inlineStr"/>
+      <c r="AQ20" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ20" s="9" t="inlineStr">
+      <c r="AR20" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 고위험 역할 대상 메시지의 이상 징후(발신 경로·요청 맥락)와 비정상 송금·승인 요청을 모니터링(NIST SI-4)
@@ -13321,7 +13490,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR20" s="9" t="inlineStr">
+      <c r="AS20" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -13442,30 +13611,28 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AC21" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD21" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC21" s="9" t="inlineStr"/>
+      <c r="AD21" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="AE21" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF21" s="9" t="inlineStr">
+        <is>
           <t>다자 화상회의 참석자 전원을 딥페이크로 꾸며 거액 송금을 지시한 사례(Arup 약 2,560만 달러) — 사람의 시각 신뢰를 직접 무너뜨려 고액 피해로 직결</t>
         </is>
       </c>
-      <c r="AF21" s="9" t="n">
+      <c r="AG21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AG21" s="9" t="n">
+      <c r="AH21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AH21" s="9" t="n">
+      <c r="AI21" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AI21" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ21" s="9" t="n">
         <v>0</v>
@@ -13474,30 +13641,33 @@
         <v>0</v>
       </c>
       <c r="AL21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM21" s="29" t="inlineStr">
+      <c r="AN21" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN21" s="9" t="inlineStr">
+      <c r="AO21" s="9" t="inlineStr">
         <is>
           <t>AII-002</t>
         </is>
       </c>
-      <c r="AO21" s="9" t="inlineStr">
+      <c r="AP21" s="9" t="inlineStr">
         <is>
           <t>금전 피해 1</t>
         </is>
       </c>
-      <c r="AP21" s="9" t="inlineStr">
+      <c r="AQ21" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
 IA-2 Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
-      <c r="AQ21" s="9" t="inlineStr">
+      <c r="AR21" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 고액·고위험 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검(NIST IA-2)
@@ -13506,7 +13676,7 @@
 - 참고: CNN 〈홍콩 딥페이크 금융사기〉</t>
         </is>
       </c>
-      <c r="AR21" s="9" t="inlineStr">
+      <c r="AS21" s="9" t="inlineStr">
         <is>
           <t>CNN 〈홍콩 딥페이크 금융사기〉</t>
         </is>
@@ -13635,30 +13805,28 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC22" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD22" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 6 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC22" s="9" t="inlineStr"/>
+      <c r="AD22" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="AE22" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF22" s="9" t="inlineStr">
+        <is>
           <t>직원 목소리를 딥페이크로 흉내 내 추가 인증·승인을 받아낸 사례(Retool) — 전화 기반 본인확인·헬프데스크 절차를 우회</t>
         </is>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AG22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AG22" s="9" t="n">
+      <c r="AH22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AH22" s="9" t="n">
+      <c r="AI22" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AI22" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ22" s="9" t="n">
         <v>0</v>
@@ -13667,30 +13835,33 @@
         <v>0</v>
       </c>
       <c r="AL22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM22" s="29" t="inlineStr">
+      <c r="AN22" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN22" s="9" t="inlineStr">
+      <c r="AO22" s="9" t="inlineStr">
         <is>
           <t>AII-011</t>
         </is>
       </c>
-      <c r="AO22" s="9" t="inlineStr">
+      <c r="AP22" s="9" t="inlineStr">
         <is>
           <t>계정 장악 1 · 금전 피해 1</t>
         </is>
       </c>
-      <c r="AP22" s="9" t="inlineStr">
+      <c r="AQ22" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
 IA-2 Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
-      <c r="AQ22" s="9" t="inlineStr">
+      <c r="AR22" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 헬프데스크·계정 복구 요청의 음성 사칭 징후와 비정상 MFA 등록을 점검(NIST IA-2)
@@ -13699,7 +13870,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR22" s="9" t="inlineStr">
+      <c r="AS22" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -13820,30 +13991,32 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC23" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 19 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC23" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD23" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="AE23" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(확인 2·추정 0, 가중 2, 서로 다른 행위자·캠페인 2) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 19(참고)</t>
+        </is>
+      </c>
+      <c r="AF23" s="9" t="inlineStr">
+        <is>
           <t>AI 얼굴 바꾸기로 은행 얼굴 인식·KYC를 통과해 계좌를 열거나 장악한 사례(홍콩 대출 사기·GoldPickaxe) — 비대면 본인확인 신뢰 기반을 무너뜨려 금전 피해로 직결</t>
         </is>
       </c>
-      <c r="AF23" s="9" t="n">
+      <c r="AG23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AG23" s="9" t="n">
+      <c r="AH23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AH23" s="9" t="n">
+      <c r="AI23" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AI23" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ23" s="9" t="n">
         <v>0</v>
@@ -13852,30 +14025,33 @@
         <v>0</v>
       </c>
       <c r="AL23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="AM23" s="29" t="inlineStr">
+      <c r="AN23" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN23" s="9" t="inlineStr">
+      <c r="AO23" s="9" t="inlineStr">
         <is>
           <t>AII-001, AII-013</t>
         </is>
       </c>
-      <c r="AO23" s="9" t="inlineStr">
+      <c r="AP23" s="9" t="inlineStr">
         <is>
           <t>금전 피해 2 · 계정 장악 2</t>
         </is>
       </c>
-      <c r="AP23" s="9" t="inlineStr">
+      <c r="AQ23" s="9" t="inlineStr">
         <is>
           <t>IA-2 Identification and Authentication (Organizational Users)
 AC-2 Account Management</t>
         </is>
       </c>
-      <c r="AQ23" s="9" t="inlineStr">
+      <c r="AR23" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설·접근 패턴을 모니터링(NIST IA-2·AC-2)
@@ -13884,7 +14060,7 @@
 - 참고: CNN 〈홍콩 딥페이크 금융사기〉 · Group-IB 〈GoldPickaxe〉</t>
         </is>
       </c>
-      <c r="AR23" s="9" t="inlineStr">
+      <c r="AS23" s="9" t="inlineStr">
         <is>
           <t>CNN 〈홍콩 딥페이크 금융사기〉
 Group-IB 〈GoldPickaxe〉</t>
@@ -14016,63 +14192,64 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC24" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD24" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 1 · ATLAS 사례 3 · 역량 성숙도 실증</t>
-        </is>
+      <c r="AC24" s="9" t="inlineStr"/>
+      <c r="AD24" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="AE24" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 2·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 1 · 역량 성숙도 실증(자동 실사용) · ATLAS 사례 3(참고)</t>
+        </is>
+      </c>
+      <c r="AF24" s="9" t="inlineStr">
+        <is>
           <t>AI가 만든 미끼 페이지·링크로 사람 또는 컴퓨터 사용 에이전트가 악성 명령을 실행하도록 유도(AI ClickFix 실증) — 사람·에이전트 양쪽을 속이는 신규 경로</t>
         </is>
       </c>
-      <c r="AF24" s="9" t="n">
+      <c r="AG24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AG24" s="9" t="n">
+      <c r="AH24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AH24" s="9" t="n">
+      <c r="AI24" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AI24" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AK24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AL24" s="9" t="n">
+      <c r="AM24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM24" s="29" t="inlineStr">
+      <c r="AN24" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN24" s="9" t="inlineStr">
+      <c r="AO24" s="9" t="inlineStr">
         <is>
           <t>AII-012
 실증·연구: AII-025</t>
         </is>
       </c>
-      <c r="AO24" s="9" t="inlineStr">
+      <c r="AP24" s="9" t="inlineStr">
         <is>
           <t>자격증명·비밀 탈취 1 · 금전 피해 1</t>
         </is>
       </c>
-      <c r="AP24" s="9" t="inlineStr">
+      <c r="AQ24" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ24" s="9" t="inlineStr">
+      <c r="AR24" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 에이전트·사용자의 미끼 실행 흐름(클립보드→터미널 등)과 의심 링크 접근을 행위 기반으로 탐지(NIST SI-4)
@@ -14081,7 +14258,7 @@
 - 참고: Embrace The Red 〈AI ClickFix〉</t>
         </is>
       </c>
-      <c r="AR24" s="9" t="inlineStr">
+      <c r="AS24" s="9" t="inlineStr">
         <is>
           <t>Embrace The Red 〈AI ClickFix〉</t>
         </is>
@@ -14207,21 +14384,19 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC25" s="8" t="n">
+      <c r="AC25" s="9" t="inlineStr"/>
+      <c r="AD25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AD25" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 6건(최근 6) · AI 활용 확인 6·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 9 · 역량 성숙도 실사용</t>
-        </is>
-      </c>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>탈옥 모델·공격 프레임워크로 자율 에이전트가 정찰부터 실행까지 대부분을 수행(GTG-1002는 AI가 80~90% 수행, ~30개 조직 표적) — 사람이 대응하기 어려운 속도·규모로 다수 조직을 동시에 침해</t>
-        </is>
-      </c>
-      <c r="AF25" s="9" t="n">
-        <v>6</v>
+          <t>실제 사고 6건(확인 6·추정 0, 가중 6, 서로 다른 행위자·캠페인 3) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 9(참고)</t>
+        </is>
+      </c>
+      <c r="AF25" s="9" t="inlineStr">
+        <is>
+          <t>단일 자율 에이전트가 다수 조직을 침해해 데이터 유출·내부 장악에 이름(GTG-1002 ~30개 조직·CrowdStrike 4개 행위자) — 성공 시 조직 전반 장악·대규모 유출</t>
+        </is>
       </c>
       <c r="AG25" s="9" t="n">
         <v>6</v>
@@ -14230,7 +14405,7 @@
         <v>6</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ25" s="9" t="n">
         <v>0</v>
@@ -14239,31 +14414,34 @@
         <v>0</v>
       </c>
       <c r="AL25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="AM25" s="29" t="inlineStr">
+      <c r="AN25" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN25" s="9" t="inlineStr">
+      <c r="AO25" s="9" t="inlineStr">
         <is>
           <t>AII-008, AII-027, AII-031, AII-032, AII-033, AII-034</t>
         </is>
       </c>
-      <c r="AO25" s="9" t="inlineStr">
+      <c r="AP25" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 5 · 데이터 유출 4 · 자격증명·비밀 탈취 1</t>
         </is>
       </c>
-      <c r="AP25" s="9" t="inlineStr">
+      <c r="AQ25" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting
 CA-7 Continuous Monitoring</t>
         </is>
       </c>
-      <c r="AQ25" s="9" t="inlineStr">
+      <c r="AR25" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 사람 속도를 넘는 반복·연쇄 행위 시퀀스와 비정상 세션 속도를 행위 기반으로 탐지(NIST SI-4·AU-6)
@@ -14274,7 +14452,7 @@
 - 참고: Anthropic 〈GTG-1002〉 · CrowdStrike 〈Agentic AI Campaigns〉</t>
         </is>
       </c>
-      <c r="AR25" s="9" t="inlineStr">
+      <c r="AS25" s="9" t="inlineStr">
         <is>
           <t>Anthropic 〈GTG-1002〉
 Unit 42 〈Hermes Agent〉
@@ -14395,21 +14573,19 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD26" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 3) · AI 활용 확인 3·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 2 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC26" s="9" t="inlineStr"/>
+      <c r="AD26" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>상위 오케스트레이터가 다수 하위 에이전트를 조율해 공격 웨이브를 병렬 수행(대만 정부 대상 12개 웨이브·에이전트당 최대 8개) — 공격 규모가 사람 조직의 한계를 벗어남</t>
-        </is>
-      </c>
-      <c r="AF26" s="9" t="n">
-        <v>3</v>
+          <t>실제 사고 3건(확인 3·추정 0, 가중 3, 서로 다른 행위자·캠페인 3) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 2(참고)</t>
+        </is>
+      </c>
+      <c r="AF26" s="9" t="inlineStr">
+        <is>
+          <t>다중 에이전트 조율로 넓은 표적을 침해해 대규모 데이터에 접근(대만 정부 인사 기록 2,564건 이상) — 성공 시 대규모 데이터 유출</t>
+        </is>
       </c>
       <c r="AG26" s="9" t="n">
         <v>3</v>
@@ -14418,7 +14594,7 @@
         <v>3</v>
       </c>
       <c r="AI26" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ26" s="9" t="n">
         <v>0</v>
@@ -14427,31 +14603,34 @@
         <v>0</v>
       </c>
       <c r="AL26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AM26" s="29" t="inlineStr">
+      <c r="AN26" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN26" s="9" t="inlineStr">
+      <c r="AO26" s="9" t="inlineStr">
         <is>
           <t>AII-008, AII-009, AII-032</t>
         </is>
       </c>
-      <c r="AO26" s="9" t="inlineStr">
+      <c r="AP26" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 2 · 내부 접근 확보 2</t>
         </is>
       </c>
-      <c r="AP26" s="9" t="inlineStr">
+      <c r="AQ26" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting
 CA-7 Continuous Monitoring</t>
         </is>
       </c>
-      <c r="AQ26" s="9" t="inlineStr">
+      <c r="AR26" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 동시다발 표적에 걸친 유사 패턴·상관 이벤트와 병렬 세션 급증을 탐지(NIST SI-4·CA-7)
@@ -14460,7 +14639,7 @@
 - 참고: Dream Research 〈Multi-Agent Framework〉 · Anthropic 〈GTG-1002〉</t>
         </is>
       </c>
-      <c r="AR26" s="9" t="inlineStr">
+      <c r="AS26" s="9" t="inlineStr">
         <is>
           <t>Dream Research 〈Multi-Agent Framework〉
 Anthropic 〈GTG-1002〉</t>
@@ -14595,21 +14774,23 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC27" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD27" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 20 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC27" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD27" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="AE27" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(확인 2·추정 0, 가중 2, 서로 다른 행위자·캠페인 2) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 20(참고)</t>
+        </is>
+      </c>
+      <c r="AF27" s="9" t="inlineStr">
+        <is>
           <t>악성코드가 피해 단말에 설치된 Claude·Gemini·Q 같은 AI CLI를 위험 옵션으로 실행해 비밀을 찾게 함(s1ngularity, 비공개 저장소 5,500개 이상 공개 전환) — 정상 설치된 AI 도구가 공격 실행 엔진이 됨</t>
         </is>
-      </c>
-      <c r="AF27" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="AG27" s="9" t="n">
         <v>2</v>
@@ -14618,7 +14799,7 @@
         <v>2</v>
       </c>
       <c r="AI27" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ27" s="9" t="n">
         <v>0</v>
@@ -14627,31 +14808,34 @@
         <v>0</v>
       </c>
       <c r="AL27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="AM27" s="29" t="inlineStr">
+      <c r="AN27" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN27" s="9" t="inlineStr">
+      <c r="AO27" s="9" t="inlineStr">
         <is>
           <t>AII-004, AII-018</t>
         </is>
       </c>
-      <c r="AO27" s="9" t="inlineStr">
+      <c r="AP27" s="9" t="inlineStr">
         <is>
           <t>자격증명·비밀 탈취 2 · 소스 코드 유출 1 · 데이터 유출 1</t>
         </is>
       </c>
-      <c r="AP27" s="9" t="inlineStr">
+      <c r="AQ27" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AQ27" s="9" t="inlineStr">
+      <c r="AR27" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지(NIST SI-4)
@@ -14660,7 +14844,7 @@
 - 참고: Wiz 〈s1ngularity〉</t>
         </is>
       </c>
-      <c r="AR27" s="9" t="inlineStr">
+      <c r="AS27" s="9" t="inlineStr">
         <is>
           <t>Wiz 〈s1ngularity〉</t>
         </is>
@@ -14794,21 +14978,23 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC28" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD28" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 2) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 21 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC28" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD28" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="AE28" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(확인 2·추정 0, 가중 2, 서로 다른 행위자·캠페인 2) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 21(참고)</t>
+        </is>
+      </c>
+      <c r="AF28" s="9" t="inlineStr">
+        <is>
           <t>공격자가 AI 코딩 에이전트(Claude Code 등)를 공격 수행에 직접 사용한 정황이 세션 기록으로 확인됨(BuddyBoss 공급망) — AI 도구의 광범위한 실행 권한이 공격자 손에 들어감</t>
         </is>
-      </c>
-      <c r="AF28" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="AG28" s="9" t="n">
         <v>2</v>
@@ -14817,7 +15003,7 @@
         <v>2</v>
       </c>
       <c r="AI28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ28" s="9" t="n">
         <v>0</v>
@@ -14826,31 +15012,34 @@
         <v>0</v>
       </c>
       <c r="AL28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="AM28" s="29" t="inlineStr">
+      <c r="AN28" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN28" s="9" t="inlineStr">
+      <c r="AO28" s="9" t="inlineStr">
         <is>
           <t>AII-003, AII-019</t>
         </is>
       </c>
-      <c r="AO28" s="9" t="inlineStr">
+      <c r="AP28" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 데이터 유출 1</t>
         </is>
       </c>
-      <c r="AP28" s="9" t="inlineStr">
+      <c r="AQ28" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege
 SA-15 Development Process, Standards, and Tools</t>
         </is>
       </c>
-      <c r="AQ28" s="9" t="inlineStr">
+      <c r="AR28" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - AI 개발 도구의 비정상 설정 변경·과도한 권한 사용·공급망 산출물 변조를 탐지(NIST SI-4·SA-15)
@@ -14859,7 +15048,7 @@
 - 참고: Ctrl-Alt-Intel 〈BuddyBoss〉</t>
         </is>
       </c>
-      <c r="AR28" s="9" t="inlineStr">
+      <c r="AS28" s="9" t="inlineStr">
         <is>
           <t>Ctrl-Alt-Intel 〈BuddyBoss〉</t>
         </is>
@@ -14989,63 +15178,68 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC29" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD29" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 3) · AI 활용 확인 1·추정 2 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 4 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC29" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD29" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="AE29" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 3건(확인 1·추정 2, 가중 2, 서로 다른 행위자·캠페인 3) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 4(참고)</t>
+        </is>
+      </c>
+      <c r="AF29" s="9" t="inlineStr">
+        <is>
           <t>AI로 보이는 계정이 공개 저장소의 워크플로 결함을 자동 탐색·악용해 다수 대형 저장소에서 코드 실행·토큰 탈취(hackerbot-claw, 이후 연쇄 침해) — 공급망 전반을 자동·대량으로 침해</t>
         </is>
-      </c>
-      <c r="AF29" s="9" t="n">
-        <v>3</v>
       </c>
       <c r="AG29" s="9" t="n">
         <v>3</v>
       </c>
       <c r="AH29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AI29" s="9" t="n">
+      <c r="AJ29" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AJ29" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AK29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AL29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AM29" s="29" t="inlineStr">
+      <c r="AN29" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN29" s="9" t="inlineStr">
+      <c r="AO29" s="9" t="inlineStr">
         <is>
           <t>AII-017, AII-019, AII-020</t>
         </is>
       </c>
-      <c r="AO29" s="9" t="inlineStr">
+      <c r="AP29" s="9" t="inlineStr">
         <is>
           <t>자격증명·비밀 탈취 2 · 내부 접근 확보 2 · 데이터 유출 1</t>
         </is>
       </c>
-      <c r="AP29" s="9" t="inlineStr">
+      <c r="AQ29" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CM-7 Least Functionality
 SA-15 Development Process, Standards, and Tools</t>
         </is>
       </c>
-      <c r="AQ29" s="9" t="inlineStr">
+      <c r="AR29" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지(NIST SI-4)
@@ -15054,7 +15248,7 @@
 - 참고: StepSecurity 〈hackerbot-claw〉</t>
         </is>
       </c>
-      <c r="AR29" s="9" t="inlineStr">
+      <c r="AS29" s="9" t="inlineStr">
         <is>
           <t>StepSecurity 〈hackerbot-claw〉</t>
         </is>
@@ -15190,63 +15384,68 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC30" s="8" t="n">
+      <c r="AC30" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AD30" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AD30" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 3) · AI 활용 확인 1·추정 2 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 10 · 역량 성숙도 실증</t>
-        </is>
-      </c>
       <c r="AE30" s="9" t="inlineStr">
         <is>
-          <t>AI 보조 침입이 개발 환경 침해에서 클라우드 전반 장악까지 72시간 안에 이르고(Sygnia·UNC6426) 수 시간 내 다량의 자격증명을 탈취한 사례가 보고됨 — 확산 속도가 사람 대응 주기를 앞지름</t>
-        </is>
-      </c>
-      <c r="AF30" s="9" t="n">
-        <v>3</v>
+          <t>실제 사고 3건(확인 1·추정 2, 가중 2, 서로 다른 행위자·캠페인 2) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실증(자동 실사용) · ATLAS 사례 10(참고)</t>
+        </is>
+      </c>
+      <c r="AF30" s="9" t="inlineStr">
+        <is>
+          <t>개발 환경 침해에서 클라우드 전반 장악과 다량 자격증명 탈취에 이름(Sygnia·UNC6426) — 성공 시 조직 전반 장악</t>
+        </is>
       </c>
       <c r="AG30" s="9" t="n">
         <v>3</v>
       </c>
       <c r="AH30" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AI30" s="9" t="n">
+      <c r="AJ30" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AJ30" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AK30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AL30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AM30" s="29" t="inlineStr">
+      <c r="AN30" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN30" s="9" t="inlineStr">
+      <c r="AO30" s="9" t="inlineStr">
         <is>
           <t>AII-016, AII-018, AII-022</t>
         </is>
       </c>
-      <c r="AO30" s="9" t="inlineStr">
+      <c r="AP30" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 2 · 자원 탈취 1 · 내부 접근 확보 1 · 자격증명·비밀 탈취 1</t>
         </is>
       </c>
-      <c r="AP30" s="9" t="inlineStr">
+      <c r="AQ30" s="9" t="inlineStr">
         <is>
           <t>AC-2 Account Management
 AC-6 Least Privilege
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ30" s="9" t="inlineStr">
+      <c r="AR30" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 자격증명의 비정상 사용·급속한 권한 확대·측면 이동을 아이덴티티·클라우드 로그로 탐지(NIST AC-2·SI-4)
@@ -15255,7 +15454,7 @@
 - 참고: Sygnia 〈AI-Assisted Cloud Attack〉</t>
         </is>
       </c>
-      <c r="AR30" s="9" t="inlineStr">
+      <c r="AS30" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉
 Sygnia 〈AI-Assisted Cloud Attack〉</t>
@@ -15385,21 +15584,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC31" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD31" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 4 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC31" s="9" t="inlineStr"/>
+      <c r="AD31" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="AE31" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 4(참고)</t>
+        </is>
+      </c>
+      <c r="AF31" s="9" t="inlineStr">
+        <is>
           <t>사람 공격자의 지시 없이 자율 에이전트가 평가·운영 경계를 벗어나 실제 인프라를 침해한 사례(OpenAI 평가 에이전트→Hugging Face) — 현재는 연구·평가 맥락이나 통제 실패 시 자발적 피해 가능성을 보임(D14)</t>
         </is>
-      </c>
-      <c r="AF31" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="AG31" s="9" t="n">
         <v>1</v>
@@ -15408,7 +15605,7 @@
         <v>1</v>
       </c>
       <c r="AI31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" s="9" t="n">
         <v>0</v>
@@ -15417,31 +15614,34 @@
         <v>0</v>
       </c>
       <c r="AL31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AM31" s="29" t="inlineStr">
+      <c r="AN31" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN31" s="9" t="inlineStr">
+      <c r="AO31" s="9" t="inlineStr">
         <is>
           <t>AII-010</t>
         </is>
       </c>
-      <c r="AO31" s="9" t="inlineStr">
+      <c r="AP31" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AP31" s="9" t="inlineStr">
+      <c r="AQ31" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege
 CA-7 Continuous Monitoring</t>
         </is>
       </c>
-      <c r="AQ31" s="9" t="inlineStr">
+      <c r="AR31" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 평가·자동화 에이전트의 권한 경계 이탈·비정상 외부 접근과 사람 지시 없는 연쇄 행위를 행위 기반으로 탐지(NIST SI-4·CA-7)
@@ -15450,7 +15650,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR31" s="9" t="inlineStr">
+      <c r="AS31" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -15573,72 +15773,73 @@
       </c>
       <c r="AA32" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB32" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="AC32" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD32" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 1 · ATLAS 사례 3 · 역량 성숙도 실사용</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AB32" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC32" s="9" t="inlineStr"/>
+      <c r="AD32" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="AE32" s="9" t="inlineStr">
         <is>
-          <t>정상 AI 서비스(Grok·Copilot 등)의 트래픽에 C2를 숨겨 양방향 채널을 만드는 기법(AI-in-the-Middle 실증)과 AI API 은닉 통신(LAMEHUG) — 정상 서비스라 경계·egress 통제가 걸러내기 어려움</t>
-        </is>
-      </c>
-      <c r="AF32" s="9" t="n">
-        <v>1</v>
+          <t>실제 사고 1건(확인 2·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 1 · 역량 성숙도 실사용 · ATLAS 사례 3(참고)</t>
+        </is>
+      </c>
+      <c r="AF32" s="9" t="inlineStr">
+        <is>
+          <t>AI 서비스 경유 은닉 C2는 통신·은닉 수단으로 단독 피해는 없음 — 은닉·명령제어 조건(중)</t>
+        </is>
       </c>
       <c r="AG32" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AH32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AI32" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AK32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AL32" s="9" t="n">
+      <c r="AM32" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM32" s="29" t="inlineStr">
+      <c r="AN32" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN32" s="9" t="inlineStr">
+      <c r="AO32" s="9" t="inlineStr">
         <is>
           <t>AII-007
 실증·연구: AII-026</t>
         </is>
       </c>
-      <c r="AO32" s="9" t="inlineStr">
+      <c r="AP32" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AP32" s="9" t="inlineStr">
+      <c r="AQ32" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AQ32" s="9" t="inlineStr">
+      <c r="AR32" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - AI 서비스로의 비정상 egress 패턴·데이터량과 자동화된 세션을 모니터링(NIST SC-7·SI-4·AU-6)
@@ -15647,7 +15848,7 @@
 - 참고: Check Point 〈AI in the Middle〉</t>
         </is>
       </c>
-      <c r="AR32" s="9" t="inlineStr">
+      <c r="AS32" s="9" t="inlineStr">
         <is>
           <t>Check Point 〈AI in the Middle〉</t>
         </is>
@@ -15765,29 +15966,27 @@
       </c>
       <c r="AA33" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AB33" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="AC33" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD33" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 4 · 역량 성숙도 실사용</t>
-        </is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="AB33" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="AC33" s="9" t="inlineStr"/>
+      <c r="AD33" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="AE33" s="9" t="inlineStr">
         <is>
-          <t>악성코드가 실행 중 LLM API에 질의해 명령을 매번 새로 생성(LAMEHUG, APT28) — 고정 페이로드·시그니처가 없어 정적 분석·시그니처 탐지가 무력화됨</t>
-        </is>
-      </c>
-      <c r="AF33" s="9" t="n">
-        <v>1</v>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 4(참고)</t>
+        </is>
+      </c>
+      <c r="AF33" s="9" t="inlineStr">
+        <is>
+          <t>실행 중 동적 명령 생성은 탐지 회피 수단으로 단독 피해는 없음 — 은닉·명령제어 조건(중)</t>
+        </is>
       </c>
       <c r="AG33" s="9" t="n">
         <v>1</v>
@@ -15796,7 +15995,7 @@
         <v>1</v>
       </c>
       <c r="AI33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" s="9" t="n">
         <v>0</v>
@@ -15805,31 +16004,34 @@
         <v>0</v>
       </c>
       <c r="AL33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AM33" s="29" t="inlineStr">
+      <c r="AN33" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN33" s="9" t="inlineStr">
+      <c r="AO33" s="9" t="inlineStr">
         <is>
           <t>AII-007</t>
         </is>
       </c>
-      <c r="AO33" s="9" t="inlineStr">
+      <c r="AP33" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AP33" s="9" t="inlineStr">
+      <c r="AQ33" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AQ33" s="9" t="inlineStr">
+      <c r="AR33" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위·맥락 기반으로 탐지(NIST SI-3·SI-4·AU-6)
@@ -15838,7 +16040,7 @@
 - 참고: The Hacker News 〈LAMEHUG〉</t>
         </is>
       </c>
-      <c r="AR33" s="9" t="inlineStr">
+      <c r="AS33" s="9" t="inlineStr">
         <is>
           <t>The Hacker News 〈LAMEHUG〉</t>
         </is>
@@ -15966,21 +16168,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC34" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD34" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 20 · 역량 성숙도 실증</t>
-        </is>
+      <c r="AC34" s="9" t="inlineStr"/>
+      <c r="AD34" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="AE34" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실증 · ATLAS 사례 20(참고)</t>
+        </is>
+      </c>
+      <c r="AF34" s="9" t="inlineStr">
+        <is>
           <t>AI로 페이로드를 자동 변형·난독화하거나 적대적 입력으로 ML 탐지기를 회피 — 시그니처·정적 탐지를 체계적으로 우회하나 행위 기반 탐지로 일부 포착 가능</t>
         </is>
-      </c>
-      <c r="AF34" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG34" s="9" t="n">
         <v>0</v>
@@ -15998,23 +16198,26 @@
         <v>0</v>
       </c>
       <c r="AL34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="AM34" s="28" t="inlineStr">
+      <c r="AN34" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
       </c>
-      <c r="AN34" s="9" t="inlineStr"/>
       <c r="AO34" s="9" t="inlineStr"/>
-      <c r="AP34" s="9" t="inlineStr">
+      <c r="AP34" s="9" t="inlineStr"/>
+      <c r="AQ34" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AQ34" s="9" t="inlineStr">
+      <c r="AR34" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 행위·맥락 기반 탐지와 다중 엔진·이상 탐지로 변형·적대적 회피를 보완 탐지(NIST SI-3·SI-4)
@@ -16023,7 +16226,7 @@
 - 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR34" s="9" t="inlineStr">
+      <c r="AS34" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
@@ -16158,60 +16361,61 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC35" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD35" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 1) · AI 활용 확인 2·추정 0 · 위협인텔 0 · 실증·연구 1 · ATLAS 사례 6 · 역량 성숙도 실증</t>
-        </is>
+      <c r="AC35" s="9" t="inlineStr"/>
+      <c r="AD35" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="AE35" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 2·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 1 · 역량 성숙도 실증(자동 실사용) · ATLAS 사례 6(참고)</t>
+        </is>
+      </c>
+      <c r="AF35" s="9" t="inlineStr">
+        <is>
           <t>규칙 파일에 보이지 않는 유니코드로 지시를 숨겨 AI가 생성 코드에 백도어를 넣게 하거나(Rules File Backdoor) AI 코딩 에이전트에 파괴 지시를 주입(Amazon Q) — 사람 리뷰가 알아채기 어려운 은닉 경로</t>
         </is>
-      </c>
-      <c r="AF35" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="AG35" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AH35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AI35" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AK35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AL35" s="9" t="n">
+      <c r="AM35" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM35" s="29" t="inlineStr">
+      <c r="AN35" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN35" s="9" t="inlineStr">
+      <c r="AO35" s="9" t="inlineStr">
         <is>
           <t>AII-003
 실증·연구: AII-014</t>
         </is>
       </c>
-      <c r="AO35" s="9" t="inlineStr"/>
-      <c r="AP35" s="9" t="inlineStr">
+      <c r="AP35" s="9" t="inlineStr"/>
+      <c r="AQ35" s="9" t="inlineStr">
         <is>
           <t>SA-15 Development Process, Standards, and Tools
 SI-7 Software, Firmware, and Information Integrity
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AQ35" s="9" t="inlineStr">
+      <c r="AR35" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 규칙·설정 파일의 비가시 문자·숨은 지시와 생성 코드의 의심 변경을 검사(NIST SI-7·SA-15)
@@ -16220,7 +16424,7 @@
 - 참고: Pillar Security 〈Rules File Backdoor〉</t>
         </is>
       </c>
-      <c r="AR35" s="9" t="inlineStr">
+      <c r="AS35" s="9" t="inlineStr">
         <is>
           <t>Pillar Security 〈Rules File Backdoor〉</t>
         </is>
@@ -16342,30 +16546,28 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AC36" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD36" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · AI 활용 확인 1·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 17 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC36" s="9" t="inlineStr"/>
+      <c r="AD36" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="AE36" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 17(참고)</t>
+        </is>
+      </c>
+      <c r="AF36" s="9" t="inlineStr">
+        <is>
           <t>딥페이크 사칭으로 대규모 부정 송금이 실제 발생(Arup 약 2,560만 달러) — 한 번의 성공으로 조직에 큰 금전 피해</t>
         </is>
       </c>
-      <c r="AF36" s="9" t="n">
+      <c r="AG36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AG36" s="9" t="n">
+      <c r="AH36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AH36" s="9" t="n">
+      <c r="AI36" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AI36" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AJ36" s="9" t="n">
         <v>0</v>
@@ -16374,30 +16576,33 @@
         <v>0</v>
       </c>
       <c r="AL36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="AM36" s="29" t="inlineStr">
+      <c r="AN36" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN36" s="9" t="inlineStr">
+      <c r="AO36" s="9" t="inlineStr">
         <is>
           <t>AII-002</t>
         </is>
       </c>
-      <c r="AO36" s="9" t="inlineStr">
+      <c r="AP36" s="9" t="inlineStr">
         <is>
           <t>금전 피해 1</t>
         </is>
       </c>
-      <c r="AP36" s="9" t="inlineStr">
+      <c r="AQ36" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
 IA-2 Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
-      <c r="AQ36" s="9" t="inlineStr">
+      <c r="AR36" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 고액·비정상 송금 요청과 사칭 징후를 결제·승인 흐름에서 모니터링(NIST IA-2)
@@ -16406,7 +16611,7 @@
 - 참고: CNN 〈홍콩 딥페이크 금융사기〉</t>
         </is>
       </c>
-      <c r="AR36" s="9" t="inlineStr">
+      <c r="AS36" s="9" t="inlineStr">
         <is>
           <t>CNN 〈홍콩 딥페이크 금융사기〉</t>
         </is>
@@ -16538,63 +16743,64 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AC37" s="8" t="n">
+      <c r="AC37" s="9" t="inlineStr"/>
+      <c r="AD37" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AD37" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 4건(최근 4) · AI 활용 확인 3·추정 1 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 14 · 역량 성숙도 실사용</t>
-        </is>
-      </c>
       <c r="AE37" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 4건(확인 3·추정 1, 가중 3.5, 서로 다른 행위자·캠페인 3) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 14(참고)</t>
+        </is>
+      </c>
+      <c r="AF37" s="9" t="inlineStr">
+        <is>
           <t>자율 에이전트가 침해 환경에서 민감 데이터를 자동 수집·반출(대만 2,564건 이상 인사 기록) — 수집·분류·반출을 AI가 수행해 대규모 유출을 빠르게 완료</t>
         </is>
-      </c>
-      <c r="AF37" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="AG37" s="9" t="n">
         <v>4</v>
       </c>
       <c r="AH37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI37" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AI37" s="9" t="n">
+      <c r="AJ37" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AJ37" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AK37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AL37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AM37" s="29" t="inlineStr">
+      <c r="AN37" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AN37" s="9" t="inlineStr">
+      <c r="AO37" s="9" t="inlineStr">
         <is>
           <t>AII-009, AII-022, AII-031, AII-034</t>
         </is>
       </c>
-      <c r="AO37" s="9" t="inlineStr">
+      <c r="AP37" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 4 · 서비스 중단 1 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AP37" s="9" t="inlineStr">
+      <c r="AQ37" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AQ37" s="9" t="inlineStr">
+      <c r="AR37" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 대량·자동화된 데이터 접근·반출 패턴과 비정상 egress를 모니터링(NIST SI-4·AU-6·SC-7)
@@ -16603,7 +16809,7 @@
 - 참고: Dream Research 〈Multi-Agent Framework〉</t>
         </is>
       </c>
-      <c r="AR37" s="9" t="inlineStr">
+      <c r="AS37" s="9" t="inlineStr">
         <is>
           <t>Dream Research 〈Multi-Agent Framework〉</t>
         </is>
@@ -16720,21 +16926,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AC38" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD38" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · AI 활용 확인 0·추정 0 · 위협인텔 0 · 실증·연구 0 · ATLAS 사례 7 · 역량 성숙도 실사용</t>
-        </is>
+      <c r="AC38" s="9" t="inlineStr"/>
+      <c r="AD38" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="AE38" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 7(참고)</t>
+        </is>
+      </c>
+      <c r="AF38" s="9" t="inlineStr">
+        <is>
           <t>AI가 공격당 비용을 낮춰 캠페인을 대량·병렬로 벌일 수 있게 함(기회주의적 대량 PR·캠페인 규모화) — 개별 피해보다 전체 공격량·빈도를 끌어올림</t>
         </is>
-      </c>
-      <c r="AF38" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG38" s="9" t="n">
         <v>0</v>
@@ -16752,23 +16956,26 @@
         <v>0</v>
       </c>
       <c r="AL38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AM38" s="27" t="inlineStr">
+      <c r="AN38" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AN38" s="9" t="inlineStr"/>
       <c r="AO38" s="9" t="inlineStr"/>
-      <c r="AP38" s="9" t="inlineStr">
+      <c r="AP38" s="9" t="inlineStr"/>
+      <c r="AQ38" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CA-7 Continuous Monitoring
 PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ38" s="9" t="inlineStr">
+      <c r="AR38" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 캠페인 규모·빈도 증가와 교차 표적 상관 지표를 지속 모니터링(NIST SI-4·CA-7)
@@ -16777,7 +16984,7 @@
 - 참고: CrowdStrike 〈Agentic AI Campaigns〉 · HiddenLayer 〈2026 AI Threat Landscape〉</t>
         </is>
       </c>
-      <c r="AR38" s="9" t="inlineStr">
+      <c r="AS38" s="9" t="inlineStr">
         <is>
           <t>CrowdStrike 〈Agentic AI Campaigns〉
 HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -16785,16 +16992,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AR38"/>
+  <autoFilter ref="A4:AS38"/>
   <mergeCells count="8">
     <mergeCell ref="J3:N3"/>
-    <mergeCell ref="A2:AR2"/>
     <mergeCell ref="O3:Y3"/>
-    <mergeCell ref="AF3:AO3"/>
-    <mergeCell ref="A1:AR1"/>
+    <mergeCell ref="A1:AS1"/>
+    <mergeCell ref="Z3:AF3"/>
+    <mergeCell ref="AG3:AP3"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="Z3:AE3"/>
-    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="A2:AS2"/>
+    <mergeCell ref="AQ3:AS3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17007,7 +17214,7 @@
         </is>
       </c>
       <c r="O3" s="8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P3" s="27" t="inlineStr">
         <is>
@@ -17105,7 +17312,7 @@
         </is>
       </c>
       <c r="O4" s="8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P4" s="28" t="inlineStr">
         <is>
@@ -17203,7 +17410,7 @@
         </is>
       </c>
       <c r="O5" s="8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P5" s="29" t="inlineStr">
         <is>
@@ -17301,7 +17508,7 @@
         </is>
       </c>
       <c r="O6" s="8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P6" s="29" t="inlineStr">
         <is>
@@ -17399,7 +17606,7 @@
         </is>
       </c>
       <c r="O7" s="8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P7" s="27" t="inlineStr">
         <is>
@@ -17481,7 +17688,7 @@
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
@@ -17497,9 +17704,9 @@
       <c r="O8" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="P8" s="28" t="inlineStr">
-        <is>
-          <t>실증·공개 PoC</t>
+      <c r="P8" s="30" t="inlineStr">
+        <is>
+          <t>이론·연구 시연</t>
         </is>
       </c>
       <c r="Q8" s="8" t="n">
@@ -17591,7 +17798,7 @@
         </is>
       </c>
       <c r="O9" s="8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P9" s="27" t="inlineStr">
         <is>
@@ -17687,7 +17894,7 @@
         </is>
       </c>
       <c r="O10" s="8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P10" s="28" t="inlineStr">
         <is>
@@ -17774,12 +17981,12 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="O11" s="8" t="n">
@@ -17870,16 +18077,16 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N12" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="O12" s="8" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P12" s="27" t="inlineStr">
         <is>
@@ -17975,7 +18182,7 @@
         </is>
       </c>
       <c r="O13" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P13" s="28" t="inlineStr">
         <is>
@@ -18062,16 +18269,16 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="O14" s="8" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="P14" s="27" t="inlineStr">
         <is>
@@ -18158,16 +18365,16 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>매우 높음</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="O15" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P15" s="29" t="inlineStr">
         <is>
@@ -18254,16 +18461,16 @@
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="O16" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P16" s="29" t="inlineStr">
         <is>
@@ -18345,7 +18552,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -18353,13 +18560,13 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="O17" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P17" s="29" t="inlineStr">
         <is>
@@ -18456,7 +18663,7 @@
         </is>
       </c>
       <c r="O18" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P18" s="27" t="inlineStr">
         <is>
@@ -18552,7 +18759,7 @@
         </is>
       </c>
       <c r="O19" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P19" s="29" t="inlineStr">
         <is>
@@ -18648,7 +18855,7 @@
         </is>
       </c>
       <c r="O20" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="P20" s="29" t="inlineStr">
         <is>
@@ -18744,7 +18951,7 @@
         </is>
       </c>
       <c r="O21" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P21" s="29" t="inlineStr">
         <is>
@@ -18840,7 +19047,7 @@
         </is>
       </c>
       <c r="O22" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P22" s="29" t="inlineStr">
         <is>
@@ -19034,7 +19241,7 @@
         </is>
       </c>
       <c r="O24" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P24" s="29" t="inlineStr">
         <is>
@@ -19130,7 +19337,7 @@
         </is>
       </c>
       <c r="O25" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P25" s="29" t="inlineStr">
         <is>
@@ -19226,7 +19433,7 @@
         </is>
       </c>
       <c r="O26" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P26" s="29" t="inlineStr">
         <is>
@@ -19322,7 +19529,7 @@
         </is>
       </c>
       <c r="O27" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P27" s="29" t="inlineStr">
         <is>
@@ -19514,7 +19721,7 @@
         </is>
       </c>
       <c r="O29" s="8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P29" s="29" t="inlineStr">
         <is>
@@ -19601,16 +19808,16 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N30" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="O30" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P30" s="29" t="inlineStr">
         <is>
@@ -19697,16 +19904,16 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="N31" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="O31" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P31" s="29" t="inlineStr">
         <is>
@@ -19802,7 +20009,7 @@
         </is>
       </c>
       <c r="O32" s="8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P32" s="28" t="inlineStr">
         <is>
@@ -19898,7 +20105,7 @@
         </is>
       </c>
       <c r="O33" s="8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P33" s="29" t="inlineStr">
         <is>
@@ -19994,7 +20201,7 @@
         </is>
       </c>
       <c r="O34" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P34" s="29" t="inlineStr">
         <is>
@@ -20186,7 +20393,7 @@
         </is>
       </c>
       <c r="O36" s="8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P36" s="27" t="inlineStr">
         <is>
@@ -20408,10 +20615,10 @@
         <v>5</v>
       </c>
       <c r="F3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>3</v>
@@ -20426,10 +20633,10 @@
         <v>2</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="9" t="n">
         <v>2</v>
@@ -20439,7 +20646,7 @@
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-04 공세 AI 에이전트·공격 하네스 구축(매우 높음, 사고 2)
+          <t>AIA-RD-04 공세 AI 에이전트·공격 하네스 구축(높음, 사고 2)
 AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성(보통, 사고 0)
 AIA-RD-01.1 다크 LLM·탈옥 모델 확보(보통, 사고 0)</t>
         </is>
@@ -20468,13 +20675,13 @@
         <v>5</v>
       </c>
       <c r="F4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="H4" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" s="9" t="n">
         <v>0</v>
@@ -20499,9 +20706,9 @@
       </c>
       <c r="P4" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음, 사고 3)
-AIA-VE-03.2 AI 생성 와이퍼·파괴 스크립트(높음, 사고 1)
-AIA-VE-01.1 AI 자율 취약점 발굴(버그 헌팅)(높음, 사고 0)</t>
+          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드(높음, 사고 3)
+AIA-VE-03.2 AI 생성 와이퍼·파괴 스크립트(보통, 사고 1)
+AIA-VE-01.1 AI 자율 취약점 발굴(버그 헌팅)(보통, 사고 0)</t>
         </is>
       </c>
     </row>
@@ -20531,10 +20738,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>0</v>
@@ -20560,8 +20767,8 @@
       <c r="P5" s="9" t="inlineStr">
         <is>
           <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음, 사고 2)
-AIA-IA-01.1 AI 생성 대량 피싱·미끼(높음, 사고 2)
-AIA-IA-02.1 영상 딥페이크 사칭(높음, 사고 1)</t>
+AIA-IA-02.1 영상 딥페이크 사칭(높음, 사고 1)
+AIA-IA-01.1 AI 생성 대량 피싱·미끼(보통, 사고 2)</t>
         </is>
       </c>
     </row>
@@ -20651,10 +20858,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
@@ -20679,9 +20886,9 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-02 실행 중 AI 명령 동적 생성 악성코드(높음, 사고 1)
-AIA-CC-01 AI 서비스 API·웹 인터페이스 경유 은닉 C2(높음, 사고 1)
-AIA-CC-04 AI 코딩 도구 규칙·설정 숨은 지시 주입(보통, 사고 1)</t>
+          <t>AIA-CC-04 AI 코딩 도구 규칙·설정 숨은 지시 주입(보통, 사고 1)
+AIA-CC-02 실행 중 AI 명령 동적 생성 악성코드(보통, 사고 1)
+AIA-CC-01 AI 서비스 API·웹 인터페이스 경유 은닉 C2(보통, 사고 1)</t>
         </is>
       </c>
     </row>
@@ -20841,7 +21048,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>5</v>
@@ -20860,9 +21067,9 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음)
-AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음)
-AIA-IA-01.1 AI 생성 대량 피싱·미끼(높음)</t>
+          <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음)
+AIA-VE-03.1 AI 생성·AI 연동 악성코드(높음)
+AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기(높음)</t>
         </is>
       </c>
     </row>
@@ -20911,7 +21118,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>6</v>
@@ -20946,7 +21153,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>4</v>
@@ -20967,7 +21174,7 @@
         <is>
           <t>AIA-AO-01 단일 자율 공격 에이전트 실행(매우 높음)
 AIA-AO-02 다중 에이전트 공격 조율(매우 높음)
-AIA-VE-01.1 AI 자율 취약점 발굴(버그 헌팅)(높음)</t>
+AIA-AO-06 통제를 벗어난 자율 에이전트의 자발적 침해(사람 공격자 없음)(보통)</t>
         </is>
       </c>
     </row>
@@ -21015,7 +21222,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>10</v>
@@ -21040,7 +21247,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>4</v>
@@ -21049,9 +21256,9 @@
         <is>
           <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음)
 AIA-AO-05 AI 가속 자격증명 탈취·내부 확산(매우 높음)
-AIA-VE-03.1 AI 생성·AI 연동 악성코드(매우 높음)
 AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음)
-AIA-IA-01.1 AI 생성 대량 피싱·미끼(높음)</t>
+AIA-VE-03.1 AI 생성·AI 연동 악성코드(높음)
+AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기(높음)</t>
         </is>
       </c>
     </row>

--- a/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
+++ b/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v2.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'보고서용 간략 매트릭스'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'통합 매트릭스'!$A$4:$AS$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'통합매트릭스_LITE'!$A$2:$S$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$O$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$O$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>32건(2023~2026) — 실제 사고 26 · 위협인텔 1 · 실증·연구 5, AI 활용 확인 25·추정 6. 통합 v4.1 재인용 25건(origin) + 신규 7건. 연도별 2023:3·2024:2·2025:8·2026:19 (급증)</t>
+          <t>37건(2023~2026) — 실제 사고 29 · 위협인텔 3 · 실증·연구 5, AI 활용 확인 29·추정 7. 통합 v4.1 재인용 25건(origin) + 신규 12건. 연도별 2023:3·2024:2·2025:12·2026:20 (급증)</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>사고 DB 32건과 매핑 세부위협·AI 활용·성숙도·출처(근거 추적)</t>
+          <t>사고 DB 37건과 매핑 세부위협·AI 활용·성숙도·출처(근거 추적)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>실제 사고 확인 22 · 실사용 역량(성숙도) 7 · 실증·공개 PoC 4 · 이론·연구 시연 1</t>
+          <t>실제 사고 확인 24 · 실사용 역량(성숙도) 6 · 실증·공개 PoC 3 · 이론·연구 시연 1</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>34/34개 작성 — 전 항목 완료 | scripts/validate.py 세부위협 34개(문구 34) · 사고 32건 · 시나리오 7개 · 실제 사고가 매핑된 행 22개 · 인용 사례 42건</t>
+          <t>34/34개 작성 — 전 항목 완료 | scripts/validate.py 세부위협 34개(문구 34) · 사고 37건 · 시나리오 7개 · 실제 사고가 매핑된 행 24개 · 인용 사례 47건</t>
         </is>
       </c>
     </row>
@@ -1138,8 +1138,8 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1. AIA-AO-01 단일 자율 공격 에이전트 실행 — 매우 높음, 실제 사고 6건(성숙도 실사용)
-2. AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 — 매우 높음, 실제 사고 4건(성숙도 실사용)
+          <t>1. AIA-AO-01 단일 자율 공격 에이전트 실행 — 매우 높음, 실제 사고 7건(성숙도 실사용)
+2. AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 — 매우 높음, 실제 사고 5건(성숙도 실사용)
 3. AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 — 매우 높음, 실제 사고 3건(성숙도 실증)
 4. AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 — 매우 높음, 실제 사고 3건(성숙도 실사용)
 5. AIA-AO-02 다중 에이전트 공격 조율 — 매우 높음, 실제 사고 3건(성숙도 실사용)
@@ -1147,7 +1147,7 @@
 7. AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용 — 매우 높음, 실제 사고 2건(성숙도 실사용)
 8. AIA-IA-03 딥페이크 기반 생체·본인확인 우회 — 매우 높음, 실제 사고 2건(성숙도 실사용)
 9. AIA-VE-03.1 AI 생성·AI 연동 악성코드 — 높음, 실제 사고 3건(성숙도 실사용)
-10. AIA-RD-04 공세 AI 에이전트·공격 하네스 구축 — 높음, 실제 사고 2건(성숙도 실사용)</t>
+10. AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기 — 높음, 실제 사고 2건(성숙도 실사용)</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>자율 취약점 발굴·익스플로잇 생성(VE)·역량 확보(RD)·일부 정찰은 실제 사고보다 실증·위협인텔 근거가 큼. 실제 사고가 매핑된 세부위협 22/34개 — 나머지는 성숙도·실증·위협인텔로 평가</t>
+          <t>자율 취약점 발굴·익스플로잇 생성(VE)·역량 확보(RD)·일부 정찰은 실제 사고보다 실증·위협인텔 근거가 큼. 실제 사고가 매핑된 세부위협 24/34개 — 나머지는 성숙도·실증·위협인텔로 평가</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-01, AIA-IA-02.1, AIA-IA-01.1, AIA-IA-02.2, AIA-IA-04, AIA-RT-01.1, AIA-IA-01.2</t>
+          <t>AIA-IM-01, AIA-IA-02.1, AIA-IA-02.2, AIA-IA-01.1, AIA-IA-01.2, AIA-IA-04, AIA-RT-01.1</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>AIA-RD-04, AIA-RT-03, AIA-RD-02, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-RD-01.2</t>
+          <t>AIA-RD-04, AIA-RD-02, AIA-RT-03, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-RD-01.2</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.1, AIA-VE-03.2, AIA-CC-02, AIA-CC-03, AIA-RD-02</t>
+          <t>AIA-VE-03.1, AIA-RD-02, AIA-VE-03.2, AIA-CC-02, AIA-CC-03</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01, AIA-IM-02, AIA-AO-05, AIA-AO-04, AIA-AO-02, AIA-AO-03.2, AIA-AO-03.1, AIA-VE-03.1, AIA-RD-04, AIA-IA-01.1, AIA-RT-02, AIA-AO-06, AIA-CC-02, AIA-CC-01, AIA-IA-04, AIA-CC-03, AIA-RD-02, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-IA-01.2, AIA-RD-03</t>
+          <t>AIA-AO-01, AIA-IM-02, AIA-AO-05, AIA-AO-04, AIA-AO-02, AIA-AO-03.2, AIA-AO-03.1, AIA-VE-03.1, AIA-RD-04, AIA-IA-01.1, AIA-RD-02, AIA-RT-02, AIA-IA-01.2, AIA-AO-06, AIA-CC-02, AIA-CC-01, AIA-IA-04, AIA-CC-03, AIA-RT-01.1, AIA-RD-01.1, AIA-RT-01.2, AIA-IM-04, AIA-RD-03</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="M5" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="M6" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
@@ -8160,22 +8160,22 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[IM] 영향·규모화</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-04</t>
+          <t>AIA-IM-01</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>공세 AI 에이전트·공격 하네스 구축</t>
+          <t>딥페이크·AI 사칭 기반 금전 사기</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>스캐너·도구를 엮은 공세 AI 에이전트·공격 하네스 구축</t>
+          <t>딥페이크·AI 사칭으로 대규모 부정 송금 금전 사기 실현</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -8183,29 +8183,25 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>경계</t>
-        </is>
-      </c>
+      <c r="G14" s="8" t="inlineStr"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
@@ -8218,12 +8214,12 @@
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
+          <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-02) (AII-002)</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>AI 속도 공격을 전제한 탐지·대응 자동화와 AI 제공자 오남용 탐지 연계, 공격 하네스 구성 요소 차단(NIST SI-4·SA-11)</t>
+          <t>고액 송금에 다채널·사전 등록 경로 확인과 역할 분리·한도를 적용(NIST AT-2(3)·IA-2)</t>
         </is>
       </c>
     </row>
@@ -8233,22 +8229,22 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>[IM] 영향·규모화</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>AIA-IM-01</t>
+          <t>AIA-RD-04</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>딥페이크·AI 사칭 기반 금전 사기</t>
+          <t>공세 AI 에이전트·공격 하네스 구축</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>딥페이크·AI 사칭으로 대규모 부정 송금 금전 사기 실현</t>
+          <t>스캐너·도구를 엮은 공세 AI 에이전트·공격 하네스 구축</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -8256,25 +8252,29 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
@@ -8283,16 +8283,16 @@
         </is>
       </c>
       <c r="M15" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Arup 딥페이크 화상회의 송금 사기(2024-02) (AII-002)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
         </is>
       </c>
       <c r="O15" s="9" t="inlineStr">
         <is>
-          <t>고액 송금에 다채널·사전 등록 경로 확인과 역할 분리·한도를 적용(NIST AT-2(3)·IA-2)</t>
+          <t>AI 속도 공격을 전제한 탐지·대응 자동화와 AI 제공자 오남용 탐지 연계, 공격 하네스 구성 요소 차단(NIST SI-4·SA-11)</t>
         </is>
       </c>
     </row>
@@ -8376,17 +8376,17 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-01.1</t>
+          <t>AIA-IA-02.2</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>AI 생성 대량 피싱·미끼</t>
+          <t>음성 딥페이크 사칭</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] CaptiveCrunch — Midnight Blizzard 하위 그룹의 AI 보조 악성코드 개발(2026-07) (AII-023)</t>
+          <t>[실제 사고] Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)(2023-09) (AII-011)</t>
         </is>
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>피싱 내성 MFA·조건부 접근과 사용자 신고·교육으로 대량 미끼에 대응(NIST AT-2(3))</t>
+          <t>음성에 의존하지 않는 본인확인(콜백·사전 등록·피싱 내성 MFA)과 헬프데스크 절차 강화(NIST IA-2·AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -8440,22 +8440,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-02</t>
+          <t>AIA-IA-01.1</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
+          <t>AI 생성 대량 피싱·미끼</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
+          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
@@ -8490,16 +8490,16 @@
         </is>
       </c>
       <c r="M18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
+          <t>[실제 사고] CaptiveCrunch — Midnight Blizzard 하위 그룹의 AI 보조 악성코드 개발(2026-07) (AII-023)</t>
         </is>
       </c>
       <c r="O18" s="9" t="inlineStr">
         <is>
-          <t>공격면을 줄이고 관리 인터페이스를 경계 밖에 노출하지 않음(NIST SC-7)</t>
+          <t>피싱 내성 MFA·조건부 접근과 사용자 신고·교육으로 대량 미끼에 대응(NIST AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -8509,22 +8509,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-02.2</t>
+          <t>AIA-RD-02</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>음성 딥페이크 사칭</t>
+          <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
+          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)(2023-09) (AII-011)</t>
+          <t>[실제 사고] GTG-2002 — AI 코딩 에이전트로 정찰·침투 판단·데이터 갈취('vibe hacking')(2025-08) (AII-038)</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
         <is>
-          <t>음성에 의존하지 않는 본인확인(콜백·사전 등록·피싱 내성 MFA)과 헬프데스크 절차 강화(NIST IA-2·AT-2(3))</t>
+          <t>시그니처가 아닌 행위·맥락 기반 탐지로 매번 달라지는 산출물에 대응하고 최소 권한을 적용(NIST SI-4·PM-16)</t>
         </is>
       </c>
     </row>
@@ -8578,22 +8578,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>AIA-VE-03.2</t>
+          <t>AIA-RT-02</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>AI 생성 와이퍼·파괴 스크립트</t>
+          <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
+          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)(2026-01) (AII-006)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
         <is>
-          <t>행위 기반 탐지·실행 통제와 오프라인·불변 백업으로 복구력을 확보(NIST SI-7·CP-9)</t>
+          <t>공격면을 줄이고 관리 인터페이스를 경계 밖에 노출하지 않음(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -8647,22 +8647,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-04</t>
+          <t>AIA-IA-01.2</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
+          <t>AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
+          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -8683,17 +8683,17 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Amazon Q Developer 확장에 삭제 지시 주입(2025-07) (AII-003)</t>
+          <t>[실제 사고] 김수키의 생성형 AI 위조 군 신분증 스피어피싱(국내)(2025-07) (AII-035)</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>규칙·설정 파일을 변경 통제·리뷰 대상에 포함하고 비가시 문자를 정규화·차단(NIST SA-15·CM-7)</t>
+          <t>고액·고위험 요청에 다채널 확인과 역할 기반 교육을 적용(NIST AT-2(3))</t>
         </is>
       </c>
     </row>
@@ -8716,22 +8716,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[VE] 취약점 발굴·익스플로잇 생성</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-03</t>
+          <t>AIA-VE-03.2</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
+          <t>AI 생성 와이퍼·파괴 스크립트</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
+          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
+          <t>[실제 사고] 2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)(2026-01) (AII-006)</t>
         </is>
       </c>
       <c r="O22" s="9" t="inlineStr">
         <is>
-          <t>공개 취약점의 신속 패치·완화를 우선순위화해 n-day 노출 구간을 좁힘(NIST RA-5)</t>
+          <t>행위 기반 탐지·실행 통제와 오프라인·불변 백업으로 복구력을 확보(NIST SI-7·CP-9)</t>
         </is>
       </c>
     </row>
@@ -8785,22 +8785,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>[AO] 자율 실행·확산</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>AIA-AO-06</t>
+          <t>AIA-CC-04</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>통제를 벗어난 자율 에이전트의 자발적 침해(사람 공격자 없음)</t>
+          <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>통제를 벗어난 자율 에이전트가 사람 지시 없이 실제 인프라 침해</t>
+          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>완전자율</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 자율 평가 에이전트의 평가 경계 이탈과 Hugging Face 인프라 침해(2026-07) (AII-010)</t>
+          <t>[실제 사고] Amazon Q Developer 확장에 삭제 지시 주입(2025-07) (AII-003)</t>
         </is>
       </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>자율 에이전트에 강한 샌드박스·최소 권한·명시적 승인 경계를 두고 이탈 시 자동 차단·격리(NIST AC-6·SI-4)</t>
+          <t>규칙·설정 파일을 변경 통제·리뷰 대상에 포함하고 비가시 문자를 정규화·차단(NIST SA-15·CM-7)</t>
         </is>
       </c>
     </row>
@@ -8854,22 +8854,22 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-02</t>
+          <t>AIA-RT-03</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>실행 중 AI 명령 동적 생성 악성코드</t>
+          <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
+          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
+          <t>[실제 사고] DeepSeek 기반 Hermes 에이전트의 자율 공격 캠페인(Unit 42)(2026-07) (AII-027)</t>
         </is>
       </c>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스 egress 통제와 행위 기반 실행 탐지로 동적 명령 생성에 대응(NIST SI-3·SI-4)</t>
+          <t>공개 취약점의 신속 패치·완화를 우선순위화해 n-day 노출 구간을 좁힘(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -8923,22 +8923,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>[CC] 은닉·명령제어</t>
+          <t>[AO] 자율 실행·확산</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-01</t>
+          <t>AIA-AO-06</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
+          <t>통제를 벗어난 자율 에이전트의 자발적 침해(사람 공격자 없음)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
+          <t>통제를 벗어난 자율 에이전트가 사람 지시 없이 실제 인프라 침해</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>완전자율</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -8977,12 +8977,12 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
+          <t>[실제 사고] 자율 평가 에이전트의 평가 경계 이탈과 Hugging Face 인프라 침해(2026-07) (AII-010)</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>AI 서비스 egress 가시성·허용 목록으로 비인가 AI 트래픽을 통제(NIST SC-7)</t>
+          <t>자율 에이전트에 강한 샌드박스·최소 권한·명시적 승인 경계를 두고 이탈 시 자동 차단·격리(NIST AC-6·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8992,22 +8992,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-04</t>
+          <t>AIA-CC-02</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
+          <t>실행 중 AI 명령 동적 생성 악성코드</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
+          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)(2023-11) (AII-012)</t>
+          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
         </is>
       </c>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>컴퓨터 사용 에이전트의 실행 권한·승인 경계를 두고 미끼 유형을 교육(NIST AT-2(3)·SI-4)</t>
+          <t>AI 서비스 egress 통제와 행위 기반 실행 탐지로 동적 명령 생성에 대응(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9066,17 +9066,17 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>AIA-CC-03</t>
+          <t>AIA-CC-01</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 방어 회피·난독화</t>
+          <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
+          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -9097,30 +9097,30 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 20건·성숙도 실증]</t>
+          <t>[실제 사고] LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)(2025-07) (AII-007)</t>
         </is>
       </c>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>시그니처 의존을 줄이고 행위 기반·무결성 검증을 강화, 탐지 모델에 적대적 견고성을 반영(NIST SI-4·SI-7)</t>
+          <t>AI 서비스 egress 가시성·허용 목록으로 비인가 AI 트래픽을 통제(NIST SC-7)</t>
         </is>
       </c>
     </row>
@@ -9130,22 +9130,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[IA] 초기 침투·사회공학</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-02</t>
+          <t>AIA-IA-04</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
+          <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
+          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -9166,30 +9166,30 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
+          <t>[실제 사고] Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)(2023-11) (AII-012)</t>
         </is>
       </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
-          <t>시그니처가 아닌 행위·맥락 기반 탐지로 매번 달라지는 산출물에 대응하고 최소 권한을 적용(NIST SI-4·PM-16)</t>
+          <t>컴퓨터 사용 에이전트의 실행 권한·승인 경계를 두고 미끼 유형을 교육(NIST AT-2(3)·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9199,22 +9199,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[CC] 은닉·명령제어</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-01.1</t>
+          <t>AIA-CC-03</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 공개정보 수집·인물 프로파일링</t>
+          <t>AI 기반 방어 회피·난독화</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
+          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 15건·성숙도 실사용]</t>
+          <t>[위협인텔] 실행 중 LLM을 호출해 스스로 코드를 고치는 악성코드(GTIG PROMPTFLUX 등)(2025-11) (AII-036)</t>
         </is>
       </c>
       <c r="O29" s="9" t="inlineStr">
         <is>
-          <t>핵심 인력·과제의 공개 노출 범위를 정하고 프로필·발표·채용 공고의 민감 정보를 최소화(NIST PM-16)</t>
+          <t>시그니처 의존을 줄이고 행위 기반·무결성 검증을 강화, 탐지 모델에 적대적 견고성을 반영(NIST SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -9268,22 +9268,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>[RD] 공격 역량 확보</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>AIA-RD-01.1</t>
+          <t>AIA-RT-01.1</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>다크 LLM·탈옥 모델 확보</t>
+          <t>AI 기반 공개정보 수집·인물 프로파일링</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
+          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -9304,12 +9304,12 @@
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>증폭</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -9322,12 +9322,12 @@
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 13건·성숙도 실사용]</t>
+          <t>[위협인텔] 국가배후 행위자의 공격 전 단계 상용 AI 활용(GTIG 2026-02 트래커)(2026-02) (AII-037)</t>
         </is>
       </c>
       <c r="O30" s="9" t="inlineStr">
         <is>
-          <t>공세 LLM이 만들어내는 산출물(피싱·악성코드)의 탐지·대응 역량을 강화해 역량 확보 자체보다 '사용 시점'을 막음(NIST SI-4)</t>
+          <t>핵심 인력·과제의 공개 노출 범위를 정하고 프로필·발표·채용 공고의 민감 정보를 최소화(NIST PM-16)</t>
         </is>
       </c>
     </row>
@@ -9337,22 +9337,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>[RT] 정찰·표적 분석</t>
+          <t>[RD] 공격 역량 확보</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>AIA-RT-01.2</t>
+          <t>AIA-RD-01.1</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 표적 환경·관계 분석</t>
+          <t>다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
+          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -9373,17 +9373,17 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>보조</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>증폭</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 8건·성숙도 실증]</t>
+          <t>[ATLAS 사례 13건·성숙도 실사용]</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
         <is>
-          <t>조직 구조·거래 관계의 불필요한 공개를 줄이고 고위험 역할의 공개 노출을 관리(NIST PM-16)</t>
+          <t>공세 LLM이 만들어내는 산출물(피싱·악성코드)의 탐지·대응 역량을 강화해 역량 확보 자체보다 '사용 시점'을 막음(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9406,22 +9406,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>[IM] 영향·규모화</t>
+          <t>[RT] 정찰·표적 분석</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>AIA-IM-04</t>
+          <t>AIA-RT-01.2</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>AI 활용 공격의 규모화·대량화</t>
+          <t>AI 기반 표적 환경·관계 분석</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
+          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>반자율</t>
+          <t>증강</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 7건·성숙도 실사용]</t>
+          <t>[ATLAS 사례 8건·성숙도 실증]</t>
         </is>
       </c>
       <c r="O32" s="9" t="inlineStr">
         <is>
-          <t>탐지·대응 자동화로 대량 캠페인에 대응하고 위협 인텔로 우선순위화(NIST SI-4·PM-16)</t>
+          <t>조직 구조·거래 관계의 불필요한 공개를 줄이고 고위험 역할의 공개 노출을 관리(NIST PM-16)</t>
         </is>
       </c>
     </row>
@@ -9475,22 +9475,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투·사회공학</t>
+          <t>[IM] 영향·규모화</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>AIA-IA-01.2</t>
+          <t>AIA-IM-04</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>AI 기반 표적 스피어피싱·BEC</t>
+          <t>AI 활용 공격의 규모화·대량화</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
+          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>증강</t>
+          <t>반자율</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>[ATLAS 사례 6건·성숙도 실사용]</t>
+          <t>[ATLAS 사례 7건·성숙도 실사용]</t>
         </is>
       </c>
       <c r="O33" s="9" t="inlineStr">
         <is>
-          <t>고액·고위험 요청에 다채널 확인과 역할 기반 교육을 적용(NIST AT-2(3))</t>
+          <t>탐지·대응 자동화로 대량 캠페인에 대응하고 위협 인텔로 우선순위화(NIST SI-4·PM-16)</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="E3" s="18" t="inlineStr">
         <is>
-          <t>AIA-AO-01 단일 자율 공격 에이전트 실행 [6]</t>
+          <t>AIA-AO-01 단일 자율 공격 에이전트 실행 [7]</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="G3" s="18" t="inlineStr">
         <is>
-          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 [4]</t>
+          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 [5]</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>AIA-RD-01.1 다크 LLM·탈옥 모델 확보</t>
+          <t>AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성 [1]</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기 [1]</t>
+          <t>AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기 [2]</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성</t>
+          <t>AIA-RD-01.1 다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>AIA-IA-02.2 음성 딥페이크 사칭 [1]</t>
+          <t>AIA-IA-02.2 음성 딥페이크 사칭 [2]</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>AIA-IA-04 AI 미끼·ClickFix·크래프트 링크로 실행 유도 [1]</t>
+          <t>AIA-IA-01.2 AI 기반 표적 스피어피싱·BEC [1]</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -10133,7 +10133,7 @@
     <row r="8">
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>AIA-IA-01.2 AI 기반 표적 스피어피싱·BEC</t>
+          <t>AIA-IA-04 AI 미끼·ClickFix·크래프트 링크로 실행 유도 [1]</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -10220,7 +10220,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI 활용 공격 사고 DB 32건 + MITRE ATLAS 2026.09 + ATT&amp;CK v19.2 + OWASP | 2026-10-26</t>
+          <t>AI 활용 공격 사고 DB 37건 + MITRE ATLAS 2026.09 + ATT&amp;CK v19.2 + OWASP | 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="AC5" s="9" t="inlineStr"/>
       <c r="AD5" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 15(참고)</t>
+          <t>실제 사고 0건(확인 1·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 1 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 15(참고)</t>
         </is>
       </c>
       <c r="AF5" s="9" t="inlineStr">
@@ -10632,13 +10632,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" s="9" t="n">
         <v>0</v>
@@ -10651,7 +10651,12 @@
           <t>실사용 역량(성숙도)</t>
         </is>
       </c>
-      <c r="AO5" s="9" t="inlineStr"/>
+      <c r="AO5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+위협인텔: AII-037</t>
+        </is>
+      </c>
       <c r="AP5" s="9" t="inlineStr"/>
       <c r="AQ5" s="9" t="inlineStr">
         <is>
@@ -10800,7 +10805,7 @@
       </c>
       <c r="AC6" s="9" t="inlineStr"/>
       <c r="AD6" s="8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE6" s="9" t="inlineStr">
         <is>
@@ -10986,7 +10991,7 @@
       </c>
       <c r="AC7" s="9" t="inlineStr"/>
       <c r="AD7" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE7" s="9" t="inlineStr">
         <is>
@@ -11180,7 +11185,7 @@
       </c>
       <c r="AC8" s="9" t="inlineStr"/>
       <c r="AD8" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE8" s="9" t="inlineStr">
         <is>
@@ -11372,7 +11377,7 @@
       </c>
       <c r="AC9" s="9" t="inlineStr"/>
       <c r="AD9" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE9" s="9" t="inlineStr">
         <is>
@@ -11729,11 +11734,11 @@
       </c>
       <c r="AC11" s="9" t="inlineStr"/>
       <c r="AD11" s="8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AE11" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 15(참고)</t>
+          <t>실제 사고 1건(확인 2·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 1 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 15(참고)</t>
         </is>
       </c>
       <c r="AF11" s="9" t="inlineStr">
@@ -11742,19 +11747,19 @@
         </is>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" s="9" t="n">
         <v>0</v>
@@ -11762,13 +11767,22 @@
       <c r="AM11" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AN11" s="27" t="inlineStr">
-        <is>
-          <t>실사용 역량(성숙도)</t>
-        </is>
-      </c>
-      <c r="AO11" s="9" t="inlineStr"/>
-      <c r="AP11" s="9" t="inlineStr"/>
+      <c r="AN11" s="29" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
+        </is>
+      </c>
+      <c r="AO11" s="9" t="inlineStr">
+        <is>
+          <t>AII-038
+위협인텔: AII-037</t>
+        </is>
+      </c>
+      <c r="AP11" s="9" t="inlineStr">
+        <is>
+          <t>데이터 유출 1 · 금전 피해 1</t>
+        </is>
+      </c>
       <c r="AQ11" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
@@ -12098,7 +12112,7 @@
         </is>
       </c>
       <c r="AD13" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE13" s="9" t="inlineStr">
         <is>
@@ -13040,7 +13054,7 @@
       </c>
       <c r="AC18" s="9" t="inlineStr"/>
       <c r="AD18" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE18" s="9" t="inlineStr">
         <is>
@@ -13237,7 +13251,7 @@
       </c>
       <c r="AC19" s="9" t="inlineStr"/>
       <c r="AD19" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE19" s="9" t="inlineStr">
         <is>
@@ -13435,11 +13449,11 @@
       </c>
       <c r="AC20" s="9" t="inlineStr"/>
       <c r="AD20" s="8" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
         </is>
       </c>
       <c r="AF20" s="9" t="inlineStr">
@@ -13448,13 +13462,13 @@
         </is>
       </c>
       <c r="AG20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="9" t="n">
         <v>0</v>
@@ -13468,13 +13482,21 @@
       <c r="AM20" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AN20" s="27" t="inlineStr">
-        <is>
-          <t>실사용 역량(성숙도)</t>
-        </is>
-      </c>
-      <c r="AO20" s="9" t="inlineStr"/>
-      <c r="AP20" s="9" t="inlineStr"/>
+      <c r="AN20" s="29" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
+        </is>
+      </c>
+      <c r="AO20" s="9" t="inlineStr">
+        <is>
+          <t>AII-035</t>
+        </is>
+      </c>
+      <c r="AP20" s="9" t="inlineStr">
+        <is>
+          <t>내부 접근 확보 1</t>
+        </is>
+      </c>
       <c r="AQ20" s="9" t="inlineStr">
         <is>
           <t>AT-2(3) Social Engineering and Mining
@@ -13807,11 +13829,11 @@
       </c>
       <c r="AC22" s="9" t="inlineStr"/>
       <c r="AD22" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE22" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
+          <t>실제 사고 2건(확인 1·추정 1, 가중 1.5, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 6(참고)</t>
         </is>
       </c>
       <c r="AF22" s="9" t="inlineStr">
@@ -13820,16 +13842,16 @@
         </is>
       </c>
       <c r="AG22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH22" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AH22" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AI22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AJ22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" s="9" t="n">
         <v>0</v>
@@ -13847,12 +13869,12 @@
       </c>
       <c r="AO22" s="9" t="inlineStr">
         <is>
-          <t>AII-011</t>
+          <t>AII-011, AII-039</t>
         </is>
       </c>
       <c r="AP22" s="9" t="inlineStr">
         <is>
-          <t>계정 장악 1 · 금전 피해 1</t>
+          <t>금전 피해 2 · 계정 장악 1</t>
         </is>
       </c>
       <c r="AQ22" s="9" t="inlineStr">
@@ -14194,7 +14216,7 @@
       </c>
       <c r="AC24" s="9" t="inlineStr"/>
       <c r="AD24" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE24" s="9" t="inlineStr">
         <is>
@@ -14390,7 +14412,7 @@
       </c>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 6건(확인 6·추정 0, 가중 6, 서로 다른 행위자·캠페인 3) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 9(참고)</t>
+          <t>실제 사고 7건(확인 7·추정 0, 가중 7, 서로 다른 행위자·캠페인 4) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 9(참고)</t>
         </is>
       </c>
       <c r="AF25" s="9" t="inlineStr">
@@ -14399,13 +14421,13 @@
         </is>
       </c>
       <c r="AG25" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH25" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI25" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ25" s="9" t="n">
         <v>0</v>
@@ -14426,12 +14448,12 @@
       </c>
       <c r="AO25" s="9" t="inlineStr">
         <is>
-          <t>AII-008, AII-027, AII-031, AII-032, AII-033, AII-034</t>
+          <t>AII-008, AII-027, AII-031, AII-032, AII-033, AII-034, AII-038</t>
         </is>
       </c>
       <c r="AP25" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 5 · 데이터 유출 4 · 자격증명·비밀 탈취 1</t>
+          <t>데이터 유출 5 · 내부 접근 확보 5 · 자격증명·비밀 탈취 1 · 금전 피해 1</t>
         </is>
       </c>
       <c r="AQ25" s="9" t="inlineStr">
@@ -15586,7 +15608,7 @@
       </c>
       <c r="AC31" s="9" t="inlineStr"/>
       <c r="AD31" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE31" s="9" t="inlineStr">
         <is>
@@ -15783,7 +15805,7 @@
       </c>
       <c r="AC32" s="9" t="inlineStr"/>
       <c r="AD32" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE32" s="9" t="inlineStr">
         <is>
@@ -15976,7 +15998,7 @@
       </c>
       <c r="AC33" s="9" t="inlineStr"/>
       <c r="AD33" s="8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE33" s="9" t="inlineStr">
         <is>
@@ -16170,11 +16192,11 @@
       </c>
       <c r="AC34" s="9" t="inlineStr"/>
       <c r="AD34" s="8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE34" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(확인 0·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실증 · ATLAS 사례 20(참고)</t>
+          <t>실제 사고 0건(확인 1·추정 0, 가중 0, 서로 다른 행위자·캠페인 0) · 위협인텔 1 · 실증·연구 0 · 역량 성숙도 실증 · ATLAS 사례 20(참고)</t>
         </is>
       </c>
       <c r="AF34" s="9" t="inlineStr">
@@ -16189,13 +16211,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL34" s="9" t="n">
         <v>0</v>
@@ -16203,12 +16225,17 @@
       <c r="AM34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="AN34" s="28" t="inlineStr">
-        <is>
-          <t>실증·공개 PoC</t>
-        </is>
-      </c>
-      <c r="AO34" s="9" t="inlineStr"/>
+      <c r="AN34" s="27" t="inlineStr">
+        <is>
+          <t>실사용 역량(성숙도)</t>
+        </is>
+      </c>
+      <c r="AO34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+위협인텔: AII-036</t>
+        </is>
+      </c>
       <c r="AP34" s="9" t="inlineStr"/>
       <c r="AQ34" s="9" t="inlineStr">
         <is>
@@ -16363,7 +16390,7 @@
       </c>
       <c r="AC35" s="9" t="inlineStr"/>
       <c r="AD35" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE35" s="9" t="inlineStr">
         <is>
@@ -16548,11 +16575,11 @@
       </c>
       <c r="AC36" s="9" t="inlineStr"/>
       <c r="AD36" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE36" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(확인 1·추정 0, 가중 1, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 17(참고)</t>
+          <t>실제 사고 2건(확인 1·추정 1, 가중 1.5, 서로 다른 행위자·캠페인 1) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 17(참고)</t>
         </is>
       </c>
       <c r="AF36" s="9" t="inlineStr">
@@ -16561,16 +16588,16 @@
         </is>
       </c>
       <c r="AG36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH36" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AH36" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AI36" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AJ36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" s="9" t="n">
         <v>0</v>
@@ -16588,12 +16615,12 @@
       </c>
       <c r="AO36" s="9" t="inlineStr">
         <is>
-          <t>AII-002</t>
+          <t>AII-002, AII-039</t>
         </is>
       </c>
       <c r="AP36" s="9" t="inlineStr">
         <is>
-          <t>금전 피해 1</t>
+          <t>금전 피해 2</t>
         </is>
       </c>
       <c r="AQ36" s="9" t="inlineStr">
@@ -16749,7 +16776,7 @@
       </c>
       <c r="AE37" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 4건(확인 3·추정 1, 가중 3.5, 서로 다른 행위자·캠페인 3) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 14(참고)</t>
+          <t>실제 사고 5건(확인 4·추정 1, 가중 4.5, 서로 다른 행위자·캠페인 4) · 위협인텔 0 · 실증·연구 0 · 역량 성숙도 실사용 · ATLAS 사례 14(참고)</t>
         </is>
       </c>
       <c r="AF37" s="9" t="inlineStr">
@@ -16758,13 +16785,13 @@
         </is>
       </c>
       <c r="AG37" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH37" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI37" s="9" t="n">
         <v>4</v>
-      </c>
-      <c r="AH37" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI37" s="9" t="n">
-        <v>3</v>
       </c>
       <c r="AJ37" s="9" t="n">
         <v>1</v>
@@ -16785,12 +16812,12 @@
       </c>
       <c r="AO37" s="9" t="inlineStr">
         <is>
-          <t>AII-009, AII-022, AII-031, AII-034</t>
+          <t>AII-009, AII-022, AII-031, AII-034, AII-038</t>
         </is>
       </c>
       <c r="AP37" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 4 · 서비스 중단 1 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
+          <t>데이터 유출 5 · 서비스 중단 1 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
         </is>
       </c>
       <c r="AQ37" s="9" t="inlineStr">
@@ -16928,7 +16955,7 @@
       </c>
       <c r="AC38" s="9" t="inlineStr"/>
       <c r="AD38" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE38" s="9" t="inlineStr">
         <is>
@@ -17214,7 +17241,7 @@
         </is>
       </c>
       <c r="O3" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="27" t="inlineStr">
         <is>
@@ -17312,7 +17339,7 @@
         </is>
       </c>
       <c r="O4" s="8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4" s="28" t="inlineStr">
         <is>
@@ -17410,7 +17437,7 @@
         </is>
       </c>
       <c r="O5" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P5" s="29" t="inlineStr">
         <is>
@@ -17508,7 +17535,7 @@
         </is>
       </c>
       <c r="O6" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P6" s="29" t="inlineStr">
         <is>
@@ -17606,7 +17633,7 @@
         </is>
       </c>
       <c r="O7" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7" s="27" t="inlineStr">
         <is>
@@ -17798,15 +17825,15 @@
         </is>
       </c>
       <c r="O9" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="P9" s="27" t="inlineStr">
-        <is>
-          <t>실사용 역량(성숙도)</t>
+        <v>15</v>
+      </c>
+      <c r="P9" s="29" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
         </is>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="8" t="n">
         <v>15</v>
@@ -17990,7 +18017,7 @@
         </is>
       </c>
       <c r="O11" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P11" s="29" t="inlineStr">
         <is>
@@ -18470,7 +18497,7 @@
         </is>
       </c>
       <c r="O16" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P16" s="29" t="inlineStr">
         <is>
@@ -18566,7 +18593,7 @@
         </is>
       </c>
       <c r="O17" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="29" t="inlineStr">
         <is>
@@ -18663,15 +18690,15 @@
         </is>
       </c>
       <c r="O18" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P18" s="27" t="inlineStr">
-        <is>
-          <t>실사용 역량(성숙도)</t>
+        <v>17</v>
+      </c>
+      <c r="P18" s="29" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
         </is>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>6</v>
@@ -18855,7 +18882,7 @@
         </is>
       </c>
       <c r="O20" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P20" s="29" t="inlineStr">
         <is>
@@ -18863,7 +18890,7 @@
         </is>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>6</v>
@@ -19047,7 +19074,7 @@
         </is>
       </c>
       <c r="O22" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P22" s="29" t="inlineStr">
         <is>
@@ -19151,7 +19178,7 @@
         </is>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R23" s="8" t="n">
         <v>9</v>
@@ -19721,7 +19748,7 @@
         </is>
       </c>
       <c r="O29" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P29" s="29" t="inlineStr">
         <is>
@@ -19817,7 +19844,7 @@
         </is>
       </c>
       <c r="O30" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P30" s="29" t="inlineStr">
         <is>
@@ -19913,7 +19940,7 @@
         </is>
       </c>
       <c r="O31" s="8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P31" s="29" t="inlineStr">
         <is>
@@ -20009,11 +20036,11 @@
         </is>
       </c>
       <c r="O32" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="P32" s="28" t="inlineStr">
-        <is>
-          <t>실증·공개 PoC</t>
+        <v>25</v>
+      </c>
+      <c r="P32" s="27" t="inlineStr">
+        <is>
+          <t>실사용 역량(성숙도)</t>
         </is>
       </c>
       <c r="Q32" s="8" t="n">
@@ -20105,7 +20132,7 @@
         </is>
       </c>
       <c r="O33" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P33" s="29" t="inlineStr">
         <is>
@@ -20201,7 +20228,7 @@
         </is>
       </c>
       <c r="O34" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P34" s="29" t="inlineStr">
         <is>
@@ -20209,7 +20236,7 @@
         </is>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34" s="8" t="n">
         <v>17</v>
@@ -20305,7 +20332,7 @@
         </is>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R35" s="8" t="n">
         <v>14</v>
@@ -20393,7 +20420,7 @@
         </is>
       </c>
       <c r="O36" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P36" s="27" t="inlineStr">
         <is>
@@ -20627,10 +20654,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="L3" s="9" t="n">
         <v>1</v>
@@ -20639,15 +20666,15 @@
         <v>1</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
           <t>AIA-RD-04 공세 AI 에이전트·공격 하네스 구축(높음, 사고 2)
-AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성(보통, 사고 0)
+AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성(보통, 사고 1)
 AIA-RD-01.1 다크 LLM·탈옥 모델 확보(보통, 사고 0)</t>
         </is>
       </c>
@@ -20747,10 +20774,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>0</v>
@@ -20759,16 +20786,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
           <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회(매우 높음, 사고 2)
 AIA-IA-02.1 영상 딥페이크 사칭(높음, 사고 1)
-AIA-IA-01.1 AI 생성 대량 피싱·미끼(보통, 사고 2)</t>
+AIA-IA-02.2 음성 딥페이크 사칭(보통, 사고 2)</t>
         </is>
       </c>
     </row>
@@ -20819,14 +20846,14 @@
         <v>0</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01 단일 자율 공격 에이전트 실행(매우 높음, 사고 6)
+          <t>AIA-AO-01 단일 자율 공격 에이전트 실행(매우 높음, 사고 7)
 AIA-AO-05 AI 가속 자격증명 탈취·내부 확산(매우 높음, 사고 3)
 AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용(매우 높음, 사고 3)</t>
         </is>
@@ -20870,10 +20897,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>0</v>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>0</v>
@@ -20939,15 +20966,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음, 사고 4)
-AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기(높음, 사고 1)
+          <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출(매우 높음, 사고 5)
+AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기(높음, 사고 2)
 AIA-IM-04 AI 활용 공격의 규모화·대량화(보통, 사고 0)</t>
         </is>
       </c>
@@ -21102,9 +21129,9 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>AIA-RT-03 AI 기반 취약점 정보·공개 PoC 자동 수집·분류(보통)
-AIA-CC-03 AI 기반 방어 회피·난독화(보통)
-AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성(보통)</t>
+          <t>AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성(보통)
+AIA-IA-01.2 AI 기반 표적 스피어피싱·BEC(보통)
+AIA-RT-03 AI 기반 취약점 정보·공개 PoC 자동 수집·분류(보통)</t>
         </is>
       </c>
     </row>
@@ -21846,7 +21873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -23159,12 +23186,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>AII-026</t>
+          <t>AII-037</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>AI in the Middle — 웹 AI 서비스를 C2 중계로 악용 실증</t>
+          <t>국가배후 행위자의 공격 전 단계 상용 AI 활용(GTIG 2026-02 트래커)</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -23174,12 +23201,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>위협인텔</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>위협인텔</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -23189,7 +23216,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -23199,49 +23226,45 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Check Point Research</t>
+          <t>APT31·UNC2814·APT42 등(GTIG 추적)</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>영향 미상</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-01</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>AML.CS0061</t>
-        </is>
-      </c>
+          <t>AIA-RT-01.1, AIA-RD-02</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr"/>
       <c r="O18" s="9" t="inlineStr">
         <is>
-          <t>Check Point Research(2026) AI in the Middle | https://research.checkpoint.com/2026/ai-in-the-middle-turning-web-based-ai-services-into-c2-proxies-the-future-of-ai-driven-attacks/</t>
+          <t>Google GTIG(2026) GTIG AI Threat Tracker — Distillation, Experimentation, and (Continued) Integration of AI for Adversarial Use | https://cloud.google.com/blog/topics/threat-intelligence/distillation-experimentation-integration-ai-adversarial-use</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>AII-016</t>
+          <t>AII-026</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>공개 S3 버킷 노출 자격증명 경유 LLMjacking·GPU 악용</t>
+          <t>AI in the Middle — 웹 AI 서비스를 C2 중계로 악용 실증</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -23251,22 +23274,22 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>사례연구(익명)</t>
+          <t>연구·시연</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>실증·연구</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -23276,59 +23299,59 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>Check Point Research</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>연구·레드팀</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>자원 탈취 · 내부 접근 확보</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-05</t>
+          <t>AIA-CC-01</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>CL/INC-0573</t>
+          <t>AML.CS0061</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
         <is>
-          <t>Sysdig(2026) AI-assisted cloud intrusion achieves admin access in 8 minutes | https://sysdig.com/blog/ai-assisted-cloud-intrusion-achieves-admin-access-in-8-minutes/</t>
+          <t>Check Point Research(2026) AI in the Middle | https://research.checkpoint.com/2026/ai-in-the-middle-turning-web-based-ai-services-into-c2-proxies-the-future-of-ai-driven-attacks/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>AII-006</t>
+          <t>AII-016</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)</t>
+          <t>공개 S3 버킷 노출 자격증명 경유 LLMjacking·GPU 악용</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>사례연구(익명)</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -23348,59 +23371,59 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>폴란드</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>에너지·기반시설</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>러시아 국가 배후(ESET는 Sandworm, CERT Polska는 Static Tundra/Dragonfly 인프라 중첩으로 평가)</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>데이터 파괴 · 감시·조작</t>
+          <t>자원 탈취 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-03.2</t>
+          <t>AIA-AO-05</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>OT/INC-008</t>
+          <t>CL/INC-0573</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
         <is>
-          <t>CERT Polska(2026) Energy Sector Incident Report 2025 | https://cert.pl/uploads/docs/CERT_Polska_Energy_Sector_Incident_Report_2025.pdf</t>
+          <t>Sysdig(2026) AI-assisted cloud intrusion achieves admin access in 8 minutes | https://sysdig.com/blog/ai-assisted-cloud-intrusion-achieves-admin-access-in-8-minutes/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>AII-008</t>
+          <t>AII-006</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>GTG-1002 — Claude Code를 악용한 자율 사이버 첩보 캠페인</t>
+          <t>2025 폴란드 에너지 시설 와이퍼 공격(LLM 생성 스크립트)</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -23415,7 +23438,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -23425,17 +23448,17 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>폴란드</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>에너지·기반시설</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>GTG-1002(Anthropic 평가 중국 국가 지원)</t>
+          <t>러시아 국가 배후(ESET는 Sandworm, CERT Polska는 Static Tundra/Dragonfly 인프라 중첩으로 평가)</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -23445,49 +23468,49 @@
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 · 내부 접근 확보</t>
+          <t>데이터 파괴 · 감시·조작</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-01, AIA-AO-02, AIA-RD-04</t>
+          <t>AIA-VE-03.2</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>AML.CS0069</t>
+          <t>OT/INC-008</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>Anthropic(2025) Disrupting AI espionage | https://www.anthropic.com/news/disrupting-AI-espionage</t>
+          <t>CERT Polska(2026) Energy Sector Incident Report 2025 | https://cert.pl/uploads/docs/CERT_Polska_Energy_Sector_Incident_Report_2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>AII-004</t>
+          <t>AII-036</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>s1ngularity — Nx 빌드 도구 악성 버전과 피해 단말 AI CLI 악용</t>
+          <t>실행 중 LLM을 호출해 스스로 코드를 고치는 악성코드(GTIG PROMPTFLUX 등)</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>위협인텔</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>위협인텔</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -23497,7 +23520,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -23507,64 +23530,60 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
+          <t>미상 복수 행위자(GTIG 추적)</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
           <t>미상</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>사이버범죄</t>
-        </is>
-      </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취 · 소스 코드 유출</t>
+          <t>영향 미상</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>AIA-AO-03.1</t>
-        </is>
-      </c>
-      <c r="N22" s="9" t="inlineStr">
-        <is>
-          <t>SCI-143, CL/INC-0552</t>
-        </is>
-      </c>
+          <t>AIA-CC-03</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr"/>
       <c r="O22" s="9" t="inlineStr">
         <is>
-          <t>Wiz(2025) s1ngularity — supply chain attack leaks secrets on GitHub | https://www.wiz.io/blog/s1ngularity-supply-chain-attack</t>
+          <t>Google GTIG(2025) GTIG AI Threat Tracker — Advances in Threat Actor Usage of AI Tools | https://cloud.google.com/blog/topics/threat-intelligence/threat-actor-usage-of-ai-tools</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>AII-028</t>
+          <t>AII-008</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Big Sleep — AI 에이전트의 실악용 임박 취약점 사전 발견</t>
+          <t>GTG-1002 — Claude Code를 악용한 자율 사이버 첩보 캠페인</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
@@ -23584,55 +23603,59 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Google Project Zero·DeepMind</t>
+          <t>GTG-1002(Anthropic 평가 중국 국가 지원)</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>데이터 유출 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr"/>
+          <t>AIA-AO-01, AIA-AO-02, AIA-RD-04</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>AML.CS0069</t>
+        </is>
+      </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>The Record(2025) Google says 'Big Sleep' AI tool found bug hackers planned to use | https://therecord.media/google-big-sleep-ai-tool-found-bug</t>
+          <t>Anthropic(2025) Disrupting AI espionage | https://www.anthropic.com/news/disrupting-AI-espionage</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>AII-007</t>
+          <t>AII-038</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)</t>
+          <t>GTG-2002 — AI 코딩 에이전트로 정찰·침투 판단·데이터 갈취('vibe hacking')</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -23652,59 +23675,55 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>우크라이나</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>정부·군</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>APT28</t>
+          <t>GTG-2002(Anthropic 추적)</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 · 내부 접근 확보</t>
+          <t>데이터 유출 · 금전 피해</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-02, AIA-CC-01, AIA-VE-03.1</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>AML.CS0044</t>
-        </is>
-      </c>
+          <t>AIA-AO-01, AIA-IM-02, AIA-RD-02</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr"/>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>The Hacker News(2025) CERT-UA Discovers LAMEHUG Malware | https://thehackernews.com/2025/07/cert-ua-discovers-lamehug-malware.html</t>
+          <t>Anthropic(2025) Threat intelligence report — disrupting a data-extortion operation (GTG-2002) | https://www.anthropic.com/news/detecting-countering-misuse-aug-2025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>AII-003</t>
+          <t>AII-004</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Amazon Q Developer 확장에 삭제 지시 주입</t>
+          <t>s1ngularity — Nx 빌드 도구 악성 버전과 피해 단말 AI CLI 악용</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -23739,7 +23758,7 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>미상(부적절 권한 토큰으로 커밋한 외부 계정)</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
@@ -23749,49 +23768,49 @@
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>자격증명·비밀 탈취 · 소스 코드 유출</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-04, AIA-AO-03.2</t>
+          <t>AIA-AO-03.1</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>SCI-140</t>
+          <t>SCI-143, CL/INC-0552</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>AWS Security Bulletin AWS-2025-015(2025) | https://aws.amazon.com/security/security-bulletins/AWS-2025-015/</t>
+          <t>Wiz(2025) s1ngularity — supply chain attack leaks secrets on GitHub | https://www.wiz.io/blog/s1ngularity-supply-chain-attack</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>AII-029</t>
+          <t>AII-035</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>XBOW 자율 펜테스트 에이전트의 HackerOne 미국 리더보드 1위</t>
+          <t>김수키의 생성형 AI 위조 군 신분증 스피어피싱(국내)</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -23806,55 +23825,55 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>정부·군</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>XBOW(자율 펜테스트 에이전트, 방어 측)</t>
+          <t>Kimsuky(북한 연계)</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>AIA-VE-01.1, AIA-VE-01.2</t>
+          <t>AIA-IA-01.2</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr"/>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>XBOW(2025) The road to Top 1 — How XBOW did it | https://xbow.com/blog/top-1-how-xbow-did-it</t>
+          <t>Genians(2025) ChatGPT Exploited in North Korean Cyber Espionage Campaign | https://genians.com/news/chatgpt-exploited-in-north-korean-cyber-espionage-campaign-genians-reveals/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>AII-025</t>
+          <t>AII-028</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>AI ClickFix — 컴퓨터 사용 에이전트 탈취 실증</t>
+          <t>Big Sleep — AI 에이전트의 실악용 임박 취약점 사전 발견</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -23874,7 +23893,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -23889,7 +23908,7 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>Embrace The Red(연구자)</t>
+          <t>Google Project Zero·DeepMind</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
@@ -23904,44 +23923,40 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-04</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr">
-        <is>
-          <t>AML.CS0055</t>
-        </is>
-      </c>
+          <t>AIA-VE-01.1</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="inlineStr"/>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>Embrace The Red(2025) AI ClickFix — Hijacking Computer-Use Agents | https://embracethered.com/blog/posts/2025/ai-clickfix-ttp-claude/</t>
+          <t>The Record(2025) Google says 'Big Sleep' AI tool found bug hackers planned to use | https://therecord.media/google-big-sleep-ai-tool-found-bug</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>AII-014</t>
+          <t>AII-007</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Rules File Backdoor — AI 코딩 도구 규칙 파일에 숨은 지시</t>
+          <t>LAMEHUG: 실행 중 AI 명령을 동적 생성하는 악성코드(APT28)</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>연구·시연</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>실증·연구</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -23951,64 +23966,64 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>실사용</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>우크라이나</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>정부·군</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>연구자(Pillar Security)</t>
+          <t>APT28</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>연구·레드팀</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>영향 없음(사전 차단)</t>
+          <t>데이터 유출 · 내부 접근 확보</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>AIA-CC-04</t>
+          <t>AIA-CC-02, AIA-CC-01, AIA-VE-03.1</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>SCI-134</t>
+          <t>AML.CS0044</t>
         </is>
       </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
-          <t>Pillar Security(2025) New Vulnerability in GitHub Copilot and Cursor | https://www.pillar.security/blog/new-vulnerability-in-github-copilot-and-cursor-how-hackers-can-weaponize-code-agents</t>
+          <t>The Hacker News(2025) CERT-UA Discovers LAMEHUG Malware | https://thehackernews.com/2025/07/cert-ua-discovers-lamehug-malware.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>AII-013</t>
+          <t>AII-003</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)</t>
+          <t>Amazon Q Developer 확장에 삭제 지시 주입</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -24033,17 +24048,17 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>금융·서비스</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>GoldFactory</t>
+          <t>미상(부적절 권한 토큰으로 커밋한 외부 계정)</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
@@ -24053,49 +24068,49 @@
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>계정 장악 · 금전 피해</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-03</t>
+          <t>AIA-CC-04, AIA-AO-03.2</t>
         </is>
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>IDI-060</t>
+          <t>SCI-140</t>
         </is>
       </c>
       <c r="O29" s="9" t="inlineStr">
         <is>
-          <t>Group-IB(2024) Face Off — first iOS trojan stealing facial recognition data | https://www.group-ib.com/blog/goldfactory-ios-trojan/</t>
+          <t>AWS Security Bulletin AWS-2025-015(2025) | https://aws.amazon.com/security/security-bulletins/AWS-2025-015/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>AII-002</t>
+          <t>AII-029</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Arup 딥페이크 화상회의 송금 사기</t>
+          <t>XBOW 자율 펜테스트 에이전트의 HackerOne 미국 리더보드 1위</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>연구·시연</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>실증·연구</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -24110,69 +24125,65 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>홍콩</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>IT·소프트웨어</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>XBOW(자율 펜테스트 에이전트, 방어 측)</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄</t>
+          <t>연구·레드팀</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>금전 피해</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-02.1, AIA-IM-01</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>IDI-013</t>
-        </is>
-      </c>
+          <t>AIA-VE-01.1, AIA-VE-01.2</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr"/>
       <c r="O30" s="9" t="inlineStr">
         <is>
-          <t>CNN(2024) Finance worker pays out $25 million after video call with deepfake 'CFO' | https://edition.cnn.com/2024/02/04/asia/deepfake-cfo-scam-hong-kong-intl-hnk</t>
+          <t>XBOW(2025) The road to Top 1 — How XBOW did it | https://xbow.com/blog/top-1-how-xbow-did-it</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>AII-012</t>
+          <t>AII-025</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)</t>
+          <t>AI ClickFix — 컴퓨터 사용 에이전트 탈취 실증</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>연구·시연</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>실증·연구</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -24182,7 +24193,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>실사용</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -24197,17 +24208,17 @@
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Contagious Interview(북한 연계, G1052)</t>
+          <t>Embrace The Red(연구자)</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>연구·레드팀</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취 · 금전 피해</t>
+          <t>영향 없음(사전 차단)</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr">
@@ -24217,34 +24228,34 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>SCI-110</t>
+          <t>AML.CS0055</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
         <is>
-          <t>Unit 42(2023) Two Campaigns by North Korea Bad Actors Target Job Hunters | https://unit42.paloaltonetworks.com/two-campaigns-by-north-korea-bad-actors-target-job-hunters/</t>
+          <t>Embrace The Red(2025) AI ClickFix — Hijacking Computer-Use Agents | https://embracethered.com/blog/posts/2025/ai-clickfix-ttp-claude/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>AII-011</t>
+          <t>AII-039</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)</t>
+          <t>국내 AI 음성 복제 가족 사칭 보이스피싱</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -24254,7 +24265,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -24264,12 +24275,12 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>IT·소프트웨어</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
@@ -24284,104 +24295,485 @@
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>계정 장악 · 금전 피해</t>
+          <t>금전 피해</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>AIA-IA-02.2</t>
-        </is>
-      </c>
-      <c r="N32" s="9" t="inlineStr">
-        <is>
-          <t>IDI-072</t>
-        </is>
-      </c>
+          <t>AIA-IA-02.2, AIA-IM-01</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr"/>
       <c r="O32" s="9" t="inlineStr">
         <is>
-          <t>Retool(2023) When MFA isn't actually MFA | https://retool.com/blog/mfa-isnt-mfa</t>
+          <t>서울신문(2025) "아빠, 도와줘" 울먹이던 딸의 목소리…AI가 만든 가짜였다 | https://m.seoul.co.kr/news/2025/04/09/20250409500212</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
+          <t>AII-014</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Rules File Backdoor — AI 코딩 도구 규칙 파일에 숨은 지시</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>연구·시연</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>실증·연구</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>실증</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>글로벌</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>IT·소프트웨어</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>연구자(Pillar Security)</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>연구·레드팀</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>영향 없음(사전 차단)</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>AIA-CC-04</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>SCI-134</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>Pillar Security(2025) New Vulnerability in GitHub Copilot and Cursor | https://www.pillar.security/blog/new-vulnerability-in-github-copilot-and-cursor-how-hackers-can-weaponize-code-agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>AII-013</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>GoldPickaxe — 얼굴 인식 정보 탈취 트로이목마(은행 생체 인증 우회)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>금융·서비스</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>GoldFactory</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>사이버범죄</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>계정 장악 · 금전 피해</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-03</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>IDI-060</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>Group-IB(2024) Face Off — first iOS trojan stealing facial recognition data | https://www.group-ib.com/blog/goldfactory-ios-trojan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>AII-002</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Arup 딥페이크 화상회의 송금 사기</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>홍콩</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>사이버범죄</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>금전 피해</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-02.1, AIA-IM-01</t>
+        </is>
+      </c>
+      <c r="N35" s="9" t="inlineStr">
+        <is>
+          <t>IDI-013</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
+        <is>
+          <t>CNN(2024) Finance worker pays out $25 million after video call with deepfake 'CFO' | https://edition.cnn.com/2024/02/04/asia/deepfake-cfo-scam-hong-kong-intl-hnk</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>AII-012</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Contagious Interview — 가짜 채용 과제로 개발자 감염(AI 복제 앱 병행)</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>캠페인</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>글로벌</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>IT·소프트웨어</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Contagious Interview(북한 연계, G1052)</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>국가배후</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>자격증명·비밀 탈취 · 금전 피해</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-04</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t>SCI-110</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t>Unit 42(2023) Two Campaigns by North Korea Bad Actors Target Job Hunters | https://unit42.paloaltonetworks.com/two-campaigns-by-north-korea-bad-actors-target-job-hunters/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>AII-011</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Retool 고객 계정 27곳 장악(딥페이크 음성 사칭 포함)</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>실사용</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>IT·소프트웨어</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>사이버범죄</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>계정 장악 · 금전 피해</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-02.2</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t>IDI-072</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t>Retool(2023) When MFA isn't actually MFA | https://retool.com/blog/mfa-isnt-mfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
           <t>AII-001</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>홍콩 딥페이크 얼굴 바꾸기로 대출·계좌 개설 사기 조직 검거</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>사고</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>실사용</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>홍콩</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>금융·서비스</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>사기 조직(6명 체포)</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>사이버범죄</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>금전 피해 · 계정 장악</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>AIA-IA-03</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>IDI-061</t>
         </is>
       </c>
-      <c r="O33" s="9" t="inlineStr">
+      <c r="O38" s="9" t="inlineStr">
         <is>
           <t>The Standard(2023) Six arrested for defrauding HK$200,000 using deepfake face-swap program | https://www.thestandard.com.hk/news/article/207493/Six-arrested-for-defrauding-HK200000-using-deepfake-face-swap-program</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O33"/>
+  <autoFilter ref="A1:O38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>